--- a/processed_products_data_clean.xlsx
+++ b/processed_products_data_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturpietrzak/Documents/vsc/customer-service-llm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B383E4BE-4BCE-B944-8955-5873386850DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E51B0B-305E-8B41-AD73-03E2562F466D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="860" windowWidth="36000" windowHeight="22520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="877">
   <si>
     <t>id</t>
   </si>
@@ -1241,9 +1241,6 @@
     <t>Powerbank 10.000mAh USB-A USB-C PD 22,5W</t>
   </si>
   <si>
-    <t>Akcesoria GSM</t>
-  </si>
-  <si>
     <t>Pojemność nominalna: 10 000 mAh
 Rodzaj ogniwa: Litowo-polimerowy
 Rodzaje złączy: USB Typu-A (Out), USB Typu-C (In/Out)
@@ -1991,9 +1988,6 @@
   </si>
   <si>
     <t>1TB M.2 PCIe Gen4 NVMe KC3000</t>
-  </si>
-  <si>
-    <t>Dysk twardy/sieciowy</t>
   </si>
   <si>
     <t>Przeznaczenie produktu: PC, Gaming
@@ -2484,9 +2478,6 @@
     <t>512GB 2,5" SATA SSD CX400</t>
   </si>
   <si>
-    <t>Dyski twarde HDD i SSD</t>
-  </si>
-  <si>
     <t>Przeznaczenie produktu: PC
 Pojemność: 512 GB
 Format: 2.5"
@@ -3202,9 +3193,6 @@
 Wysokiej jakości komponenty oraz grafenowa osłona termiczna gwarantują niezawodną pracę. Czujniki termiczne, zmniejszone zużycie energii oraz technologia SmartECC dbają o utrzymanie stabilnej wydajności w każdej sytuacji. Niezależnie od systemu, z którego korzystasz, Patriot Viper VP4300 Lite zapewni Ci idealne połączenia osiągów, bezpieczeństwa i wytrzymałości.</t>
   </si>
   <si>
-    <t>Inteligentne zegarki</t>
-  </si>
-  <si>
     <t>Garmin</t>
   </si>
   <si>
@@ -4173,9 +4161,6 @@
   </si>
   <si>
     <t>GeForce RTX 4070 SUPER XLR8 Gaming VERTO X3 OC 12GB GDDR6X</t>
-  </si>
-  <si>
-    <t>Karta graficzna</t>
   </si>
   <si>
     <t>Seria karty graficznej: GeForce RTX z serii 40
@@ -5187,9 +5172,6 @@
   </si>
   <si>
     <t>Eisa Max</t>
-  </si>
-  <si>
-    <t>Klawiatura</t>
   </si>
   <si>
     <t>Rodzaj przełączników: Mechaniczne - Mint Mambo
@@ -6143,9 +6125,6 @@
     <t>Inspiron 3535 Ryzen 7 7730U/32GB/1TB/Win11 120Hz Srebrny</t>
   </si>
   <si>
-    <t>Laptop/Notebook/Ultrabook</t>
-  </si>
-  <si>
     <t>Procesor: AMD Ryzen™ 7 7730U (8 rdzeni, 16 wątków, 2.00–4.50 GHz, 20 MB cache)
 Pamięć RAM: 32 GB (DDR4, 3200 MHz)
 Maksymalna obsługiwana ilość pamięci RAM: 32 GB
@@ -6422,9 +6401,6 @@
     <t>Yoga 7 2-in-1 Ultra 5-125H/16GB/1TB/Win11</t>
   </si>
   <si>
-    <t>Laptopy/Notebooki/Ultrabooki</t>
-  </si>
-  <si>
     <t>Procesor: Intel® Core™ Ultra 5 125H (14 rdzeni, 18 wątków, 1.20-4.50 GHz, 18MB cache)
 Pamięć RAM: 16 GB (LPDDR5x, 7467 MHz)
 Maksymalna obsługiwana ilość pamięci RAM: 16 GB
@@ -6489,738 +6465,6 @@
   </si>
   <si>
     <t>Acer</t>
-  </si>
-  <si>
-    <t>Chromebook 315 N4500/8GB/128/FHD ChromeOS</t>
-  </si>
-  <si>
-    <t>Procesor: Intel® Celeron N4500 (2 rdzenie, 2 wątki, 1.10-2.80 GHz, 4 MB cache)
-Pamięć RAM: 8 GB (LPDDR4x, 2133 MHz)
-Maksymalna obsługiwana ilość pamięci RAM: 8 GB
-Liczba gniazd pamięci (ogółem / wolne): 0/0 (pamięć wlutowana)
-Dysk eMMC: 128 GB
-Dotykowy ekran: Nie
-Typ ekranu: Matowy, LED, IPS
-Przekątna ekranu: 15,6"
-Rozdzielczość ekranu: 1920 x 1080 (Full HD)
-Karta graficzna: Intel UHD Graphics
-Pamięć karty graficznej: Pamięć współdzielona
-Dźwięk: Wbudowane głośniki stereo; Wbudowane dwa mikrofony
-Kamera internetowa: HD
-Łączność: Wi-Fi 6; Moduł Bluetooth 5.0
-Złącza: USB 3.2 Gen. 1 - 2 szt.; USB Typu-C (z DisplayPort) - 1 szt.; USB Typu-C (z DisplayPort i Power Delivery) - 1 szt.; Czytnik kart pamięci microSD - 1 szt.; Wyjście słuchawkowe/wejście mikrofonowe - 1 szt.
-Typ baterii: Litowo-jonowa
-Kolor dominujący: Srebrny
-Czytnik linii papilarnych: Nie
-Podświetlana klawiatura: Nie
-Zabezpieczenia: Możliwość zabezpieczenia linką (port Kensington Lock); Szyfrowanie TPM
-System operacyjny: Chrome OS
-Dołączone oprogramowanie: Partycja recovery (opcja przywrócenia systemu z dysku)
-Zasilacz: 45 W; Wtyk: USB-C
-Dodatkowe informacje: Wydzielona klawiatura numeryczna; Wielodotykowy, intuicyjny touchpad
-Wysokość: 20 mm
-Szerokość: 366 mm
-Głębokość: 244 mm
-Waga: 1,60 kg
-Dołączone akcesoria: Zasilacz
-Rodzaj gwarancji: Standardowa
-Gwarancja: 24 miesiące (gwarancja producenta)</t>
-  </si>
-  <si>
-    <t>&lt;div class="content"&gt;&lt;!-- Xkom_Only --&gt;
-&lt;div class="row text-left fresh-content"&gt;
-	&lt;div class="col-md-2 text-center"&gt;
-		&lt;img alt="stoperplay ikona" class="ico lazyload" decoding="async" fetchpriority="low" data-src="https://satysfakcja.stati.pl/icons_all/stoperplay.svg"&gt;&lt;/div&gt;
-	&lt;div class="col-md-10"&gt;
-		&lt;h2 class="text-left"&gt;
-			Poznaj Acer Chromebook 315 w 100 sekund&lt;/h2&gt;
-		&lt;p&gt;
-			Chcesz lepiej poznać Acer Chromebook 315? Oglądając poniższy materiał wideo, w zaledwie 100 sekund odkryjesz wszystkie cechy, jakie ma ten produkt.&lt;/p&gt;
-		&lt;div class="video-container" style="position:relative;padding-bottom:56.25%; background: none; margin: 30px 0 40px 0;height:0;overflow:hidden;border-radius: 30px"&gt;
-			&lt;div class="embed-responsive embed-responsive-16by9"&gt;
-				&lt;iframe class="embed-responsive-item lazyload" style="position:absolute;top:0;left:0;width:100%;height:100%;border:none;" data-src="https://www.youtube-nocookie.com/embed/frtvM-EK0SY?rel=0&amp;amp;showinfo=0&amp;amp;controls=0"&gt;&lt;/iframe&gt;&lt;/div&gt;
-		&lt;/div&gt;
-	&lt;/div&gt;
-&lt;/div&gt;
-&lt;!-- Xkom_Only end --&gt;
-&lt;style type="text/css"&gt;
-.dbIxxS .product-description .elementor-8 p {
-margin: inherit !important;
-margin-left: inherit !important;
-margin-right: inherit !important;
-margin-top: inherit !important;
-margin-bottom: inherit !important;
-padding: inherit !important;
-padding-left: inherit !important;
-padding-right: inherit !important;
-padding-top: inherit !important;
-padding-bottom: inherit !important;
-font-size: inherit !important;
-font-weight: inherit !important;
-letter-spacing: inherit !important;
-line-height: inherit !important;
-color: inherit !important;}
-.dbIxxS .product-description .elementor-8 p strong {
-font-weight: 600;
-}&lt;/style&gt;
-&lt;style id="wp-block-library-theme-inline-css" type="text/css"&gt;
-.wp-block-audio figcaption {
-  color: #555;
-  font-size: 13px;
-  text-align: center;
-}
-.is-dark-theme .wp-block-audio figcaption {
-  color: hsla(0, 0%, 100%, 0.65);
-}
-.wp-block-audio {
-  margin: 0 0 1em;
-}
-.wp-block-code {
-  border: 1px solid #ccc;
-  border-radius: 4px;
-  font-family: Menlo, Consolas, monaco, monospace;
-  padding: 0.8em 1em;
-}
-.wp-block-embed figcaption {
-  color: #555;
-  font-size: 13px;
-  text-align: center;
-}
-.is-dark-theme .wp-block-embed figcaption {
-  color: hsla(0, 0%, 100%, 0.65);
-}
-.wp-block-embed {
-  margin: 0 0 1em;
-}
-.blocks-gallery-caption {
-  color: #555;
-  font-size: 13px;
-  text-align: center;
-}
-.is-dark-theme .blocks-gallery-caption {
-  color: hsla(0, 0%, 100%, 0.65);
-}
-.wp-block-image figcaption {
-  color: #555;
-  font-size: 13px;
-  text-align: center;
-}
-.is-dark-theme .wp-block-image figcaption {
-  color: hsla(0, 0%, 100%, 0.65);
-}
-.wp-block-image {
-  margin: 0 0 1em;
-}
-.wp-block-pullquote {
-  border-bottom: 4px solid;
-  border-top: 4px solid;
-  color: currentColor;
-  margin-bottom: 1.75em;
-}
-.wp-block-pullquote cite,
-.wp-block-pullquote footer,
-.wp-block-pullquote__citation {
-  color: currentColor;
-  font-size: 0.8125em;
-  font-style: normal;
-  text-transform: uppercase;
-}
-.wp-block-quote {
-  border-left: 0.25em solid;
-  margin: 0 0 1.75em;
-  padding-left: 1em;
-}
-.wp-block-quote cite,
-.wp-block-quote footer {
-  color: currentColor;
-  font-size: 0.8125em;
-  font-style: normal;
-  position: relative;
-}
-.wp-block-quote.has-text-align-right {
-  border-left: none;
-  border-right: 0.25em solid;
-  padding-left: 0;
-  padding-right: 1em;
-}
-.wp-block-quote.has-text-align-center {
-  border: none;
-  padding-left: 0;
-}
-.wp-block-quote.is-large,
-.wp-block-quote.is-style-large,
-.wp-block-quote.is-style-plain {
-  border: none;
-}
-.wp-block-search .wp-block-search__label {
-  font-weight: 700;
-}
-.wp-block-search__button {
-  border: 1px solid #ccc;
-  padding: 0.375em 0.625em;
-}
-:where(.wp-block-group.has-background) {
-  padding: 1.25em 2.375em;
-}
-.wp-block-separator.has-css-opacity {
-  opacity: 0.4;
-}
-.wp-block-separator {
-  border: none;
-  border-bottom: 2px solid;
-  margin-left: auto;
-  margin-right: auto;
-}
-.wp-block-separator.has-alpha-channel-opacity {
-  opacity: 1;
-}
-.wp-block-separator:not(.is-style-wide):not(.is-style-dots) {
-  width: 100px;
-}
-.wp-block-separator.has-background:not(.is-style-dots) {
-  border-bottom: none;
-  height: 1px;
-}
-.wp-block-separator.has-background:not(.is-style-wide):not(.is-style-dots) {
-  height: 2px;
-}
-.wp-block-table {
-  margin: 0 0 1em;
-}
-.wp-block-table td,
-.wp-block-table th {
-  word-break: normal;
-}
-.wp-block-table figcaption {
-  color: #555;
-  font-size: 13px;
-  text-align: center;
-}
-.is-dark-theme .wp-block-table figcaption {
-  color: hsla(0, 0%, 100%, 0.65);
-}
-.wp-block-video figcaption {
-  color: #555;
-  font-size: 13px;
-  text-align: center;
-}
-.is-dark-theme .wp-block-video figcaption {
-  color: hsla(0, 0%, 100%, 0.65);
-}
-.wp-block-video {
-  margin: 0 0 1em;
-}
-.wp-block-template-part.has-background {
-  margin-bottom: 0;
-  margin-top: 0;
-  padding: 1.25em 2.375em;
-}&lt;/style&gt;
-&lt;style id="global-styles-inline-css" type="text/css"&gt;
-body {
-  --wp--preset--color--black: #000000;
-  --wp--preset--color--cyan-bluish-gray: #abb8c3;
-  --wp--preset--color--white: #ffffff;
-  --wp--preset--color--pale-pink: #f78da7;
-  --wp--preset--color--vivid-red: #cf2e2e;
-  --wp--preset--color--luminous-vivid-orange: #ff6900;
-  --wp--preset--color--luminous-vivid-amber: #fcb900;
-  --wp--preset--color--light-green-cyan: #7bdcb5;
-  --wp--preset--color--vivid-green-cyan: #00d084;
-  --wp--preset--color--pale-cyan-blue: #8ed1fc;
-  --wp--preset--color--vivid-cyan-blue: #0693e3;
-  --wp--preset--color--vivid-purple: #9b51e0;
-  --wp--preset--gradient--vivid-cyan-blue-to-vivid-purple: linear-gradient(
-    135deg,
-    rgba(6, 147, 227, 1) 0%,
-    rgb(155, 81, 224) 100%
-  );
-  --wp--preset--gradient--light-green-cyan-to-vivid-green-cyan: linear-gradient(
-    135deg,
-    rgb(122, 220, 180) 0%,
-    rgb(0, 208, 130) 100%
-  );
-  --wp--preset--gradient--luminous-vivid-amber-to-luminous-vivid-orange: linear-gradient(
-    135deg,
-    rgba(252, 185, 0, 1) 0%,
-    rgba(255, 105, 0, 1) 100%
-  );
-  --wp--preset--gradient--luminous-vivid-orange-to-vivid-red: linear-gradient(
-    135deg,
-    rgba(255, 105, 0, 1) 0%,
-    rgb(207, 46, 46) 100%
-  );
-  --wp--preset--gradient--very-light-gray-to-cyan-bluish-gray: linear-gradient(
-    135deg,
-    rgb(238, 238, 238) 0%,
-    rgb(169, 184, 195) 100%
-  );
-  --wp--preset--gradient--cool-to-warm-spectrum: linear-gradient(
-    135deg,
-    rgb(74, 234, 220) 0%,
-    rgb(151, 120, 209) 20%,
-    rgb(207, 42, 186) 40%,
-    rgb(238, 44, 130) 60%,
-    rgb(251, 105, 98) 80%,
-    rgb(254, 248, 76) 100%
-  );
-  --wp--preset--gradient--blush-light-purple: linear-gradient(
-    135deg,
-    rgb(255, 206, 236) 0%,
-    rgb(152, 150, 240) 100%
-  );
-  --wp--preset--gradient--blush-bordeaux: linear-gradient(
-    135deg,
-    rgb(254, 205, 165) 0%,
-    rgb(254, 45, 45) 50%,
-    rgb(107, 0, 62) 100%
-  );
-  --wp--preset--gradient--luminous-dusk: linear-gradient(
-    135deg,
-    rgb(255, 203, 112) 0%,
-    rgb(199, 81, 192) 50%,
-    rgb(65, 88, 208) 100%
-  );
-  --wp--preset--gradient--pale-ocean: linear-gradient(
-    135deg,
-    rgb(255, 245, 203) 0%,
-    rgb(182, 227, 212) 50%,
-    rgb(51, 167, 181) 100%
-  );
-  --wp--preset--gradient--electric-grass: linear-gradient(
-    135deg,
-    rgb(202, 248, 128) 0%,
-    rgb(113, 206, 126) 100%
-  );
-  --wp--preset--gradient--midnight: linear-gradient(
-    135deg,
-    rgb(2, 3, 129) 0%,
-    rgb(40, 116, 252) 100%
-  );
-  --wp--preset--duotone--dark-grayscale: url("#wp-duotone-dark-grayscale");
-  --wp--preset--duotone--grayscale: url("#wp-duotone-grayscale");
-  --wp--preset--duotone--purple-yellow: url("#wp-duotone-purple-yellow");
-  --wp--preset--duotone--blue-red: url("#wp-duotone-blue-red");
-  --wp--preset--duotone--midnight: url("#wp-duotone-midnight");
-  --wp--preset--duotone--magenta-yellow: url("#wp-duotone-magenta-yellow");
-  --wp--preset--duotone--purple-green: url("#wp-duotone-purple-green");
-  --wp--preset--duotone--blue-orange: url("#wp-duotone-blue-orange");
-  --wp--preset--font-size--small: 13px;
-  --wp--preset--font-size--medium: 20px;
-  --wp--preset--font-size--large: 36px;
-  --wp--preset--font-size--x-large: 42px;
-  --wp--preset--spacing--20: 0.44rem;
-  --wp--preset--spacing--30: 0.67rem;
-  --wp--preset--spacing--40: 1rem;
-  --wp--preset--spacing--50: 1.5rem;
-  --wp--preset--spacing--60: 2.25rem;
-  --wp--preset--spacing--70: 3.38rem;
-  --wp--preset--spacing--80: 5.06rem;
-  --wp--preset--shadow--natural: 6px 6px 9px rgba(0, 0, 0, 0.2);
-  --wp--preset--shadow--deep: 12px 12px 50px rgba(0, 0, 0, 0.4);
-  --wp--preset--shadow--sharp: 6px 6px 0px rgba(0, 0, 0, 0.2);
-  --wp--preset--shadow--outlined: 6px 6px 0px -3px rgba(255, 255, 255, 1),
-    6px 6px rgba(0, 0, 0, 1);
-  --wp--preset--shadow--crisp: 6px 6px 0px rgba(0, 0, 0, 1);
-}
-:where(.is-layout-flex) {
-  gap: 0.5em;
-}
-body .is-layout-flow &gt; .alignleft {
-  float: left;
-  margin-inline-start: 0;
-  margin-inline-end: 2em;
-}
-body .is-layout-flow &gt; .alignright {
-  float: right;
-  margin-inline-start: 2em;
-  margin-inline-end: 0;
-}
-body .is-layout-flow &gt; .aligncenter {
-  margin-left: auto !important;
-  margin-right: auto !important;
-}
-body .is-layout-constrained &gt; .alignleft {
-  float: left;
-  margin-inline-start: 0;
-  margin-inline-end: 2em;
-}
-body .is-layout-constrained &gt; .alignright {
-  float: right;
-  margin-inline-start: 2em;
-  margin-inline-end: 0;
-}
-body .is-layout-constrained &gt; .aligncenter {
-  margin-left: auto !important;
-  margin-right: auto !important;
-}
-body
-  .is-layout-constrained
-  &gt; :where(:not(.alignleft):not(.alignright):not(.alignfull)) {
-  max-width: var(--wp--style--global--content-size);
-  margin-left: auto !important;
-  margin-right: auto !important;
-}
-body .is-layout-constrained &gt; .alignwide {
-  max-width: var(--wp--style--global--wide-size);
-}
-body .is-layout-flex {
-  display: flex;
-}
-body .is-layout-flex {
-  flex-wrap: wrap;
-  align-items: center;
-}
-body .is-layout-flex &gt; * {
-  margin: 0;
-}
-:where(.wp-block-columns.is-layout-flex) {
-  gap: 2em;
-}
-.has-black-color {
-  color: var(--wp--preset--color--black) !important;
-}
-.has-cyan-bluish-gray-color {
-  color: var(--wp--preset--color--cyan-bluish-gray) !important;
-}
-.has-white-color {
-  color: var(--wp--preset--color--white) !important;
-}
-.has-pale-pink-color {
-  color: var(--wp--preset--color--pale-pink) !important;
-}
-.has-vivid-red-color {
-  color: var(--wp--preset--color--vivid-red) !important;
-}
-.has-luminous-vivid-orange-color {
-  color: var(--wp--preset--color--luminous-vivid-orange) !important;
-}
-.has-luminous-vivid-amber-color {
-  color: var(--wp--preset--color--luminous-vivid-amber) !important;
-}
-.has-light-green-cyan-color {
-  color: var(--wp--preset--color--light-green-cyan) !important;
-}
-.has-vivid-green-cyan-color {
-  color: var(--wp--preset--color--vivid-green-cyan) !important;
-}
-.has-pale-cyan-blue-color {
-  color: var(--wp--preset--color--pale-cyan-blue) !important;
-}
-.has-vivid-cyan-blue-color {
-  color: var(--wp--preset--color--vivid-cyan-blue) !important;
-}
-.has-vivid-purple-color {
-  color: var(--wp--preset--color--vivid-purple) !important;
-}
-.has-black-background-color {
-  background-color: var(--wp--preset--color--black) !important;
-}
-.has-cyan-bluish-gray-background-color {
-  background-color: var(--wp--preset--color--cyan-bluish-gray) !important;
-}
-.has-white-background-color {
-  background-color: var(--wp--preset--color--white) !important;
-}
-.has-pale-pink-background-color {
-  background-color: var(--wp--preset--color--pale-pink) !important;
-}
-.has-vivid-red-background-color {
-  background-color: var(--wp--preset--color--vivid-red) !important;
-}
-.has-luminous-vivid-orange-background-color {
-  background-color: var(--wp--preset--color--luminous-vivid-orange) !important;
-}
-.has-luminous-vivid-amber-background-color {
-  background-color: var(--wp--preset--color--luminous-vivid-amber) !important;
-}
-.has-light-green-cyan-background-color {
-  background-color: var(--wp--preset--color--light-green-cyan) !important;
-}
-.has-vivid-green-cyan-background-color {
-  background-color: var(--wp--preset--color--vivid-green-cyan) !important;
-}
-.has-pale-cyan-blue-background-color {
-  background-color: var(--wp--preset--color--pale-cyan-blue) !important;
-}
-.has-vivid-cyan-blue-background-color {
-  background-color: var(--wp--preset--color--vivid-cyan-blue) !important;
-}
-.has-vivid-purple-background-color {
-  background-color: var(--wp--preset--color--vivid-purple) !important;
-}
-.has-black-border-color {
-  border-color: var(--wp--preset--color--black) !important;
-}
-.has-cyan-bluish-gray-border-color {
-  border-color: var(--wp--preset--color--cyan-bluish-gray) !important;
-}
-.has-white-border-color {
-  border-color: var(--wp--preset--color--white) !important;
-}
-.has-pale-pink-border-color {
-  border-color: var(--wp--preset--color--pale-pink) !important;
-}
-.has-vivid-red-border-color {
-  border-color: var(--wp--preset--color--vivid-red) !important;
-}
-.has-luminous-vivid-orange-border-color {
-  border-color: var(--wp--preset--color--luminous-vivid-orange) !important;
-}
-.has-luminous-vivid-amber-border-color {
-  border-color: var(--wp--preset--color--luminous-vivid-amber) !important;
-}
-.has-light-green-cyan-border-color {
-  border-color: var(--wp--preset--color--light-green-cyan) !important;
-}
-.has-vivid-green-cyan-border-color {
-  border-color: var(--wp--preset--color--vivid-green-cyan) !important;
-}
-.has-pale-cyan-blue-border-color {
-  border-color: var(--wp--preset--color--pale-cyan-blue) !important;
-}
-.has-vivid-cyan-blue-border-color {
-  border-color: var(--wp--preset--color--vivid-cyan-blue) !important;
-}
-.has-vivid-purple-border-color {
-  border-color: var(--wp--preset--color--vivid-purple) !important;
-}
-.has-vivid-cyan-blue-to-vivid-purple-gradient-background {
-  background: var(
-    --wp--preset--gradient--vivid-cyan-blue-to-vivid-purple
-  ) !important;
-}
-.has-light-green-cyan-to-vivid-green-cyan-gradient-background {
-  background: var(
-    --wp--preset--gradient--light-green-cyan-to-vivid-green-cyan
-  ) !important;
-}
-.has-luminous-vivid-amber-to-luminous-vivid-orange-gradient-background {
-  background: var(
-    --wp--preset--gradient--luminous-vivid-amber-to-luminous-vivid-orange
-  ) !important;
-}
-.has-luminous-vivid-orange-to-vivid-red-gradient-background {
-  background: var(
-    --wp--preset--gradient--luminous-vivid-orange-to-vivid-red
-  ) !important;
-}
-.has-very-light-gray-to-cyan-bluish-gray-gradient-background {
-  background: var(
-    --wp--preset--gradient--very-light-gray-to-cyan-bluish-gray
-  ) !important;
-}
-.has-cool-to-warm-spectrum-gradient-background {
-  background: var(--wp--preset--gradient--cool-to-warm-spectrum) !important;
-}
-.has-blush-light-purple-gradient-background {
-  background: var(--wp--preset--gradient--blush-light-purple) !important;
-}
-.has-blush-bordeaux-gradient-background {
-  background: var(--wp--preset--gradient--blush-bordeaux) !important;
-}
-.has-luminous-dusk-gradient-background {
-  background: var(--wp--preset--gradient--luminous-dusk) !important;
-}
-.has-pale-ocean-gradient-background {
-  background: var(--wp--preset--gradient--pale-ocean) !important;
-}
-.has-electric-grass-gradient-background {
-  background: var(--wp--preset--gradient--electric-grass) !important;
-}
-.has-midnight-gradient-background {
-  background: var(--wp--preset--gradient--midnight) !important;
-}
-.has-small-font-size {
-  font-size: var(--wp--preset--font-size--small) !important;
-}
-.has-medium-font-size {
-  font-size: var(--wp--preset--font-size--medium) !important;
-}
-.has-large-font-size {
-  font-size: var(--wp--preset--font-size--large) !important;
-}
-.has-x-large-font-size {
-  font-size: var(--wp--preset--font-size--x-large) !important;
-}
-.wp-block-navigation a:where(:not(.wp-element-button)) {
-  color: inherit;
-}
-:where(.wp-block-columns.is-layout-flex) {
-  gap: 2em;
-}
-.wp-block-pullquote {
-  font-size: 1.5em;
-  line-height: 1.6;
-}&lt;/style&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/plugins/elementor/assets/css/frontend-legacy.min.css?ver=3.13.1" id="elementor-frontend-legacy-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/plugins/elementor/assets/css/frontend.min.css?ver=3.13.1" id="elementor-frontend-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/elementor/css/post-29.css?ver=1683709347" id="elementor-post-29-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/elementor/css/post-33.css?ver=1683709347" id="elementor-post-33-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/themes/oceanwp/assets/fonts/fontawesome/css/all.min.css?ver=5.15.1" id="font-awesome-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/themes/oceanwp/assets/css/third/simple-line-icons.min.css?ver=2.4.0" id="simple-line-icons-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/themes/oceanwp/assets/css/style.min.css?ver=3.4.3" id="oceanwp-style-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/plugins/elementor/assets/lib/eicons/css/elementor-icons.min.css?ver=5.20.0" id="elementor-icons-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/plugins/elementor/assets/lib/swiper/css/swiper.min.css?ver=5.3.6" id="swiper-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/elementor/css/post-12.css?ver=1683709347" id="elementor-post-12-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/plugins/elementor-pro/assets/css/frontend.min.css?ver=3.13.0" id="elementor-pro-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/elementor/css/global.css?ver=1683709347" id="elementor-global-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/elementor/css/post-8.css?ver=1683715001" id="elementor-post-8-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://fonts.googleapis.com/css?family=Roboto%3A100%2C100italic%2C200%2C200italic%2C300%2C300italic%2C400%2C400italic%2C500%2C500italic%2C600%2C600italic%2C700%2C700italic%2C800%2C800italic%2C900%2C900italic%7CRoboto+Slab%3A100%2C100italic%2C200%2C200italic%2C300%2C300italic%2C400%2C400italic%2C500%2C500italic%2C600%2C600italic%2C700%2C700italic%2C800%2C800italic%2C900%2C900italic%7CMontserrat%3A100%2C100italic%2C200%2C200italic%2C300%2C300italic%2C400%2C400italic%2C500%2C500italic%2C600%2C600italic%2C700%2C700italic%2C800%2C800italic%2C900%2C900italic&amp;amp;display=auto&amp;amp;subset=latin-ext&amp;amp;ver=6.2" id="google-fonts-1-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/plugins/elementor/assets/lib/font-awesome/css/fontawesome.min.css?ver=5.15.3" id="elementor-icons-shared-0-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/plugins/elementor/assets/lib/font-awesome/css/solid.min.css?ver=5.15.3" id="elementor-icons-fa-solid-css" media="all" rel="stylesheet"&gt;
-&lt;link href="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/plugins/elementor/assets/lib/font-awesome/css/brands.min.css?ver=5.15.3" id="elementor-icons-fa-brands-css" media="all" rel="stylesheet"&gt;
-&lt;div class="elementor elementor-8" data-elementor-id="8" data-elementor-type="wp-page"&gt;
-	&lt;div class="elementor-inner"&gt;
-		&lt;div class="elementor-section-wrap"&gt;
-			&lt;div class="elementor-element elementor-element-4ab431d e-con-full e-flex e-con" data-element_type="container" data-id="4ab431d" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-				&lt;div class="elementor-element elementor-element-3b4d738 e-con-full e-flex e-con" data-element_type="container" data-id="3b4d738" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-					&lt;div class="elementor-element elementor-element-d768a27 e-con-full e-flex e-con" data-element_type="container" data-id="d768a27" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-						&lt;div class="elementor-element elementor-element-6571b389 animated-slow elementor-widget elementor-widget-image" data-element_type="widget" data-id="6571b389" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;none&amp;quot;,&amp;quot;_animation_mobile&amp;quot;:
-&amp;quot;none&amp;quot;}" data-widget_type="image.default"&gt;
-							&lt;div class="elementor-widget-container"&gt;
-								&lt;div class="elementor-image"&gt;
-									&lt;img alt="" class="attachment-full size-full wp-image-178 lazyload" decoding="async" height="50" width="217" data-src="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/acer.png"&gt;&lt;/div&gt;
-							&lt;/div&gt;
-						&lt;/div&gt;
-					&lt;/div&gt;
-					&lt;div class="elementor-element elementor-element-4c867064 e-con-full e-flex e-con" data-element_type="container" data-id="4c867064" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-						&lt;div class="elementor-element elementor-element-49d06c51 animated-slow elementor-widget elementor-widget-image" data-element_type="widget" data-id="49d06c51" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;none&amp;quot;,&amp;quot;_animation_mobile&amp;quot;:
-&amp;quot;none&amp;quot;}" data-widget_type="image.default"&gt;
-							&lt;div class="elementor-widget-container"&gt;
-								&lt;div class="elementor-image"&gt;
-									&lt;img alt="" class="attachment-full size-full wp-image-179 lazyload" decoding="async" height="34" width="179" data-src="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/logo_chromebook_rgb.png"&gt;&lt;/div&gt;
-							&lt;/div&gt;
-						&lt;/div&gt;
-					&lt;/div&gt;
-				&lt;/div&gt;
-				&lt;div class="elementor-element elementor-element-7b4824f e-con-full e-flex e-con" data-element_type="container" data-id="7b4824f" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-					&lt;div class="elementor-element elementor-element-51bdbe8 e-con-boxed e-flex e-con" data-element_type="container" data-id="51bdbe8" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;boxed&amp;quot;}"&gt;
-						&lt;div class="e-con-inner"&gt;
-							&lt;div class="elementor-element elementor-element-8165bbe elementor-widget elementor-widget-heading" data-element_type="widget" data-id="8165bbe" data-widget_type="heading.default"&gt;
-								&lt;div class="elementor-widget-container"&gt;
-									&lt;h2 class="elementor-heading-title elementor-size-default"&gt;
-										&lt;span style="color:#7ac142"&gt;Acer Chromebook 315&lt;/span&gt;&lt;br&gt;
-										Mniej zmartwień&lt;br&gt;
-										- więcej możliwości&lt;/h2&gt;
-								&lt;/div&gt;
-							&lt;/div&gt;
-							&lt;div class="elementor-element elementor-element-39a7b6d6 animated-slow elementor-invisible elementor-widget elementor-widget-heading" data-element_type="widget" data-id="39a7b6d6" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;fadeIn&amp;quot;}" data-widget_type="heading.default"&gt;
-								&lt;div class="elementor-widget-container"&gt;
-									&lt;span class="elementor-heading-title elementor-size-default"&gt;Chromebook to znak towarowy Google LLC.&lt;/span&gt;&lt;/div&gt;
-							&lt;/div&gt;
-						&lt;/div&gt;
-					&lt;/div&gt;
-					&lt;div class="elementor-element elementor-element-f96e613 e-con-boxed e-flex e-con" data-element_type="container" data-id="f96e613" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;boxed&amp;quot;}"&gt;
-						&lt;div class="e-con-inner"&gt;
-							&lt;div class="elementor-element elementor-element-60ecccd2 animated-slow elementor-widget elementor-widget-image" data-element_type="widget" data-id="60ecccd2" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;none&amp;quot;,&amp;quot;_animation_tablet&amp;quot;:
-&amp;quot;fadeIn&amp;quot;,&amp;quot;_animation_mobile&amp;quot;:
-&amp;quot;none&amp;quot;}" data-widget_type="image.default"&gt;
-								&lt;div class="elementor-widget-container"&gt;
-									&lt;div class="elementor-image"&gt;
-										&lt;img alt="" class="attachment-full size-full wp-image-181 lazyload" decoding="async" height="933" sizes="(max-width: 1448px) 100vw, 1448px" srcset="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/Grupa-2-min.png 1448w, https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/Grupa-2-min-300x193.png 300w, https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/Grupa-2-min-1024x660.png 1024w, https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/Grupa-2-min-768x495.png 768w" width="1448" data-src="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/Grupa-2-min.png"&gt;&lt;/div&gt;
-								&lt;/div&gt;
-							&lt;/div&gt;
-						&lt;/div&gt;
-					&lt;/div&gt;
-				&lt;/div&gt;
-			&lt;/div&gt;
-			&lt;div class="elementor-element elementor-element-f411f34 e-con-full e-flex e-con" data-element_type="container" data-id="f411f34" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-				&lt;div class="video-container" style="position:relative;padding-bottom:56.25%; background: none; margin: 30px 0 40px 0;height:0;overflow:hidden;border-radius: 30px"&gt;
-					&lt;div class="embed-responsive embed-responsive-16by9"&gt;
-						&lt;iframe class="embed-responsive-item lazyload" style="position:absolute;top:0;left:0;width:100%;height:100%;border:none;" data-src="https://www.youtube-nocookie.com/embed/LA18ozv5FpU?rel=0&amp;amp;showinfo=0&amp;amp;controls=0"&gt;&lt;/iframe&gt;&lt;/div&gt;
-				&lt;/div&gt;
-				&lt;div class="elementor-element elementor-element-542b06cb e-con-full e-flex e-con" data-element_type="container" data-id="542b06cb" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-					&lt;div class="elementor-element elementor-element-4741a060 e-con-full e-flex e-con" data-element_type="container" data-id="4741a060" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-						&lt;div class="elementor-element elementor-element-4ee4605b animated-slow elementor-widget elementor-widget-heading" data-element_type="widget" data-id="4ee4605b" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;none&amp;quot;}" data-widget_type="heading.default" id="wiecej"&gt;
-							&lt;div class="elementor-widget-container"&gt;
-								&lt;h2 class="elementor-heading-title elementor-size-default"&gt;
-									Acer Chromebook 315 to wyjątkowy laptop, kt&amp;oacute;ry łączy&lt;br&gt;
-									w sobie trzy niezwykle ważne cechy: &lt;span style="color:#7ac142"&gt;szybkość, łatwość obsługi&lt;br&gt;
-									oraz bezpieczeństwo&lt;/span&gt;.&lt;/h2&gt;
-							&lt;/div&gt;
-						&lt;/div&gt;
-					&lt;/div&gt;
-					&lt;div class="elementor-element elementor-element-13519a4d e-con-full e-flex e-con" data-element_type="container" data-id="13519a4d" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-						&lt;div class="elementor-element elementor-element-1ec7c796 e-con-full e-flex e-con" data-element_type="container" data-id="1ec7c796" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-							&lt;div class="elementor-element elementor-element-6014675 e-con-full animated-slow e-flex e-con" data-element_type="container" data-id="6014675" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;,&amp;quot;animation&amp;quot;:
-&amp;quot;none&amp;quot;,&amp;quot;animation_mobile&amp;quot;:
-&amp;quot;fadeIn&amp;quot;}"&gt;
-								&lt;div class="elementor-element elementor-element-33c63b07 e-con-full e-flex e-con" data-element_type="container" data-id="33c63b07" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-									&lt;div class="elementor-element elementor-element-11505c51 animated-slow elementor-widget elementor-widget-image" data-element_type="widget" data-id="11505c51" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;none&amp;quot;}" data-widget_type="image.default"&gt;
-										&lt;div class="elementor-widget-container"&gt;
-											&lt;div class="elementor-image"&gt;
-												&lt;img alt="" class="attachment-full size-full wp-image-189 lazyload" decoding="async" height="94" width="120" data-src="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/Inteligentny-obiekt-wektorowy2.png"&gt;&lt;/div&gt;
-										&lt;/div&gt;
-									&lt;/div&gt;
-								&lt;/div&gt;
-								&lt;div class="elementor-element elementor-element-56708cfc e-con-full e-flex e-con" data-element_type="container" data-id="56708cfc" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-									&lt;div class="elementor-element elementor-element-4eb49ebe animated-slow elementor-widget elementor-widget-text-editor" data-element_type="widget" data-id="4eb49ebe" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;none&amp;quot;}" data-widget_type="text-editor.default"&gt;
-										&lt;div class="elementor-widget-container"&gt;
-											&lt;div class="elementor-text-editor elementor-clearfix"&gt;
-												&lt;p&gt;
-													W por&amp;oacute;wnaniu z tradycyjnymi laptopami, kt&amp;oacute;re często wymagają długiego czasu uruchomienia i zapewnienia odpowiedniej wydajności, ten model zapewnia &lt;strong&gt;natychmiastową reakcję&lt;/strong&gt; i płynną pracę.&lt;/p&gt;
-											&lt;/div&gt;
-										&lt;/div&gt;
-									&lt;/div&gt;
-								&lt;/div&gt;
-							&lt;/div&gt;
-							&lt;div class="elementor-element elementor-element-3f7139b4 e-con-full animated-slow e-flex e-con" data-element_type="container" data-id="3f7139b4" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;,&amp;quot;animation&amp;quot;:
-&amp;quot;none&amp;quot;,&amp;quot;animation_mobile&amp;quot;:
-&amp;quot;fadeIn&amp;quot;}"&gt;
-								&lt;div class="elementor-element elementor-element-646c33cc e-con-full e-flex e-con" data-element_type="container" data-id="646c33cc" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-									&lt;div class="elementor-element elementor-element-24b7d327 animated-slow elementor-widget elementor-widget-image" data-element_type="widget" data-id="24b7d327" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;none&amp;quot;}" data-widget_type="image.default"&gt;
-										&lt;div class="elementor-widget-container"&gt;
-											&lt;div class="elementor-image"&gt;
-												&lt;img alt="" class="attachment-large size-large wp-image-190 lazyload" decoding="async" height="90" width="101" data-src="https://allegro.stati.pl/!ALLEGRO_IMG/PRODUCENCI/ACER/Chromebook/wp-content/uploads/2023/05/Inteligentny-obiekt-wektorowy1.png"&gt;&lt;/div&gt;
-										&lt;/div&gt;
-									&lt;/div&gt;
-								&lt;/div&gt;
-								&lt;div class="elementor-element elementor-element-4ee688a e-con-full e-flex e-con" data-element_type="container" data-id="4ee688a" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-									&lt;div class="elementor-element elementor-element-7ad83edb animated-slow elementor-widget elementor-widget-text-editor" data-element_type="widget" data-id="7ad83edb" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot;none&amp;quot;}" data-widget_type="text-editor.default"&gt;
-										&lt;div class="elementor-widget-container"&gt;
-											&lt;div class="elementor-text-editor elementor-clearfix"&gt;
-												&lt;p&gt;
-													Dzięki wykorzystaniu &lt;strong&gt;systemu operacyjnego ChromeOS&lt;/strong&gt;, kt&amp;oacute;ry jest przejrzysty i intuicyjny, użytkownicy nie muszą się obawiać skomplikowanych instrukcji czy konieczności instalowania oprogramowania. Wszystko jest dostępne w chmurze i gotowe do użytku w zaledwie &lt;strong&gt;kilka minut&lt;/strong&gt;.&lt;/p&gt;
-											&lt;/div&gt;
-										&lt;/div&gt;
-									&lt;/div&gt;
-								&lt;/div&gt;
-							&lt;/div&gt;
-							&lt;div class="elementor-element elementor-element-a1993a1 e-con-full e-flex e-con" data-element_type="container" data-id="a1993a1" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;,&amp;quot;animation&amp;quot;:
-&amp;quot;none&amp;quot;,&amp;quot;animation_mobile&amp;quot;:
-&amp;quot;fadeIn&amp;quot;}"&gt;
-								&lt;div class="elementor-element elementor-element-15023c06 e-con-full e-flex e-con" data-element_type="container" data-id="15023c06" data-settings="{&amp;quot;content_width&amp;quot;:
-&amp;quot;full&amp;quot;}"&gt;
-									&lt;div class="elementor-element elementor-element-590c10aa animated-slow elementor-widget elementor-widget-image" data-element_type="widget" data-id="590c10aa" data-settings="{&amp;quot;_animation&amp;quot;:
-&amp;quot</t>
   </si>
   <si>
     <t>Inspiron 3530 i5-1334U/16GB/1TB/Win11 120Hz Srebrny</t>
@@ -7617,130 +6861,6 @@
 Laptop oferuje szybkie połączenia dzięki Wi-Fi 6E oraz Bluetooth 5.3. Zintegrowana karta graficzna Intel UHD oraz wbudowane głośniki stereo zapewniają doskonałe wrażenia multimedialne. Wysoka jakość kamery HD sprawia, że wideokonferencje stają się przyjemnością.</t>
   </si>
   <si>
-    <t>ThinkBook 16 G6 IRL i5-13420H/16GB/512/Win11P</t>
-  </si>
-  <si>
-    <t>Procesor: Intel® Core™ i5-13420H (8 rdzeń, 12 wątków, 3.40-4.60 GHz, 12MB cache)
-Pamięć RAM: 16 GB (DDR5, 5600 MHz)
-Maksymalna obsługiwana ilość pamięci RAM: 64 GB
-Liczba gniazd pamięci (ogółem / wolne): 2/1
-Dysk SSD M.2 PCIe: 512 GB
-Opcje dołożenia dysków: Możliwość montażu dysku M.2 PCIe (elementy montażowe w zestawie)
-Dotykowy ekran: Nie
-Typ ekranu: Matowy, LED, IPS
-Przekątna ekranu: 16"
-Rozdzielczość ekranu: 1920 x 1200 (WUXGA)
-Jasność matrycy: 300 cd/m²
-Karta graficzna: Intel UHD Graphics
-Pamięć karty graficznej: Pamięć współdzielona
-Dźwięk: Wbudowane głośniki stereo, Wbudowane dwa mikrofony
-Kamera internetowa: Kamera na podczerwień, Full HD
-Łączność: LAN 1 Gb/s, Wi-Fi 6, Moduł Bluetooth 5.2
-Złącza: USB 3.2 Gen. 1 - 2 szt., USB Typu-C (z DisplayPort i Power Delivery) - 1 szt., USB4 Typu-C (z Thunderbolt™ 4) - 1 szt., HDMI 2.1 - 1 szt., Czytnik kart pamięci SD - 1 szt., RJ-45 (LAN) - 1 szt., Wyjście słuchawkowe/wejście mikrofonowe - 1 szt.
-Typ baterii: Litowo-jonowa
-Pojemność baterii: 4-komorowa, 4625 mAh
-Kolor dominujący: Szary
-Czytnik linii papilarnych: Tak
-Podświetlana klawiatura: Tak
-Kolor podświetlenia klawiatury: Biały
-Zabezpieczenia: Możliwość zabezpieczenia linką (port Kensington NanoSaver), Szyfrowanie TPM, Windows Hello, Kamera z wbudowaną zaślepką
-Obudowa i wykonanie: Standard militarny MIL-STD-810H
-System operacyjny: Microsoft Windows 11 Pro
-Dołączone oprogramowanie: Partycja recovery (opcja przywrócenia systemu z dysku)
-Zasilacz: 100 W
-Dodatkowe informacje: Wydzielona klawiatura numeryczna, Wielodotykowy, intuicyjny touchpad
-Wysokość: 17,5 mm
-Szerokość: 356 mm
-Głębokość: 254 mm
-Waga: 1,70 kg
-Dołączone akcesoria: Zasilacz
-Układ klawiatury: QWERTY
-Rodzaj gwarancji: Standardowa
-Gwarancja: 36 miesięcy (gwarancja producenta)</t>
-  </si>
-  <si>
-    <t>&lt;div class="content"&gt;&lt;link href="https://fonts.googleapis.com/css2?family=Instrument+Sans:ital,wght@0,400..700;1,400..700&amp;amp;display=swap" rel="stylesheet"&gt;
-&lt;link href="https://ftp.stati.pl/KP/styles_1.css?v=1.3" rel="stylesheet"&gt;
-&lt;div id="new_content_desc" style="margin-bottom: 30px;"&gt;
-	&lt;!-- HEADER_INTRO --&gt;
-	&lt;div class="desc_section head_desc"&gt;
-		&lt;h2&gt;
-			Lenovo ThinkBook 16 G6 IRL&lt;/h2&gt;
-		&lt;p&gt;
-			Lenovo ThinkBook 16 G6 to laptop, kt&amp;oacute;ry łączy wydajność i funkcjonalność, zapewniając wygodę użytkowania w każdej sytuacji. Z procesorem Intel Core 13. generacji masz pewność, że urządzenie sprosta nawet najbardziej wymagającym zadaniom. Duży ekran IPS WUXGA gwarantuje doskonałą jakość obrazu, idealną zar&amp;oacute;wno do pracy, jak i rozrywki. To nowoczesne narzędzie stworzone z myślą o tych, kt&amp;oacute;rzy oczekują najlepszych parametr&amp;oacute;w.&lt;/p&gt;
-	&lt;/div&gt;
-	&lt;!-- HEADER_INTRO_END --&gt;&lt;!-- HEADER_IMAGE --&gt;
-	&lt;div class="desc_section img_head"&gt;
-		&lt;img alt="Lenovo ThinkBook 16 G6 IRL wygląd laptopa" class="header_desktop lazyloaded lazyload" data-src="https://allegro.stati.pl/AllegroIMG/PRODUCENCI/LENOVO/ThinkBook-16-G6-IRL/Lenovo-ThinkBook-16-G6-IRL-wyglad.jpg"&gt; &lt;img alt="Lenovo ThinkBook 16 G6 IRL wygląd laptopa" class="header_mobile lazyloaded lazyload" data-src="https://allegro.stati.pl/AllegroIMG/PRODUCENCI/LENOVO/ThinkBook-16-G6-IRL/Lenovo-ThinkBook-16-G6-IRL-wyglad1.jpg"&gt;&lt;/div&gt;
-	&lt;!-- HEADER_IMAGE_END --&gt;&lt;!-- ICONS --&gt;
-	&lt;div class="desc_section emo_keys"&gt;
-		&lt;h2&gt;
-			Lenovo ThinkBook 16 G6 &amp;ndash; niezawodność i nowoczesność w jednym&lt;/h2&gt;
-		&lt;div class="keys_emo"&gt;
-			&lt;div class="emo_text"&gt;
-				&lt;span class="emoji"&gt;&lt;img alt="ikona ekranrozmiar" class="lazyload" data-src="https://satysfakcja.stati.pl/icons_all/ekranrozmiar.svg"&gt;&lt;/span&gt;
-				&lt;h3&gt;
-					Perfekcyjna jakość obrazu i wygoda pracy&lt;/h3&gt;
-				&lt;p&gt;
-					Ekran IPS o wysokiej rozdzielczości WUXGA oferuje żywe kolory oraz szerokie kąty widzenia, co sprawia, że każde zadanie staje się łatwiejsze. Zar&amp;oacute;wno podczas edycji dokument&amp;oacute;w, oglądania film&amp;oacute;w, jak i przeglądania stron internetowych, obraz będzie wyraźny i pełen szczeg&amp;oacute;ł&amp;oacute;w. Duży ekran to r&amp;oacute;wnież większa przestrzeń robocza, kt&amp;oacute;ra ułatwi organizację pracy i poprawi efektywność.&lt;/p&gt;
-			&lt;/div&gt;
-			&lt;div class="emo_text"&gt;
-				&lt;span class="emoji"&gt;&lt;img alt="ikona bezpieczenstwo" class="lazyload" data-src="https://satysfakcja.stati.pl/icons_all/bezpieczenstwo.svg"&gt;&lt;/span&gt;
-				&lt;h3&gt;
-					Zaawansowane rozwiązania zwiększające bezpieczeństwo&lt;/h3&gt;
-				&lt;p&gt;
-					Laptop został wyposażony w kamerę Full HD z technologią podczerwieni, kt&amp;oacute;ra obsługuje logowanie za pomocą rozpoznawania twarzy. Dzięki wbudowanej zaślepce na kamerę, prywatność jest zawsze na pierwszym miejscu &amp;ndash; wystarczy ją przesunąć, aby mieć pewność, że nikt Cię nie obserwuje. To proste, a jednocześnie skuteczne rozwiązanie.&lt;/p&gt;
-			&lt;/div&gt;
-			&lt;div class="emo_text"&gt;
-				&lt;span class="emoji"&gt;&lt;img alt="ikona wydajnosc" class="lazyload" data-src="https://satysfakcja.stati.pl/icons_all/wydajnosc.svg"&gt;&lt;/span&gt;
-				&lt;h3&gt;
-					Wydajność na miarę nowoczesnych wymagań&lt;/h3&gt;
-				&lt;p&gt;
-					Intel Core 13. generacji gwarantuje nie tylko płynność działania, ale także szybką reakcję systemu na wielozadaniowość. Nawet przy intensywnym korzystaniu z aplikacji, laptop działa bez op&amp;oacute;źnień, co znacząco wpływa na komfort użytkowania. Procesor ten pozwala na sprawne zarządzanie zar&amp;oacute;wno codziennymi zadaniami, jak i bardziej zaawansowanymi projektami.&lt;/p&gt;
-			&lt;/div&gt;
-			&lt;div class="emo_text"&gt;
-				&lt;span class="emoji"&gt;&lt;img alt="ikona wytrzymalosc" class="lazyload" data-src="https://satysfakcja.stati.pl/icons_all/wytrzymalosc.svg"&gt;&lt;/span&gt;
-				&lt;h3&gt;
-					Solidność potwierdzona standardem wojskowym&lt;/h3&gt;
-				&lt;p&gt;
-					Lenovo ThinkBook 16 G6 spełnia rygorystyczne normy standardu militarnego MIL-STD-810H, co oznacza, że laptop jest odporny na trudne warunki użytkowania. Bez obaw można go używać w r&amp;oacute;żnych środowiskach &amp;ndash; urządzenie poradzi sobie z wstrząsami, pyłem, wilgocią oraz ekstremalnymi temperaturami. To gwarancja trwałości na lata.&lt;/p&gt;
-			&lt;/div&gt;
-			&lt;div class="emo_text"&gt;
-				&lt;span class="emoji"&gt;&lt;img alt="ikona podswietlanaklawiatura" class="lazyload" data-src="https://satysfakcja.stati.pl/icons_all/podswietlanaklawiatura.svg"&gt;&lt;/span&gt;
-				&lt;h3&gt;
-					Podświetlana klawiatura dla maksymalnej wygody&lt;/h3&gt;
-				&lt;p&gt;
-					Praca po zmroku nie będzie już problemem dzięki podświetlanej klawiaturze, kt&amp;oacute;ra pozwala na komfortowe pisanie w każdych warunkach oświetleniowych. Klawiatura jest ergonomicznie zaprojektowana, aby minimalizować zmęczenie podczas długiego korzystania z laptopa. Lenovo ThinkBook 16 G6 stawia na wygodę i funkcjonalność w każdym detalu.&lt;/p&gt;
-			&lt;/div&gt;
-		&lt;/div&gt;
-	&lt;/div&gt;
-	&lt;!-- ICONS_END --&gt;&lt;/div&gt;
-&lt;script type="text/javascript"&gt;
-function keyToggle(selector) {
-	var selectedElements = selector.children;
-	if(selectedElements[0].innerText === "+") {
-		selectedElements[0].innerText = " − ";
-	} else {
-		selectedElements[0].innerText = " + ";
-	}
-	selectedElements[1].classList.toggle("visible");
-	selectedElements[2].classList.toggle("visible");
-}
-function activeVideo(id) {
-	document.querySelector(".collapse_miniature.active").classList.remove("active");
-	document.getElementById(id).classList.add("active");
-	let newString = id.replace("video_menu_", "video_review_");
-	var activeText = document.querySelector(".video-container.active");
-	activeText.classList.remove("active");
-	var newActiveText = document.getElementById(newString);
-	newActiveText.classList.add("active");
-}
-function show360(overlay) {
-	overlay.style.display = "none";
-}
-&lt;/script&gt;&lt;/div&gt;</t>
-  </si>
-  <si>
     <t>Victus 15 i5-13420H/16GB/512/Win11 RTX4050 144Hz</t>
   </si>
   <si>
@@ -8186,9 +7306,6 @@
   </si>
   <si>
     <t>UltraGear 27GS75Q-B</t>
-  </si>
-  <si>
-    <t>Monitor</t>
   </si>
   <si>
     <t>Przeznaczenie produktu: Dla graczy
@@ -9810,9 +8927,6 @@
   </si>
   <si>
     <t>MX Anywhere 3S Grafit</t>
-  </si>
-  <si>
-    <t>Myszka</t>
   </si>
   <si>
     <t>Łączność: Bezprzewodowa
@@ -12230,9 +11344,6 @@
     <t>Galaxy Tab A9 X110 WiFi 8/128GB granatowy</t>
   </si>
   <si>
-    <t>Tablet</t>
-  </si>
-  <si>
     <t>Procesor: MediaTek MT8781V
 Pamięć RAM: 8 GB
 Pamięć wbudowana: 128 GB
@@ -13339,9 +12450,6 @@
     <t>WR3600 (3600Mb/s a/b/g/n/ac/ax/be)</t>
   </si>
   <si>
-    <t>Urządzenia sieciowe</t>
-  </si>
-  <si>
     <t>Tryb pracy: Router
 Rodzaj urządzenia: Router bezprzewodowy
 Rodzaje wejść/wyjść: RJ-45 10/100/1000 (LAN) - 4 szt., RJ-45 10/100/1000 (WAN) - 1 szt.
@@ -14058,9 +13166,6 @@
 A może chcesz utworzyć płynną sieć Wi-Fi, dostępną na całej powierzchni domu? Archer AX23 obsługuje technologię OneMesh, która zapobiega utratom połączenia z siecią i opóźnieniami w transmisji podczas przemieszczania się po domu.</t>
   </si>
   <si>
-    <t>Urządzenie sieciowe</t>
-  </si>
-  <si>
     <t>Archer AX53 (3000Mb/s a/b/g/n/ac/ax)</t>
   </si>
   <si>
@@ -14226,6 +13331,21 @@
 Cudy TR1200 oferuje obsługę sześciu popularnych protokołów VPN, gwarantując bezpieczne i poufne przesyłanie danych zarówno jako klient, jak i serwer VPN. Dzięki wbudowanym VPN WireGuard i OpenVPN możesz udostępniać swoją komercyjną sieć VPN wszystkim połączonym urządzeniom. Decyduj, które urządzenia mają korzystać z połączenia VPN, zapewniając maksymalne bezpieczeństwo lub optymalną wydajność. Funkcja ZeroTier umożliwia hosting serwera VPN nawet bez publicznego adresu IP, co jest idealne podczas podróży do hoteli czy kawiarni.
 Lekka i funkcjonalna konstrukcja
 Ważący zaledwie 99,9 g router Cudy TR1200 to idealne rozwiązanie dla osób podróżujących, zapewniając niezawodne połączenie internetowe gdziekolwiek się znajdziesz. Po prostu podłącz TR1200 do swojego laptopa lub ładowarki do telefonu za pomocą złącza USB-C. Wbudowany przełącznik pozwala szybko przełączać się między różnymi ustawieniami VPN, bez konieczności wchodzenia do panelu konfiguracyjnego. Dzięki portowi USB 2.0 możesz podłączyć swój dysk i hostować swoją własną stację chmury, korzystając z protokołów Samba i FTP.</t>
+  </si>
+  <si>
+    <t>Powerbanki</t>
+  </si>
+  <si>
+    <t>Dyski</t>
+  </si>
+  <si>
+    <t>Smartwatche</t>
+  </si>
+  <si>
+    <t>Laptopy</t>
+  </si>
+  <si>
+    <t>Routery</t>
   </si>
 </sst>
 </file>
@@ -14589,24 +13709,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G262"/>
+  <dimension ref="A1:G260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -14620,16 +13743,16 @@
         <v>1275908</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>449</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -14643,16 +13766,16 @@
         <v>1315538</v>
       </c>
       <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>4998</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -14666,16 +13789,16 @@
         <v>1309423</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>6399</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
@@ -14689,16 +13812,16 @@
         <v>1276020</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>649</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -14712,16 +13835,16 @@
         <v>1276626</v>
       </c>
       <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>699</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -14735,16 +13858,16 @@
         <v>1308418</v>
       </c>
       <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>699</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -14758,16 +13881,16 @@
         <v>1306175</v>
       </c>
       <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1489</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>31</v>
@@ -14781,16 +13904,16 @@
         <v>1311166</v>
       </c>
       <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>1499</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>35</v>
@@ -14804,16 +13927,16 @@
         <v>1275905</v>
       </c>
       <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>399</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>38</v>
@@ -14827,16 +13950,16 @@
         <v>1301316</v>
       </c>
       <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>42</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>899</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>43</v>
@@ -14850,16 +13973,16 @@
         <v>1203369</v>
       </c>
       <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>3078</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>47</v>
@@ -14873,16 +13996,16 @@
         <v>1267692</v>
       </c>
       <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
         <v>49</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>50</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>926</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>51</v>
@@ -14896,16 +14019,16 @@
         <v>1281379</v>
       </c>
       <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>26</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>53</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>349</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
@@ -14919,16 +14042,16 @@
         <v>1308427</v>
       </c>
       <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
         <v>26</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>56</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>1048</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>57</v>
@@ -14942,16 +14065,16 @@
         <v>1297576</v>
       </c>
       <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>59</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>2449</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>60</v>
@@ -14965,16 +14088,16 @@
         <v>1311800</v>
       </c>
       <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
         <v>62</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>63</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>7299</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
       </c>
       <c r="F17" t="s">
         <v>64</v>
@@ -14988,16 +14111,16 @@
         <v>1319519</v>
       </c>
       <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
         <v>66</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>67</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>1999</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>68</v>
@@ -15011,16 +14134,16 @@
         <v>1314673</v>
       </c>
       <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
         <v>49</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>70</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>1499</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>71</v>
@@ -15034,16 +14157,16 @@
         <v>1268020</v>
       </c>
       <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
         <v>45</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>73</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>1798</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
       </c>
       <c r="F20" t="s">
         <v>74</v>
@@ -15057,22 +14180,22 @@
         <v>1195867</v>
       </c>
       <c r="B21" t="s">
+        <v>872</v>
+      </c>
+      <c r="C21" t="s">
         <v>76</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>77</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>79</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>78</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>79</v>
-      </c>
-      <c r="G21" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -15080,22 +14203,22 @@
         <v>1256852</v>
       </c>
       <c r="B22" t="s">
+        <v>872</v>
+      </c>
+      <c r="C22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" t="s">
         <v>81</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22">
+        <v>329</v>
+      </c>
+      <c r="F22" t="s">
         <v>82</v>
       </c>
-      <c r="D22">
-        <v>329</v>
-      </c>
-      <c r="E22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>83</v>
-      </c>
-      <c r="G22" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -15103,22 +14226,22 @@
         <v>1299238</v>
       </c>
       <c r="B23" t="s">
+        <v>872</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
         <v>85</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23">
+        <v>389</v>
+      </c>
+      <c r="F23" t="s">
         <v>86</v>
       </c>
-      <c r="D23">
-        <v>389</v>
-      </c>
-      <c r="E23" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>87</v>
-      </c>
-      <c r="G23" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -15126,22 +14249,22 @@
         <v>1276972</v>
       </c>
       <c r="B24" t="s">
+        <v>872</v>
+      </c>
+      <c r="C24" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" t="s">
         <v>89</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24">
+        <v>139</v>
+      </c>
+      <c r="F24" t="s">
         <v>90</v>
       </c>
-      <c r="D24">
-        <v>139</v>
-      </c>
-      <c r="E24" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>91</v>
-      </c>
-      <c r="G24" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -15149,22 +14272,22 @@
         <v>1274200</v>
       </c>
       <c r="B25" t="s">
+        <v>872</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
         <v>93</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25">
+        <v>239</v>
+      </c>
+      <c r="F25" t="s">
         <v>94</v>
       </c>
-      <c r="D25">
-        <v>239</v>
-      </c>
-      <c r="E25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>95</v>
-      </c>
-      <c r="G25" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -15172,22 +14295,22 @@
         <v>1310912</v>
       </c>
       <c r="B26" t="s">
+        <v>872</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" t="s">
         <v>97</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26">
+        <v>89</v>
+      </c>
+      <c r="F26" t="s">
         <v>98</v>
       </c>
-      <c r="D26">
-        <v>89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>99</v>
-      </c>
-      <c r="G26" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -15195,22 +14318,22 @@
         <v>1294886</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>872</v>
       </c>
       <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27">
+        <v>599</v>
+      </c>
+      <c r="F27" t="s">
         <v>101</v>
       </c>
-      <c r="D27">
-        <v>599</v>
-      </c>
-      <c r="E27" t="s">
-        <v>78</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>102</v>
-      </c>
-      <c r="G27" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -15218,22 +14341,22 @@
         <v>1316771</v>
       </c>
       <c r="B28" t="s">
+        <v>872</v>
+      </c>
+      <c r="C28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" t="s">
         <v>104</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E28">
+        <v>159</v>
+      </c>
+      <c r="F28" t="s">
         <v>105</v>
       </c>
-      <c r="D28">
-        <v>159</v>
-      </c>
-      <c r="E28" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>106</v>
-      </c>
-      <c r="G28" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -15241,22 +14364,22 @@
         <v>1276422</v>
       </c>
       <c r="B29" t="s">
+        <v>872</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
         <v>108</v>
       </c>
-      <c r="C29" t="s">
+      <c r="E29">
+        <v>169</v>
+      </c>
+      <c r="F29" t="s">
         <v>109</v>
       </c>
-      <c r="D29">
-        <v>169</v>
-      </c>
-      <c r="E29" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>110</v>
-      </c>
-      <c r="G29" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -15264,22 +14387,22 @@
         <v>1287637</v>
       </c>
       <c r="B30" t="s">
+        <v>872</v>
+      </c>
+      <c r="C30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" t="s">
         <v>112</v>
       </c>
-      <c r="C30" t="s">
+      <c r="E30">
+        <v>99</v>
+      </c>
+      <c r="F30" t="s">
         <v>113</v>
       </c>
-      <c r="D30">
-        <v>99</v>
-      </c>
-      <c r="E30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>114</v>
-      </c>
-      <c r="G30" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -15287,22 +14410,22 @@
         <v>1310903</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>872</v>
       </c>
       <c r="C31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31">
+        <v>134</v>
+      </c>
+      <c r="F31" t="s">
         <v>116</v>
       </c>
-      <c r="D31">
-        <v>134</v>
-      </c>
-      <c r="E31" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>117</v>
-      </c>
-      <c r="G31" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -15310,22 +14433,22 @@
         <v>1276909</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>872</v>
       </c>
       <c r="C32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32">
+        <v>399</v>
+      </c>
+      <c r="F32" t="s">
         <v>119</v>
       </c>
-      <c r="D32">
-        <v>399</v>
-      </c>
-      <c r="E32" t="s">
-        <v>78</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>120</v>
-      </c>
-      <c r="G32" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -15333,22 +14456,22 @@
         <v>1220008</v>
       </c>
       <c r="B33" t="s">
+        <v>872</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
         <v>122</v>
       </c>
-      <c r="C33" t="s">
+      <c r="E33">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
         <v>123</v>
       </c>
-      <c r="D33">
-        <v>49</v>
-      </c>
-      <c r="E33" t="s">
-        <v>78</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>124</v>
-      </c>
-      <c r="G33" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -15356,22 +14479,22 @@
         <v>1314072</v>
       </c>
       <c r="B34" t="s">
+        <v>872</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
         <v>126</v>
       </c>
-      <c r="C34" t="s">
+      <c r="E34">
+        <v>369</v>
+      </c>
+      <c r="F34" t="s">
         <v>127</v>
       </c>
-      <c r="D34">
-        <v>369</v>
-      </c>
-      <c r="E34" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>128</v>
-      </c>
-      <c r="G34" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -15379,22 +14502,22 @@
         <v>1245980</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>872</v>
       </c>
       <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35">
+        <v>349</v>
+      </c>
+      <c r="F35" t="s">
         <v>130</v>
       </c>
-      <c r="D35">
-        <v>349</v>
-      </c>
-      <c r="E35" t="s">
-        <v>78</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>131</v>
-      </c>
-      <c r="G35" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -15402,22 +14525,22 @@
         <v>1288162</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>872</v>
       </c>
       <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36">
+        <v>149</v>
+      </c>
+      <c r="F36" t="s">
         <v>133</v>
       </c>
-      <c r="D36">
-        <v>149</v>
-      </c>
-      <c r="E36" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>134</v>
-      </c>
-      <c r="G36" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -15425,19 +14548,19 @@
         <v>1178231</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>872</v>
       </c>
       <c r="C37" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37">
+        <v>199</v>
+      </c>
+      <c r="F37" t="s">
         <v>136</v>
-      </c>
-      <c r="D37">
-        <v>199</v>
-      </c>
-      <c r="E37" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -15445,22 +14568,22 @@
         <v>1270311</v>
       </c>
       <c r="B38" t="s">
-        <v>112</v>
+        <v>872</v>
       </c>
       <c r="C38" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38">
+        <v>89</v>
+      </c>
+      <c r="F38" t="s">
         <v>138</v>
       </c>
-      <c r="D38">
-        <v>89</v>
-      </c>
-      <c r="E38" t="s">
-        <v>78</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>139</v>
-      </c>
-      <c r="G38" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -15468,22 +14591,22 @@
         <v>1310909</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>872</v>
       </c>
       <c r="C39" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39">
+        <v>89</v>
+      </c>
+      <c r="F39" t="s">
         <v>141</v>
       </c>
-      <c r="D39">
-        <v>89</v>
-      </c>
-      <c r="E39" t="s">
-        <v>78</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>142</v>
-      </c>
-      <c r="G39" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -15491,22 +14614,22 @@
         <v>1279543</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>872</v>
       </c>
       <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40">
+        <v>89</v>
+      </c>
+      <c r="F40" t="s">
         <v>144</v>
       </c>
-      <c r="D40">
-        <v>89</v>
-      </c>
-      <c r="E40" t="s">
-        <v>78</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>145</v>
-      </c>
-      <c r="G40" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -15514,22 +14637,22 @@
         <v>1284014</v>
       </c>
       <c r="B41" t="s">
+        <v>872</v>
+      </c>
+      <c r="C41" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" t="s">
         <v>147</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E41">
+        <v>349</v>
+      </c>
+      <c r="F41" t="s">
         <v>148</v>
       </c>
-      <c r="D41">
-        <v>349</v>
-      </c>
-      <c r="E41" t="s">
-        <v>78</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>149</v>
-      </c>
-      <c r="G41" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -15537,22 +14660,22 @@
         <v>1279537</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>872</v>
       </c>
       <c r="C42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" t="s">
+        <v>150</v>
+      </c>
+      <c r="E42">
+        <v>99</v>
+      </c>
+      <c r="F42" t="s">
         <v>151</v>
       </c>
-      <c r="D42">
-        <v>99</v>
-      </c>
-      <c r="E42" t="s">
-        <v>78</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>152</v>
-      </c>
-      <c r="G42" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -15560,22 +14683,22 @@
         <v>691100</v>
       </c>
       <c r="B43" t="s">
+        <v>873</v>
+      </c>
+      <c r="C43" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43" t="s">
         <v>154</v>
       </c>
-      <c r="C43" t="s">
+      <c r="E43">
+        <v>369</v>
+      </c>
+      <c r="F43" t="s">
         <v>155</v>
       </c>
-      <c r="D43">
-        <v>369</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>156</v>
-      </c>
-      <c r="F43" t="s">
-        <v>157</v>
-      </c>
-      <c r="G43" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -15583,22 +14706,22 @@
         <v>590339</v>
       </c>
       <c r="B44" t="s">
+        <v>873</v>
+      </c>
+      <c r="C44" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" t="s">
+        <v>158</v>
+      </c>
+      <c r="E44">
+        <v>79</v>
+      </c>
+      <c r="F44" t="s">
         <v>159</v>
       </c>
-      <c r="C44" t="s">
+      <c r="G44" t="s">
         <v>160</v>
-      </c>
-      <c r="D44">
-        <v>79</v>
-      </c>
-      <c r="E44" t="s">
-        <v>156</v>
-      </c>
-      <c r="F44" t="s">
-        <v>161</v>
-      </c>
-      <c r="G44" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -15606,22 +14729,22 @@
         <v>1309298</v>
       </c>
       <c r="B45" t="s">
+        <v>873</v>
+      </c>
+      <c r="C45" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" t="s">
+        <v>162</v>
+      </c>
+      <c r="E45">
+        <v>279</v>
+      </c>
+      <c r="F45" t="s">
         <v>163</v>
       </c>
-      <c r="C45" t="s">
+      <c r="G45" t="s">
         <v>164</v>
-      </c>
-      <c r="D45">
-        <v>279</v>
-      </c>
-      <c r="E45" t="s">
-        <v>156</v>
-      </c>
-      <c r="F45" t="s">
-        <v>165</v>
-      </c>
-      <c r="G45" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -15629,22 +14752,22 @@
         <v>1160141</v>
       </c>
       <c r="B46" t="s">
+        <v>873</v>
+      </c>
+      <c r="C46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46">
+        <v>259</v>
+      </c>
+      <c r="F46" t="s">
         <v>167</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
         <v>168</v>
-      </c>
-      <c r="D46">
-        <v>259</v>
-      </c>
-      <c r="E46" t="s">
-        <v>156</v>
-      </c>
-      <c r="F46" t="s">
-        <v>169</v>
-      </c>
-      <c r="G46" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -15652,22 +14775,22 @@
         <v>1163934</v>
       </c>
       <c r="B47" t="s">
+        <v>873</v>
+      </c>
+      <c r="C47" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" t="s">
+        <v>170</v>
+      </c>
+      <c r="E47">
+        <v>299</v>
+      </c>
+      <c r="F47" t="s">
         <v>171</v>
       </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
         <v>172</v>
-      </c>
-      <c r="D47">
-        <v>299</v>
-      </c>
-      <c r="E47" t="s">
-        <v>156</v>
-      </c>
-      <c r="F47" t="s">
-        <v>173</v>
-      </c>
-      <c r="G47" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -15675,22 +14798,22 @@
         <v>1311951</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>873</v>
       </c>
       <c r="C48" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48">
+        <v>269</v>
+      </c>
+      <c r="F48" t="s">
+        <v>174</v>
+      </c>
+      <c r="G48" t="s">
         <v>175</v>
-      </c>
-      <c r="D48">
-        <v>269</v>
-      </c>
-      <c r="E48" t="s">
-        <v>156</v>
-      </c>
-      <c r="F48" t="s">
-        <v>176</v>
-      </c>
-      <c r="G48" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -15698,22 +14821,22 @@
         <v>1290963</v>
       </c>
       <c r="B49" t="s">
+        <v>873</v>
+      </c>
+      <c r="C49" t="s">
         <v>7</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
+        <v>176</v>
+      </c>
+      <c r="E49">
+        <v>559</v>
+      </c>
+      <c r="F49" t="s">
+        <v>177</v>
+      </c>
+      <c r="G49" t="s">
         <v>178</v>
-      </c>
-      <c r="D49">
-        <v>559</v>
-      </c>
-      <c r="E49" t="s">
-        <v>156</v>
-      </c>
-      <c r="F49" t="s">
-        <v>179</v>
-      </c>
-      <c r="G49" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -15721,22 +14844,22 @@
         <v>1083717</v>
       </c>
       <c r="B50" t="s">
+        <v>873</v>
+      </c>
+      <c r="C50" t="s">
         <v>7</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>179</v>
+      </c>
+      <c r="E50">
+        <v>449</v>
+      </c>
+      <c r="F50" t="s">
+        <v>180</v>
+      </c>
+      <c r="G50" t="s">
         <v>181</v>
-      </c>
-      <c r="D50">
-        <v>449</v>
-      </c>
-      <c r="E50" t="s">
-        <v>156</v>
-      </c>
-      <c r="F50" t="s">
-        <v>182</v>
-      </c>
-      <c r="G50" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -15744,22 +14867,22 @@
         <v>1273617</v>
       </c>
       <c r="B51" t="s">
+        <v>873</v>
+      </c>
+      <c r="C51" t="s">
+        <v>182</v>
+      </c>
+      <c r="D51" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51">
+        <v>515</v>
+      </c>
+      <c r="F51" t="s">
         <v>184</v>
       </c>
-      <c r="C51" t="s">
+      <c r="G51" t="s">
         <v>185</v>
-      </c>
-      <c r="D51">
-        <v>515</v>
-      </c>
-      <c r="E51" t="s">
-        <v>156</v>
-      </c>
-      <c r="F51" t="s">
-        <v>186</v>
-      </c>
-      <c r="G51" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -15767,22 +14890,22 @@
         <v>1273429</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>873</v>
       </c>
       <c r="C52" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" t="s">
+        <v>186</v>
+      </c>
+      <c r="E52">
+        <v>249</v>
+      </c>
+      <c r="F52" t="s">
+        <v>187</v>
+      </c>
+      <c r="G52" t="s">
         <v>188</v>
-      </c>
-      <c r="D52">
-        <v>249</v>
-      </c>
-      <c r="E52" t="s">
-        <v>156</v>
-      </c>
-      <c r="F52" t="s">
-        <v>189</v>
-      </c>
-      <c r="G52" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -15790,22 +14913,22 @@
         <v>590335</v>
       </c>
       <c r="B53" t="s">
-        <v>159</v>
+        <v>873</v>
       </c>
       <c r="C53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" t="s">
+        <v>189</v>
+      </c>
+      <c r="E53">
+        <v>129</v>
+      </c>
+      <c r="F53" t="s">
+        <v>190</v>
+      </c>
+      <c r="G53" t="s">
         <v>191</v>
-      </c>
-      <c r="D53">
-        <v>129</v>
-      </c>
-      <c r="E53" t="s">
-        <v>192</v>
-      </c>
-      <c r="F53" t="s">
-        <v>193</v>
-      </c>
-      <c r="G53" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -15813,22 +14936,22 @@
         <v>1146134</v>
       </c>
       <c r="B54" t="s">
-        <v>184</v>
+        <v>873</v>
       </c>
       <c r="C54" t="s">
-        <v>195</v>
-      </c>
-      <c r="D54">
+        <v>182</v>
+      </c>
+      <c r="D54" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54">
         <v>324</v>
       </c>
-      <c r="E54" t="s">
-        <v>192</v>
-      </c>
       <c r="F54" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G54" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -15836,22 +14959,22 @@
         <v>1290960</v>
       </c>
       <c r="B55" t="s">
+        <v>873</v>
+      </c>
+      <c r="C55" t="s">
         <v>7</v>
       </c>
-      <c r="C55" t="s">
-        <v>198</v>
-      </c>
-      <c r="D55">
+      <c r="D55" t="s">
+        <v>195</v>
+      </c>
+      <c r="E55">
         <v>329</v>
       </c>
-      <c r="E55" t="s">
-        <v>192</v>
-      </c>
       <c r="F55" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G55" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -15859,22 +14982,22 @@
         <v>621625</v>
       </c>
       <c r="B56" t="s">
-        <v>184</v>
+        <v>873</v>
       </c>
       <c r="C56" t="s">
-        <v>201</v>
-      </c>
-      <c r="D56">
+        <v>182</v>
+      </c>
+      <c r="D56" t="s">
+        <v>198</v>
+      </c>
+      <c r="E56">
         <v>249</v>
       </c>
-      <c r="E56" t="s">
-        <v>192</v>
-      </c>
       <c r="F56" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G56" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -15882,22 +15005,22 @@
         <v>1083719</v>
       </c>
       <c r="B57" t="s">
+        <v>873</v>
+      </c>
+      <c r="C57" t="s">
         <v>7</v>
       </c>
-      <c r="C57" t="s">
-        <v>204</v>
-      </c>
-      <c r="D57">
+      <c r="D57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E57">
         <v>699</v>
       </c>
-      <c r="E57" t="s">
-        <v>192</v>
-      </c>
       <c r="F57" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G57" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
@@ -15905,22 +15028,22 @@
         <v>1273616</v>
       </c>
       <c r="B58" t="s">
-        <v>184</v>
+        <v>873</v>
       </c>
       <c r="C58" t="s">
-        <v>207</v>
-      </c>
-      <c r="D58">
+        <v>182</v>
+      </c>
+      <c r="D58" t="s">
+        <v>204</v>
+      </c>
+      <c r="E58">
         <v>279</v>
       </c>
-      <c r="E58" t="s">
-        <v>192</v>
-      </c>
       <c r="F58" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G58" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
@@ -15928,22 +15051,22 @@
         <v>1275363</v>
       </c>
       <c r="B59" t="s">
+        <v>873</v>
+      </c>
+      <c r="C59" t="s">
+        <v>207</v>
+      </c>
+      <c r="D59" t="s">
+        <v>208</v>
+      </c>
+      <c r="E59">
+        <v>619</v>
+      </c>
+      <c r="F59" t="s">
+        <v>209</v>
+      </c>
+      <c r="G59" t="s">
         <v>210</v>
-      </c>
-      <c r="C59" t="s">
-        <v>211</v>
-      </c>
-      <c r="D59">
-        <v>619</v>
-      </c>
-      <c r="E59" t="s">
-        <v>192</v>
-      </c>
-      <c r="F59" t="s">
-        <v>212</v>
-      </c>
-      <c r="G59" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
@@ -15951,22 +15074,22 @@
         <v>1146135</v>
       </c>
       <c r="B60" t="s">
-        <v>184</v>
+        <v>873</v>
       </c>
       <c r="C60" t="s">
-        <v>214</v>
-      </c>
-      <c r="D60">
+        <v>182</v>
+      </c>
+      <c r="D60" t="s">
+        <v>211</v>
+      </c>
+      <c r="E60">
         <v>549</v>
       </c>
-      <c r="E60" t="s">
-        <v>192</v>
-      </c>
       <c r="F60" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G60" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
@@ -15974,22 +15097,22 @@
         <v>691108</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>873</v>
       </c>
       <c r="C61" t="s">
-        <v>217</v>
-      </c>
-      <c r="D61">
+        <v>153</v>
+      </c>
+      <c r="D61" t="s">
+        <v>214</v>
+      </c>
+      <c r="E61">
         <v>629</v>
       </c>
-      <c r="E61" t="s">
-        <v>192</v>
-      </c>
       <c r="F61" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G61" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
@@ -15997,22 +15120,22 @@
         <v>590340</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>873</v>
       </c>
       <c r="C62" t="s">
-        <v>220</v>
-      </c>
-      <c r="D62">
+        <v>157</v>
+      </c>
+      <c r="D62" t="s">
+        <v>217</v>
+      </c>
+      <c r="E62">
         <v>229</v>
       </c>
-      <c r="E62" t="s">
-        <v>192</v>
-      </c>
       <c r="F62" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G62" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
@@ -16020,22 +15143,22 @@
         <v>704554</v>
       </c>
       <c r="B63" t="s">
-        <v>184</v>
+        <v>873</v>
       </c>
       <c r="C63" t="s">
-        <v>223</v>
-      </c>
-      <c r="D63">
+        <v>182</v>
+      </c>
+      <c r="D63" t="s">
+        <v>220</v>
+      </c>
+      <c r="E63">
         <v>489</v>
       </c>
-      <c r="E63" t="s">
-        <v>192</v>
-      </c>
       <c r="F63" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G63" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
@@ -16043,22 +15166,22 @@
         <v>734881</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>873</v>
       </c>
       <c r="C64" t="s">
-        <v>226</v>
-      </c>
-      <c r="D64">
+        <v>165</v>
+      </c>
+      <c r="D64" t="s">
+        <v>223</v>
+      </c>
+      <c r="E64">
         <v>329</v>
       </c>
-      <c r="E64" t="s">
-        <v>192</v>
-      </c>
       <c r="F64" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G64" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
@@ -16066,22 +15189,22 @@
         <v>1138151</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>873</v>
       </c>
       <c r="C65" t="s">
-        <v>229</v>
-      </c>
-      <c r="D65">
+        <v>169</v>
+      </c>
+      <c r="D65" t="s">
+        <v>226</v>
+      </c>
+      <c r="E65">
         <v>239</v>
       </c>
-      <c r="E65" t="s">
-        <v>192</v>
-      </c>
       <c r="F65" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G65" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -16089,22 +15212,22 @@
         <v>1154568</v>
       </c>
       <c r="B66" t="s">
+        <v>873</v>
+      </c>
+      <c r="C66" t="s">
+        <v>229</v>
+      </c>
+      <c r="D66" t="s">
+        <v>230</v>
+      </c>
+      <c r="E66">
+        <v>529</v>
+      </c>
+      <c r="F66" t="s">
+        <v>231</v>
+      </c>
+      <c r="G66" t="s">
         <v>232</v>
-      </c>
-      <c r="C66" t="s">
-        <v>233</v>
-      </c>
-      <c r="D66">
-        <v>529</v>
-      </c>
-      <c r="E66" t="s">
-        <v>192</v>
-      </c>
-      <c r="F66" t="s">
-        <v>234</v>
-      </c>
-      <c r="G66" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -16112,22 +15235,22 @@
         <v>1145893</v>
       </c>
       <c r="B67" t="s">
-        <v>237</v>
+        <v>874</v>
       </c>
       <c r="C67" t="s">
-        <v>238</v>
-      </c>
-      <c r="D67">
+        <v>233</v>
+      </c>
+      <c r="D67" t="s">
+        <v>234</v>
+      </c>
+      <c r="E67">
         <v>1349</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
+        <v>235</v>
+      </c>
+      <c r="G67" t="s">
         <v>236</v>
-      </c>
-      <c r="F67" t="s">
-        <v>239</v>
-      </c>
-      <c r="G67" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -16135,22 +15258,22 @@
         <v>1206542</v>
       </c>
       <c r="B68" t="s">
+        <v>874</v>
+      </c>
+      <c r="C68" t="s">
         <v>41</v>
       </c>
-      <c r="C68" t="s">
-        <v>241</v>
-      </c>
-      <c r="D68">
+      <c r="D68" t="s">
+        <v>237</v>
+      </c>
+      <c r="E68">
         <v>199</v>
       </c>
-      <c r="E68" t="s">
-        <v>236</v>
-      </c>
       <c r="F68" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G68" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -16158,22 +15281,22 @@
         <v>1278012</v>
       </c>
       <c r="B69" t="s">
+        <v>874</v>
+      </c>
+      <c r="C69" t="s">
         <v>40</v>
       </c>
-      <c r="C69" t="s">
-        <v>244</v>
-      </c>
-      <c r="D69">
+      <c r="D69" t="s">
+        <v>240</v>
+      </c>
+      <c r="E69">
         <v>968</v>
       </c>
-      <c r="E69" t="s">
-        <v>236</v>
-      </c>
       <c r="F69" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G69" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -16181,22 +15304,22 @@
         <v>1242902</v>
       </c>
       <c r="B70" t="s">
-        <v>247</v>
+        <v>874</v>
       </c>
       <c r="C70" t="s">
-        <v>248</v>
-      </c>
-      <c r="D70">
+        <v>243</v>
+      </c>
+      <c r="D70" t="s">
+        <v>244</v>
+      </c>
+      <c r="E70">
         <v>349</v>
       </c>
-      <c r="E70" t="s">
-        <v>236</v>
-      </c>
       <c r="F70" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G70" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -16204,22 +15327,22 @@
         <v>1311370</v>
       </c>
       <c r="B71" t="s">
+        <v>874</v>
+      </c>
+      <c r="C71" t="s">
         <v>26</v>
       </c>
-      <c r="C71" t="s">
-        <v>251</v>
-      </c>
-      <c r="D71">
+      <c r="D71" t="s">
+        <v>247</v>
+      </c>
+      <c r="E71">
         <v>389</v>
       </c>
-      <c r="E71" t="s">
-        <v>236</v>
-      </c>
       <c r="F71" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G71" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
@@ -16227,22 +15350,22 @@
         <v>1262079</v>
       </c>
       <c r="B72" t="s">
+        <v>874</v>
+      </c>
+      <c r="C72" t="s">
         <v>41</v>
       </c>
-      <c r="C72" t="s">
-        <v>254</v>
-      </c>
-      <c r="D72">
+      <c r="D72" t="s">
+        <v>250</v>
+      </c>
+      <c r="E72">
         <v>299</v>
       </c>
-      <c r="E72" t="s">
-        <v>236</v>
-      </c>
       <c r="F72" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G72" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
@@ -16250,22 +15373,22 @@
         <v>1273180</v>
       </c>
       <c r="B73" t="s">
+        <v>874</v>
+      </c>
+      <c r="C73" t="s">
         <v>62</v>
       </c>
-      <c r="C73" t="s">
-        <v>257</v>
-      </c>
-      <c r="D73">
+      <c r="D73" t="s">
+        <v>253</v>
+      </c>
+      <c r="E73">
         <v>649</v>
       </c>
-      <c r="E73" t="s">
-        <v>236</v>
-      </c>
       <c r="F73" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G73" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
@@ -16273,22 +15396,22 @@
         <v>1154522</v>
       </c>
       <c r="B74" t="s">
-        <v>237</v>
+        <v>874</v>
       </c>
       <c r="C74" t="s">
-        <v>260</v>
-      </c>
-      <c r="D74">
+        <v>233</v>
+      </c>
+      <c r="D74" t="s">
+        <v>256</v>
+      </c>
+      <c r="E74">
         <v>1659</v>
       </c>
-      <c r="E74" t="s">
-        <v>236</v>
-      </c>
       <c r="F74" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G74" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
@@ -16296,22 +15419,22 @@
         <v>1141440</v>
       </c>
       <c r="B75" t="s">
-        <v>263</v>
+        <v>874</v>
       </c>
       <c r="C75" t="s">
-        <v>264</v>
-      </c>
-      <c r="D75">
+        <v>259</v>
+      </c>
+      <c r="D75" t="s">
+        <v>260</v>
+      </c>
+      <c r="E75">
         <v>1877</v>
       </c>
-      <c r="E75" t="s">
-        <v>236</v>
-      </c>
       <c r="F75" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G75" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
@@ -16319,22 +15442,22 @@
         <v>1276872</v>
       </c>
       <c r="B76" t="s">
+        <v>874</v>
+      </c>
+      <c r="C76" t="s">
         <v>62</v>
       </c>
-      <c r="C76" t="s">
-        <v>267</v>
-      </c>
-      <c r="D76">
+      <c r="D76" t="s">
+        <v>263</v>
+      </c>
+      <c r="E76">
         <v>1499</v>
       </c>
-      <c r="E76" t="s">
-        <v>236</v>
-      </c>
       <c r="F76" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G76" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
@@ -16342,22 +15465,22 @@
         <v>1276873</v>
       </c>
       <c r="B77" t="s">
+        <v>874</v>
+      </c>
+      <c r="C77" t="s">
         <v>62</v>
       </c>
-      <c r="C77" t="s">
-        <v>270</v>
-      </c>
-      <c r="D77">
+      <c r="D77" t="s">
+        <v>266</v>
+      </c>
+      <c r="E77">
         <v>1199</v>
       </c>
-      <c r="E77" t="s">
-        <v>236</v>
-      </c>
       <c r="F77" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G77" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
@@ -16365,22 +15488,22 @@
         <v>1224532</v>
       </c>
       <c r="B78" t="s">
-        <v>273</v>
+        <v>874</v>
       </c>
       <c r="C78" t="s">
-        <v>274</v>
-      </c>
-      <c r="D78">
+        <v>269</v>
+      </c>
+      <c r="D78" t="s">
+        <v>270</v>
+      </c>
+      <c r="E78">
         <v>2349</v>
       </c>
-      <c r="E78" t="s">
-        <v>236</v>
-      </c>
       <c r="F78" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G78" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
@@ -16388,22 +15511,22 @@
         <v>1204690</v>
       </c>
       <c r="B79" t="s">
-        <v>277</v>
+        <v>874</v>
       </c>
       <c r="C79" t="s">
-        <v>278</v>
-      </c>
-      <c r="D79">
+        <v>273</v>
+      </c>
+      <c r="D79" t="s">
+        <v>274</v>
+      </c>
+      <c r="E79">
         <v>679</v>
       </c>
-      <c r="E79" t="s">
-        <v>236</v>
-      </c>
       <c r="F79" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G79" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
@@ -16411,22 +15534,22 @@
         <v>1150231</v>
       </c>
       <c r="B80" t="s">
-        <v>237</v>
+        <v>874</v>
       </c>
       <c r="C80" t="s">
-        <v>281</v>
-      </c>
-      <c r="D80">
+        <v>233</v>
+      </c>
+      <c r="D80" t="s">
+        <v>277</v>
+      </c>
+      <c r="E80">
         <v>2899</v>
       </c>
-      <c r="E80" t="s">
-        <v>236</v>
-      </c>
       <c r="F80" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G80" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
@@ -16434,22 +15557,22 @@
         <v>1241003</v>
       </c>
       <c r="B81" t="s">
+        <v>874</v>
+      </c>
+      <c r="C81" t="s">
         <v>62</v>
       </c>
-      <c r="C81" t="s">
-        <v>284</v>
-      </c>
-      <c r="D81">
+      <c r="D81" t="s">
+        <v>280</v>
+      </c>
+      <c r="E81">
         <v>549</v>
       </c>
-      <c r="E81" t="s">
-        <v>236</v>
-      </c>
       <c r="F81" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G81" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
@@ -16457,22 +15580,22 @@
         <v>1229681</v>
       </c>
       <c r="B82" t="s">
-        <v>263</v>
+        <v>874</v>
       </c>
       <c r="C82" t="s">
-        <v>287</v>
-      </c>
-      <c r="D82">
+        <v>259</v>
+      </c>
+      <c r="D82" t="s">
+        <v>283</v>
+      </c>
+      <c r="E82">
         <v>2199</v>
       </c>
-      <c r="E82" t="s">
-        <v>236</v>
-      </c>
       <c r="F82" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G82" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
@@ -16480,22 +15603,22 @@
         <v>1233789</v>
       </c>
       <c r="B83" t="s">
-        <v>290</v>
+        <v>874</v>
       </c>
       <c r="C83" t="s">
-        <v>291</v>
-      </c>
-      <c r="D83">
+        <v>286</v>
+      </c>
+      <c r="D83" t="s">
+        <v>287</v>
+      </c>
+      <c r="E83">
         <v>2959</v>
       </c>
-      <c r="E83" t="s">
-        <v>236</v>
-      </c>
       <c r="F83" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G83" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
@@ -16503,22 +15626,22 @@
         <v>1048088</v>
       </c>
       <c r="B84" t="s">
+        <v>874</v>
+      </c>
+      <c r="C84" t="s">
+        <v>286</v>
+      </c>
+      <c r="D84" t="s">
         <v>290</v>
       </c>
-      <c r="C84" t="s">
-        <v>294</v>
-      </c>
-      <c r="D84">
+      <c r="E84">
         <v>999</v>
       </c>
-      <c r="E84" t="s">
-        <v>236</v>
-      </c>
       <c r="F84" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G84" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
@@ -16526,22 +15649,22 @@
         <v>1221697</v>
       </c>
       <c r="B85" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C85" t="s">
-        <v>298</v>
-      </c>
-      <c r="D85">
+        <v>293</v>
+      </c>
+      <c r="D85" t="s">
+        <v>294</v>
+      </c>
+      <c r="E85">
         <v>3334</v>
       </c>
-      <c r="E85" t="s">
-        <v>299</v>
-      </c>
       <c r="F85" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G85" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
@@ -16549,22 +15672,22 @@
         <v>1226981</v>
       </c>
       <c r="B86" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C86" t="s">
-        <v>303</v>
-      </c>
-      <c r="D86">
+        <v>297</v>
+      </c>
+      <c r="D86" t="s">
+        <v>298</v>
+      </c>
+      <c r="E86">
         <v>1439</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>299</v>
       </c>
-      <c r="F86" t="s">
-        <v>304</v>
-      </c>
       <c r="G86" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
@@ -16572,22 +15695,22 @@
         <v>1300165</v>
       </c>
       <c r="B87" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C87" t="s">
-        <v>307</v>
-      </c>
-      <c r="D87">
+        <v>301</v>
+      </c>
+      <c r="D87" t="s">
+        <v>302</v>
+      </c>
+      <c r="E87">
         <v>1549</v>
       </c>
-      <c r="E87" t="s">
-        <v>299</v>
-      </c>
       <c r="F87" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G87" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
@@ -16595,22 +15718,22 @@
         <v>715089</v>
       </c>
       <c r="B88" t="s">
+        <v>312</v>
+      </c>
+      <c r="C88" t="s">
+        <v>301</v>
+      </c>
+      <c r="D88" t="s">
+        <v>305</v>
+      </c>
+      <c r="E88">
+        <v>717</v>
+      </c>
+      <c r="F88" t="s">
         <v>306</v>
       </c>
-      <c r="C88" t="s">
-        <v>310</v>
-      </c>
-      <c r="D88">
-        <v>717</v>
-      </c>
-      <c r="E88" t="s">
-        <v>299</v>
-      </c>
-      <c r="F88" t="s">
-        <v>311</v>
-      </c>
       <c r="G88" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
@@ -16618,22 +15741,22 @@
         <v>742554</v>
       </c>
       <c r="B89" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C89" t="s">
-        <v>313</v>
-      </c>
-      <c r="D89">
+        <v>297</v>
+      </c>
+      <c r="D89" t="s">
+        <v>308</v>
+      </c>
+      <c r="E89">
         <v>784</v>
       </c>
-      <c r="E89" t="s">
-        <v>299</v>
-      </c>
       <c r="F89" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="G89" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
@@ -16641,22 +15764,22 @@
         <v>661713</v>
       </c>
       <c r="B90" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C90" t="s">
-        <v>316</v>
-      </c>
-      <c r="D90">
+        <v>297</v>
+      </c>
+      <c r="D90" t="s">
+        <v>311</v>
+      </c>
+      <c r="E90">
         <v>1279</v>
       </c>
-      <c r="E90" t="s">
-        <v>317</v>
-      </c>
       <c r="F90" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G90" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
@@ -16664,22 +15787,22 @@
         <v>1309819</v>
       </c>
       <c r="B91" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C91" t="s">
-        <v>320</v>
-      </c>
-      <c r="D91">
+        <v>297</v>
+      </c>
+      <c r="D91" t="s">
+        <v>315</v>
+      </c>
+      <c r="E91">
         <v>4189</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
+        <v>316</v>
+      </c>
+      <c r="G91" t="s">
         <v>317</v>
-      </c>
-      <c r="F91" t="s">
-        <v>321</v>
-      </c>
-      <c r="G91" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
@@ -16687,22 +15810,22 @@
         <v>1335485</v>
       </c>
       <c r="B92" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C92" t="s">
-        <v>324</v>
-      </c>
-      <c r="D92">
+        <v>318</v>
+      </c>
+      <c r="D92" t="s">
+        <v>319</v>
+      </c>
+      <c r="E92">
         <v>1299</v>
       </c>
-      <c r="E92" t="s">
-        <v>317</v>
-      </c>
       <c r="F92" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G92" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
@@ -16710,22 +15833,22 @@
         <v>1226950</v>
       </c>
       <c r="B93" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
-      </c>
-      <c r="D93">
+        <v>322</v>
+      </c>
+      <c r="D93" t="s">
+        <v>323</v>
+      </c>
+      <c r="E93">
         <v>799</v>
       </c>
-      <c r="E93" t="s">
-        <v>317</v>
-      </c>
       <c r="F93" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G93" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
@@ -16733,22 +15856,22 @@
         <v>1314559</v>
       </c>
       <c r="B94" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="C94" t="s">
-        <v>331</v>
-      </c>
-      <c r="D94">
+        <v>161</v>
+      </c>
+      <c r="D94" t="s">
+        <v>326</v>
+      </c>
+      <c r="E94">
         <v>12499</v>
       </c>
-      <c r="E94" t="s">
-        <v>317</v>
-      </c>
       <c r="F94" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G94" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
@@ -16756,22 +15879,22 @@
         <v>1104110</v>
       </c>
       <c r="B95" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C95" t="s">
-        <v>335</v>
-      </c>
-      <c r="D95">
+        <v>329</v>
+      </c>
+      <c r="D95" t="s">
+        <v>330</v>
+      </c>
+      <c r="E95">
         <v>3849</v>
       </c>
-      <c r="E95" t="s">
-        <v>317</v>
-      </c>
       <c r="F95" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="G95" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
@@ -16779,22 +15902,22 @@
         <v>1165457</v>
       </c>
       <c r="B96" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C96" t="s">
-        <v>338</v>
-      </c>
-      <c r="D96">
+        <v>301</v>
+      </c>
+      <c r="D96" t="s">
+        <v>333</v>
+      </c>
+      <c r="E96">
         <v>1999</v>
       </c>
-      <c r="E96" t="s">
-        <v>317</v>
-      </c>
       <c r="F96" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="G96" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
@@ -16802,22 +15925,22 @@
         <v>1299534</v>
       </c>
       <c r="B97" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="C97" t="s">
-        <v>341</v>
-      </c>
-      <c r="D97">
+        <v>161</v>
+      </c>
+      <c r="D97" t="s">
+        <v>336</v>
+      </c>
+      <c r="E97">
         <v>979</v>
       </c>
-      <c r="E97" t="s">
-        <v>317</v>
-      </c>
       <c r="F97" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G97" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
@@ -16825,22 +15948,22 @@
         <v>1072799</v>
       </c>
       <c r="B98" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C98" t="s">
-        <v>344</v>
-      </c>
-      <c r="D98">
+        <v>297</v>
+      </c>
+      <c r="D98" t="s">
+        <v>339</v>
+      </c>
+      <c r="E98">
         <v>1239</v>
       </c>
-      <c r="E98" t="s">
-        <v>317</v>
-      </c>
       <c r="F98" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G98" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
@@ -16848,22 +15971,22 @@
         <v>1300167</v>
       </c>
       <c r="B99" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C99" t="s">
-        <v>347</v>
-      </c>
-      <c r="D99">
+        <v>301</v>
+      </c>
+      <c r="D99" t="s">
+        <v>342</v>
+      </c>
+      <c r="E99">
         <v>1049</v>
       </c>
-      <c r="E99" t="s">
-        <v>317</v>
-      </c>
       <c r="F99" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="G99" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
@@ -16871,22 +15994,22 @@
         <v>1330926</v>
       </c>
       <c r="B100" t="s">
-        <v>350</v>
+        <v>312</v>
       </c>
       <c r="C100" t="s">
-        <v>351</v>
-      </c>
-      <c r="D100">
+        <v>345</v>
+      </c>
+      <c r="D100" t="s">
+        <v>346</v>
+      </c>
+      <c r="E100">
         <v>3499</v>
       </c>
-      <c r="E100" t="s">
-        <v>317</v>
-      </c>
       <c r="F100" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G100" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
@@ -16894,22 +16017,22 @@
         <v>1177472</v>
       </c>
       <c r="B101" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C101" t="s">
-        <v>354</v>
-      </c>
-      <c r="D101">
+        <v>297</v>
+      </c>
+      <c r="D101" t="s">
+        <v>349</v>
+      </c>
+      <c r="E101">
         <v>1849</v>
       </c>
-      <c r="E101" t="s">
-        <v>317</v>
-      </c>
       <c r="F101" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G101" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
@@ -16917,22 +16040,22 @@
         <v>1321575</v>
       </c>
       <c r="B102" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C102" t="s">
-        <v>357</v>
-      </c>
-      <c r="D102">
+        <v>301</v>
+      </c>
+      <c r="D102" t="s">
+        <v>352</v>
+      </c>
+      <c r="E102">
         <v>2999</v>
       </c>
-      <c r="E102" t="s">
-        <v>317</v>
-      </c>
       <c r="F102" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G102" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
@@ -16940,22 +16063,22 @@
         <v>1309821</v>
       </c>
       <c r="B103" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C103" t="s">
-        <v>360</v>
-      </c>
-      <c r="D103">
+        <v>297</v>
+      </c>
+      <c r="D103" t="s">
+        <v>355</v>
+      </c>
+      <c r="E103">
         <v>2999</v>
       </c>
-      <c r="E103" t="s">
-        <v>317</v>
-      </c>
       <c r="F103" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="G103" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
@@ -16963,22 +16086,22 @@
         <v>1331028</v>
       </c>
       <c r="B104" t="s">
-        <v>363</v>
+        <v>312</v>
       </c>
       <c r="C104" t="s">
-        <v>364</v>
-      </c>
-      <c r="D104">
+        <v>358</v>
+      </c>
+      <c r="D104" t="s">
+        <v>359</v>
+      </c>
+      <c r="E104">
         <v>1749</v>
       </c>
-      <c r="E104" t="s">
-        <v>317</v>
-      </c>
       <c r="F104" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G104" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
@@ -16986,22 +16109,22 @@
         <v>1309179</v>
       </c>
       <c r="B105" t="s">
-        <v>367</v>
+        <v>312</v>
       </c>
       <c r="C105" t="s">
-        <v>368</v>
-      </c>
-      <c r="D105">
+        <v>362</v>
+      </c>
+      <c r="D105" t="s">
+        <v>363</v>
+      </c>
+      <c r="E105">
         <v>5189</v>
       </c>
-      <c r="E105" t="s">
-        <v>317</v>
-      </c>
       <c r="F105" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G105" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
@@ -17009,22 +16132,22 @@
         <v>687373</v>
       </c>
       <c r="B106" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C106" t="s">
-        <v>371</v>
-      </c>
-      <c r="D106">
+        <v>301</v>
+      </c>
+      <c r="D106" t="s">
+        <v>366</v>
+      </c>
+      <c r="E106">
         <v>909</v>
       </c>
-      <c r="E106" t="s">
-        <v>317</v>
-      </c>
       <c r="F106" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="G106" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
@@ -17032,22 +16155,22 @@
         <v>1316744</v>
       </c>
       <c r="B107" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="C107" t="s">
-        <v>375</v>
-      </c>
-      <c r="D107">
+        <v>369</v>
+      </c>
+      <c r="D107" t="s">
+        <v>370</v>
+      </c>
+      <c r="E107">
         <v>269</v>
       </c>
-      <c r="E107" t="s">
-        <v>376</v>
-      </c>
       <c r="F107" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G107" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
@@ -17055,22 +16178,22 @@
         <v>338132</v>
       </c>
       <c r="B108" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C108" t="s">
-        <v>380</v>
-      </c>
-      <c r="D108">
+        <v>373</v>
+      </c>
+      <c r="D108" t="s">
+        <v>374</v>
+      </c>
+      <c r="E108">
         <v>69</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
+        <v>375</v>
+      </c>
+      <c r="G108" t="s">
         <v>376</v>
-      </c>
-      <c r="F108" t="s">
-        <v>381</v>
-      </c>
-      <c r="G108" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
@@ -17078,22 +16201,22 @@
         <v>1314060</v>
       </c>
       <c r="B109" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="C109" t="s">
-        <v>384</v>
-      </c>
-      <c r="D109">
+        <v>377</v>
+      </c>
+      <c r="D109" t="s">
+        <v>378</v>
+      </c>
+      <c r="E109">
         <v>99</v>
       </c>
-      <c r="E109" t="s">
-        <v>376</v>
-      </c>
       <c r="F109" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G109" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
@@ -17101,22 +16224,22 @@
         <v>1310434</v>
       </c>
       <c r="B110" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C110" t="s">
-        <v>389</v>
-      </c>
-      <c r="D110">
+        <v>382</v>
+      </c>
+      <c r="D110" t="s">
+        <v>383</v>
+      </c>
+      <c r="E110">
         <v>449</v>
       </c>
-      <c r="E110" t="s">
-        <v>376</v>
-      </c>
       <c r="F110" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G110" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
@@ -17124,22 +16247,22 @@
         <v>57307</v>
       </c>
       <c r="B111" t="s">
+        <v>402</v>
+      </c>
+      <c r="C111" t="s">
+        <v>381</v>
+      </c>
+      <c r="D111" t="s">
+        <v>386</v>
+      </c>
+      <c r="E111">
+        <v>79</v>
+      </c>
+      <c r="F111" t="s">
         <v>387</v>
       </c>
-      <c r="C111" t="s">
-        <v>392</v>
-      </c>
-      <c r="D111">
-        <v>79</v>
-      </c>
-      <c r="E111" t="s">
-        <v>376</v>
-      </c>
-      <c r="F111" t="s">
-        <v>393</v>
-      </c>
       <c r="G111" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
@@ -17147,22 +16270,22 @@
         <v>741760</v>
       </c>
       <c r="B112" t="s">
+        <v>402</v>
+      </c>
+      <c r="C112" t="s">
         <v>76</v>
       </c>
-      <c r="C112" t="s">
-        <v>395</v>
-      </c>
-      <c r="D112">
+      <c r="D112" t="s">
+        <v>389</v>
+      </c>
+      <c r="E112">
         <v>119</v>
       </c>
-      <c r="E112" t="s">
-        <v>376</v>
-      </c>
       <c r="F112" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="G112" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
@@ -17170,22 +16293,22 @@
         <v>1219218</v>
       </c>
       <c r="B113" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C113" t="s">
-        <v>399</v>
-      </c>
-      <c r="D113">
+        <v>392</v>
+      </c>
+      <c r="D113" t="s">
+        <v>393</v>
+      </c>
+      <c r="E113">
         <v>199</v>
       </c>
-      <c r="E113" t="s">
-        <v>376</v>
-      </c>
       <c r="F113" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="G113" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
@@ -17193,22 +16316,22 @@
         <v>741766</v>
       </c>
       <c r="B114" t="s">
+        <v>402</v>
+      </c>
+      <c r="C114" t="s">
         <v>76</v>
       </c>
-      <c r="C114" t="s">
-        <v>402</v>
-      </c>
-      <c r="D114">
+      <c r="D114" t="s">
+        <v>396</v>
+      </c>
+      <c r="E114">
         <v>89</v>
       </c>
-      <c r="E114" t="s">
-        <v>376</v>
-      </c>
       <c r="F114" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="G114" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
@@ -17216,22 +16339,22 @@
         <v>1301397</v>
       </c>
       <c r="B115" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C115" t="s">
-        <v>405</v>
-      </c>
-      <c r="D115">
+        <v>392</v>
+      </c>
+      <c r="D115" t="s">
+        <v>399</v>
+      </c>
+      <c r="E115">
         <v>349</v>
       </c>
-      <c r="E115" t="s">
-        <v>376</v>
-      </c>
       <c r="F115" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="G115" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
@@ -17239,22 +16362,22 @@
         <v>595144</v>
       </c>
       <c r="B116" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C116" t="s">
-        <v>410</v>
-      </c>
-      <c r="D116">
+        <v>403</v>
+      </c>
+      <c r="D116" t="s">
+        <v>404</v>
+      </c>
+      <c r="E116">
         <v>379</v>
       </c>
-      <c r="E116" t="s">
-        <v>408</v>
-      </c>
       <c r="F116" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="G116" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -17262,22 +16385,22 @@
         <v>1290024</v>
       </c>
       <c r="B117" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C117" t="s">
-        <v>413</v>
-      </c>
-      <c r="D117">
+        <v>392</v>
+      </c>
+      <c r="D117" t="s">
+        <v>407</v>
+      </c>
+      <c r="E117">
         <v>249</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>408</v>
       </c>
-      <c r="F117" t="s">
-        <v>414</v>
-      </c>
       <c r="G117" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
@@ -17285,22 +16408,22 @@
         <v>719865</v>
       </c>
       <c r="B118" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C118" t="s">
-        <v>416</v>
-      </c>
-      <c r="D118">
+        <v>381</v>
+      </c>
+      <c r="D118" t="s">
+        <v>410</v>
+      </c>
+      <c r="E118">
         <v>279</v>
       </c>
-      <c r="E118" t="s">
-        <v>408</v>
-      </c>
       <c r="F118" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="G118" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
@@ -17308,22 +16431,22 @@
         <v>1290020</v>
       </c>
       <c r="B119" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C119" t="s">
-        <v>419</v>
-      </c>
-      <c r="D119">
+        <v>392</v>
+      </c>
+      <c r="D119" t="s">
+        <v>413</v>
+      </c>
+      <c r="E119">
         <v>299</v>
       </c>
-      <c r="E119" t="s">
-        <v>408</v>
-      </c>
       <c r="F119" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G119" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
@@ -17331,22 +16454,22 @@
         <v>1310435</v>
       </c>
       <c r="B120" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C120" t="s">
-        <v>422</v>
-      </c>
-      <c r="D120">
+        <v>382</v>
+      </c>
+      <c r="D120" t="s">
+        <v>416</v>
+      </c>
+      <c r="E120">
         <v>699</v>
       </c>
-      <c r="E120" t="s">
-        <v>408</v>
-      </c>
       <c r="F120" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G120" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
@@ -17354,22 +16477,22 @@
         <v>1069873</v>
       </c>
       <c r="B121" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="C121" t="s">
-        <v>426</v>
-      </c>
-      <c r="D121">
+        <v>419</v>
+      </c>
+      <c r="D121" t="s">
+        <v>420</v>
+      </c>
+      <c r="E121">
         <v>429</v>
       </c>
-      <c r="E121" t="s">
-        <v>408</v>
-      </c>
       <c r="F121" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G121" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
@@ -17377,22 +16500,22 @@
         <v>1056646</v>
       </c>
       <c r="B122" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="C122" t="s">
-        <v>430</v>
-      </c>
-      <c r="D122">
+        <v>423</v>
+      </c>
+      <c r="D122" t="s">
+        <v>424</v>
+      </c>
+      <c r="E122">
         <v>799</v>
       </c>
-      <c r="E122" t="s">
-        <v>408</v>
-      </c>
       <c r="F122" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="G122" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
@@ -17400,22 +16523,22 @@
         <v>679823</v>
       </c>
       <c r="B123" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C123" t="s">
-        <v>433</v>
-      </c>
-      <c r="D123">
+        <v>373</v>
+      </c>
+      <c r="D123" t="s">
+        <v>427</v>
+      </c>
+      <c r="E123">
         <v>349</v>
       </c>
-      <c r="E123" t="s">
-        <v>408</v>
-      </c>
       <c r="F123" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="G123" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
@@ -17423,22 +16546,22 @@
         <v>1066515</v>
       </c>
       <c r="B124" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="C124" t="s">
-        <v>437</v>
-      </c>
-      <c r="D124">
+        <v>430</v>
+      </c>
+      <c r="D124" t="s">
+        <v>431</v>
+      </c>
+      <c r="E124">
         <v>299</v>
       </c>
-      <c r="E124" t="s">
-        <v>408</v>
-      </c>
       <c r="F124" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="G124" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
@@ -17446,22 +16569,22 @@
         <v>1266238</v>
       </c>
       <c r="B125" t="s">
+        <v>402</v>
+      </c>
+      <c r="C125" t="s">
         <v>76</v>
       </c>
-      <c r="C125" t="s">
-        <v>440</v>
-      </c>
-      <c r="D125">
+      <c r="D125" t="s">
+        <v>434</v>
+      </c>
+      <c r="E125">
         <v>259</v>
       </c>
-      <c r="E125" t="s">
-        <v>408</v>
-      </c>
       <c r="F125" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="G125" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -17469,22 +16592,22 @@
         <v>148477</v>
       </c>
       <c r="B126" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C126" t="s">
-        <v>443</v>
-      </c>
-      <c r="D126">
+        <v>381</v>
+      </c>
+      <c r="D126" t="s">
+        <v>437</v>
+      </c>
+      <c r="E126">
         <v>139</v>
       </c>
-      <c r="E126" t="s">
-        <v>408</v>
-      </c>
       <c r="F126" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="G126" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
@@ -17492,22 +16615,22 @@
         <v>1331550</v>
       </c>
       <c r="B127" t="s">
-        <v>379</v>
+        <v>875</v>
       </c>
       <c r="C127" t="s">
-        <v>446</v>
-      </c>
-      <c r="D127">
+        <v>373</v>
+      </c>
+      <c r="D127" t="s">
+        <v>440</v>
+      </c>
+      <c r="E127">
         <v>2699</v>
       </c>
-      <c r="E127" t="s">
-        <v>447</v>
-      </c>
       <c r="F127" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="G127" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
@@ -17515,22 +16638,22 @@
         <v>1307417</v>
       </c>
       <c r="B128" t="s">
-        <v>450</v>
+        <v>875</v>
       </c>
       <c r="C128" t="s">
-        <v>451</v>
-      </c>
-      <c r="D128">
+        <v>443</v>
+      </c>
+      <c r="D128" t="s">
+        <v>444</v>
+      </c>
+      <c r="E128">
         <v>2499</v>
       </c>
-      <c r="E128" t="s">
-        <v>447</v>
-      </c>
       <c r="F128" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="G128" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -17538,22 +16661,22 @@
         <v>1328947</v>
       </c>
       <c r="B129" t="s">
-        <v>450</v>
+        <v>875</v>
       </c>
       <c r="C129" t="s">
-        <v>454</v>
-      </c>
-      <c r="D129">
+        <v>443</v>
+      </c>
+      <c r="D129" t="s">
+        <v>447</v>
+      </c>
+      <c r="E129">
         <v>2899</v>
       </c>
-      <c r="E129" t="s">
-        <v>447</v>
-      </c>
       <c r="F129" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="G129" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -17561,22 +16684,22 @@
         <v>1301192</v>
       </c>
       <c r="B130" t="s">
-        <v>457</v>
+        <v>875</v>
       </c>
       <c r="C130" t="s">
-        <v>458</v>
-      </c>
-      <c r="D130">
+        <v>450</v>
+      </c>
+      <c r="D130" t="s">
+        <v>451</v>
+      </c>
+      <c r="E130">
         <v>3249</v>
       </c>
-      <c r="E130" t="s">
-        <v>447</v>
-      </c>
       <c r="F130" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="G130" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -17584,22 +16707,22 @@
         <v>1297981</v>
       </c>
       <c r="B131" t="s">
-        <v>457</v>
+        <v>875</v>
       </c>
       <c r="C131" t="s">
-        <v>461</v>
-      </c>
-      <c r="D131">
+        <v>450</v>
+      </c>
+      <c r="D131" t="s">
+        <v>454</v>
+      </c>
+      <c r="E131">
         <v>2549</v>
       </c>
-      <c r="E131" t="s">
-        <v>447</v>
-      </c>
       <c r="F131" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="G131" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -17607,3015 +16730,2970 @@
         <v>1241536</v>
       </c>
       <c r="B132" t="s">
-        <v>450</v>
+        <v>875</v>
       </c>
       <c r="C132" t="s">
-        <v>464</v>
-      </c>
-      <c r="D132">
+        <v>443</v>
+      </c>
+      <c r="D132" t="s">
+        <v>457</v>
+      </c>
+      <c r="E132">
         <v>4799</v>
       </c>
-      <c r="E132" t="s">
-        <v>465</v>
-      </c>
       <c r="F132" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="G132" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>1129603</v>
+        <v>1323373</v>
       </c>
       <c r="B133" t="s">
-        <v>468</v>
+        <v>875</v>
       </c>
       <c r="C133" t="s">
-        <v>469</v>
-      </c>
-      <c r="D133">
-        <v>1299</v>
-      </c>
-      <c r="E133" t="s">
-        <v>465</v>
+        <v>373</v>
+      </c>
+      <c r="D133" t="s">
+        <v>461</v>
+      </c>
+      <c r="E133">
+        <v>2499</v>
       </c>
       <c r="F133" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="G133" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>1323373</v>
+        <v>1271993</v>
       </c>
       <c r="B134" t="s">
-        <v>379</v>
+        <v>875</v>
       </c>
       <c r="C134" t="s">
-        <v>472</v>
-      </c>
-      <c r="D134">
-        <v>2499</v>
-      </c>
-      <c r="E134" t="s">
+        <v>161</v>
+      </c>
+      <c r="D134" t="s">
+        <v>464</v>
+      </c>
+      <c r="E134">
+        <v>2699</v>
+      </c>
+      <c r="F134" t="s">
         <v>465</v>
       </c>
-      <c r="F134" t="s">
-        <v>473</v>
-      </c>
       <c r="G134" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>1271993</v>
+        <v>1292135</v>
       </c>
       <c r="B135" t="s">
-        <v>163</v>
+        <v>875</v>
       </c>
       <c r="C135" t="s">
-        <v>475</v>
-      </c>
-      <c r="D135">
-        <v>2699</v>
-      </c>
-      <c r="E135" t="s">
-        <v>465</v>
+        <v>373</v>
+      </c>
+      <c r="D135" t="s">
+        <v>467</v>
+      </c>
+      <c r="E135">
+        <v>1999</v>
       </c>
       <c r="F135" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="G135" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>1292135</v>
+        <v>1292431</v>
       </c>
       <c r="B136" t="s">
-        <v>379</v>
+        <v>875</v>
       </c>
       <c r="C136" t="s">
-        <v>478</v>
-      </c>
-      <c r="D136">
-        <v>1999</v>
-      </c>
-      <c r="E136" t="s">
-        <v>465</v>
+        <v>40</v>
+      </c>
+      <c r="D136" t="s">
+        <v>470</v>
+      </c>
+      <c r="E136">
+        <v>3699</v>
       </c>
       <c r="F136" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="G136" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>1292431</v>
+        <v>1281089</v>
       </c>
       <c r="B137" t="s">
-        <v>40</v>
+        <v>875</v>
       </c>
       <c r="C137" t="s">
-        <v>481</v>
-      </c>
-      <c r="D137">
-        <v>3699</v>
-      </c>
-      <c r="E137" t="s">
-        <v>465</v>
+        <v>443</v>
+      </c>
+      <c r="D137" t="s">
+        <v>473</v>
+      </c>
+      <c r="E137">
+        <v>2199</v>
       </c>
       <c r="F137" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="G137" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>1281089</v>
+        <v>1312203</v>
       </c>
       <c r="B138" t="s">
+        <v>875</v>
+      </c>
+      <c r="C138" t="s">
         <v>450</v>
       </c>
-      <c r="C138" t="s">
-        <v>484</v>
-      </c>
-      <c r="D138">
-        <v>2199</v>
-      </c>
-      <c r="E138" t="s">
-        <v>465</v>
+      <c r="D138" t="s">
+        <v>476</v>
+      </c>
+      <c r="E138">
+        <v>2799</v>
       </c>
       <c r="F138" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="G138" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>1312203</v>
+        <v>1299517</v>
       </c>
       <c r="B139" t="s">
-        <v>457</v>
+        <v>875</v>
       </c>
       <c r="C139" t="s">
-        <v>487</v>
-      </c>
-      <c r="D139">
-        <v>2799</v>
-      </c>
-      <c r="E139" t="s">
-        <v>465</v>
+        <v>450</v>
+      </c>
+      <c r="D139" t="s">
+        <v>479</v>
+      </c>
+      <c r="E139">
+        <v>3499</v>
       </c>
       <c r="F139" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G139" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140">
-        <v>1288275</v>
+        <v>1298239</v>
       </c>
       <c r="B140" t="s">
+        <v>875</v>
+      </c>
+      <c r="C140" t="s">
         <v>450</v>
       </c>
-      <c r="C140" t="s">
-        <v>490</v>
-      </c>
-      <c r="D140">
-        <v>3549</v>
-      </c>
-      <c r="E140" t="s">
-        <v>465</v>
+      <c r="D140" t="s">
+        <v>482</v>
+      </c>
+      <c r="E140">
+        <v>2499</v>
       </c>
       <c r="F140" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="G140" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>1299517</v>
+        <v>1222789</v>
       </c>
       <c r="B141" t="s">
-        <v>457</v>
+        <v>875</v>
       </c>
       <c r="C141" t="s">
-        <v>493</v>
-      </c>
-      <c r="D141">
-        <v>3499</v>
-      </c>
-      <c r="E141" t="s">
-        <v>465</v>
+        <v>443</v>
+      </c>
+      <c r="D141" t="s">
+        <v>485</v>
+      </c>
+      <c r="E141">
+        <v>3399</v>
       </c>
       <c r="F141" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="G141" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>1298239</v>
+        <v>1271981</v>
       </c>
       <c r="B142" t="s">
-        <v>457</v>
+        <v>875</v>
       </c>
       <c r="C142" t="s">
-        <v>496</v>
-      </c>
-      <c r="D142">
-        <v>2499</v>
-      </c>
-      <c r="E142" t="s">
-        <v>465</v>
+        <v>161</v>
+      </c>
+      <c r="D142" t="s">
+        <v>488</v>
+      </c>
+      <c r="E142">
+        <v>2999</v>
       </c>
       <c r="F142" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="G142" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>1222789</v>
+        <v>1317567</v>
       </c>
       <c r="B143" t="s">
-        <v>450</v>
+        <v>875</v>
       </c>
       <c r="C143" t="s">
-        <v>499</v>
-      </c>
-      <c r="D143">
-        <v>3399</v>
-      </c>
-      <c r="E143" t="s">
-        <v>465</v>
+        <v>443</v>
+      </c>
+      <c r="D143" t="s">
+        <v>491</v>
+      </c>
+      <c r="E143">
+        <v>2899</v>
       </c>
       <c r="F143" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="G143" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>1271981</v>
+        <v>1273586</v>
       </c>
       <c r="B144" t="s">
-        <v>163</v>
+        <v>875</v>
       </c>
       <c r="C144" t="s">
-        <v>502</v>
-      </c>
-      <c r="D144">
-        <v>2999</v>
-      </c>
-      <c r="E144" t="s">
-        <v>465</v>
+        <v>373</v>
+      </c>
+      <c r="D144" t="s">
+        <v>494</v>
+      </c>
+      <c r="E144">
+        <v>2379</v>
       </c>
       <c r="F144" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="G144" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>1317567</v>
+        <v>1296932</v>
       </c>
       <c r="B145" t="s">
-        <v>450</v>
+        <v>875</v>
       </c>
       <c r="C145" t="s">
-        <v>505</v>
-      </c>
-      <c r="D145">
-        <v>2899</v>
-      </c>
-      <c r="E145" t="s">
-        <v>465</v>
+        <v>322</v>
+      </c>
+      <c r="D145" t="s">
+        <v>497</v>
+      </c>
+      <c r="E145">
+        <v>4579</v>
       </c>
       <c r="F145" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="G145" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146">
-        <v>1273586</v>
+        <v>1316334</v>
       </c>
       <c r="B146" t="s">
-        <v>379</v>
+        <v>875</v>
       </c>
       <c r="C146" t="s">
-        <v>508</v>
-      </c>
-      <c r="D146">
-        <v>2379</v>
-      </c>
-      <c r="E146" t="s">
-        <v>465</v>
+        <v>297</v>
+      </c>
+      <c r="D146" t="s">
+        <v>500</v>
+      </c>
+      <c r="E146">
+        <v>3199</v>
       </c>
       <c r="F146" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="G146" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>1296932</v>
+        <v>1276733</v>
       </c>
       <c r="B147" t="s">
-        <v>327</v>
+        <v>509</v>
       </c>
       <c r="C147" t="s">
-        <v>511</v>
-      </c>
-      <c r="D147">
-        <v>4579</v>
-      </c>
-      <c r="E147" t="s">
-        <v>465</v>
+        <v>503</v>
+      </c>
+      <c r="D147" t="s">
+        <v>504</v>
+      </c>
+      <c r="E147">
+        <v>869</v>
       </c>
       <c r="F147" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="G147" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>1316334</v>
+        <v>1228926</v>
       </c>
       <c r="B148" t="s">
-        <v>302</v>
+        <v>509</v>
       </c>
       <c r="C148" t="s">
-        <v>514</v>
-      </c>
-      <c r="D148">
-        <v>3199</v>
-      </c>
-      <c r="E148" t="s">
-        <v>465</v>
+        <v>507</v>
+      </c>
+      <c r="D148" t="s">
+        <v>508</v>
+      </c>
+      <c r="E148">
+        <v>399</v>
       </c>
       <c r="F148" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="G148" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>1276733</v>
+        <v>1241603</v>
       </c>
       <c r="B149" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C149" t="s">
-        <v>518</v>
-      </c>
-      <c r="D149">
-        <v>869</v>
-      </c>
-      <c r="E149" t="s">
-        <v>519</v>
+        <v>161</v>
+      </c>
+      <c r="D149" t="s">
+        <v>512</v>
+      </c>
+      <c r="E149">
+        <v>769</v>
       </c>
       <c r="F149" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="G149" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>1228926</v>
+        <v>1247744</v>
       </c>
       <c r="B150" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="C150" t="s">
-        <v>523</v>
-      </c>
-      <c r="D150">
-        <v>399</v>
-      </c>
-      <c r="E150" t="s">
-        <v>524</v>
+        <v>7</v>
+      </c>
+      <c r="D150" t="s">
+        <v>515</v>
+      </c>
+      <c r="E150">
+        <v>829</v>
       </c>
       <c r="F150" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="G150" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>1241603</v>
+        <v>1123913</v>
       </c>
       <c r="B151" t="s">
-        <v>163</v>
+        <v>509</v>
       </c>
       <c r="C151" t="s">
-        <v>527</v>
-      </c>
-      <c r="D151">
-        <v>769</v>
-      </c>
-      <c r="E151" t="s">
-        <v>524</v>
+        <v>161</v>
+      </c>
+      <c r="D151" t="s">
+        <v>518</v>
+      </c>
+      <c r="E151">
+        <v>649</v>
       </c>
       <c r="F151" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="G151" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152">
-        <v>1247744</v>
+        <v>1210799</v>
       </c>
       <c r="B152" t="s">
+        <v>509</v>
+      </c>
+      <c r="C152" t="s">
         <v>7</v>
       </c>
-      <c r="C152" t="s">
-        <v>530</v>
-      </c>
-      <c r="D152">
-        <v>829</v>
-      </c>
-      <c r="E152" t="s">
-        <v>524</v>
+      <c r="D152" t="s">
+        <v>521</v>
+      </c>
+      <c r="E152">
+        <v>699</v>
       </c>
       <c r="F152" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="G152" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>1123913</v>
+        <v>1109993</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>509</v>
       </c>
       <c r="C153" t="s">
-        <v>533</v>
-      </c>
-      <c r="D153">
-        <v>649</v>
-      </c>
-      <c r="E153" t="s">
+        <v>297</v>
+      </c>
+      <c r="D153" t="s">
         <v>524</v>
       </c>
+      <c r="E153">
+        <v>529</v>
+      </c>
       <c r="F153" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="G153" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>1210799</v>
+        <v>1265660</v>
       </c>
       <c r="B154" t="s">
+        <v>509</v>
+      </c>
+      <c r="C154" t="s">
         <v>7</v>
       </c>
-      <c r="C154" t="s">
-        <v>536</v>
-      </c>
-      <c r="D154">
-        <v>699</v>
-      </c>
-      <c r="E154" t="s">
-        <v>524</v>
+      <c r="D154" t="s">
+        <v>527</v>
+      </c>
+      <c r="E154">
+        <v>4899</v>
       </c>
       <c r="F154" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="G154" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>1109993</v>
+        <v>1222094</v>
       </c>
       <c r="B155" t="s">
-        <v>302</v>
+        <v>509</v>
       </c>
       <c r="C155" t="s">
-        <v>539</v>
-      </c>
-      <c r="D155">
-        <v>529</v>
-      </c>
-      <c r="E155" t="s">
-        <v>524</v>
+        <v>161</v>
+      </c>
+      <c r="D155" t="s">
+        <v>530</v>
+      </c>
+      <c r="E155">
+        <v>399</v>
       </c>
       <c r="F155" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="G155" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>1265660</v>
+        <v>1328816</v>
       </c>
       <c r="B156" t="s">
+        <v>509</v>
+      </c>
+      <c r="C156" t="s">
         <v>7</v>
       </c>
-      <c r="C156" t="s">
-        <v>542</v>
-      </c>
-      <c r="D156">
-        <v>4899</v>
-      </c>
-      <c r="E156" t="s">
-        <v>524</v>
+      <c r="D156" t="s">
+        <v>533</v>
+      </c>
+      <c r="E156">
+        <v>4399</v>
       </c>
       <c r="F156" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="G156" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>1222094</v>
+        <v>1212512</v>
       </c>
       <c r="B157" t="s">
-        <v>163</v>
+        <v>509</v>
       </c>
       <c r="C157" t="s">
-        <v>545</v>
-      </c>
-      <c r="D157">
-        <v>399</v>
-      </c>
-      <c r="E157" t="s">
-        <v>524</v>
+        <v>161</v>
+      </c>
+      <c r="D157" t="s">
+        <v>536</v>
+      </c>
+      <c r="E157">
+        <v>449</v>
       </c>
       <c r="F157" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="G157" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>1328816</v>
+        <v>1328818</v>
       </c>
       <c r="B158" t="s">
+        <v>509</v>
+      </c>
+      <c r="C158" t="s">
         <v>7</v>
       </c>
-      <c r="C158" t="s">
-        <v>548</v>
-      </c>
-      <c r="D158">
-        <v>4399</v>
-      </c>
-      <c r="E158" t="s">
-        <v>524</v>
+      <c r="D158" t="s">
+        <v>539</v>
+      </c>
+      <c r="E158">
+        <v>3999</v>
       </c>
       <c r="F158" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="G158" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>1212512</v>
+        <v>1228812</v>
       </c>
       <c r="B159" t="s">
-        <v>163</v>
+        <v>509</v>
       </c>
       <c r="C159" t="s">
-        <v>551</v>
-      </c>
-      <c r="D159">
-        <v>449</v>
-      </c>
-      <c r="E159" t="s">
-        <v>524</v>
+        <v>542</v>
+      </c>
+      <c r="D159" t="s">
+        <v>543</v>
+      </c>
+      <c r="E159">
+        <v>319</v>
       </c>
       <c r="F159" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="G159" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>1328818</v>
+        <v>1160222</v>
       </c>
       <c r="B160" t="s">
-        <v>7</v>
+        <v>509</v>
       </c>
       <c r="C160" t="s">
-        <v>554</v>
-      </c>
-      <c r="D160">
-        <v>3999</v>
-      </c>
-      <c r="E160" t="s">
-        <v>524</v>
+        <v>373</v>
+      </c>
+      <c r="D160" t="s">
+        <v>546</v>
+      </c>
+      <c r="E160">
+        <v>999</v>
       </c>
       <c r="F160" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="G160" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>1228812</v>
+        <v>1092721</v>
       </c>
       <c r="B161" t="s">
-        <v>557</v>
+        <v>509</v>
       </c>
       <c r="C161" t="s">
-        <v>558</v>
-      </c>
-      <c r="D161">
-        <v>319</v>
-      </c>
-      <c r="E161" t="s">
-        <v>524</v>
+        <v>7</v>
+      </c>
+      <c r="D161" t="s">
+        <v>549</v>
+      </c>
+      <c r="E161">
+        <v>1849</v>
       </c>
       <c r="F161" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="G161" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>1160222</v>
+        <v>1333834</v>
       </c>
       <c r="B162" t="s">
-        <v>379</v>
+        <v>509</v>
       </c>
       <c r="C162" t="s">
-        <v>561</v>
-      </c>
-      <c r="D162">
-        <v>999</v>
-      </c>
-      <c r="E162" t="s">
-        <v>524</v>
+        <v>503</v>
+      </c>
+      <c r="D162" t="s">
+        <v>552</v>
+      </c>
+      <c r="E162">
+        <v>699</v>
       </c>
       <c r="F162" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="G162" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>1092721</v>
+        <v>1266587</v>
       </c>
       <c r="B163" t="s">
-        <v>7</v>
+        <v>509</v>
       </c>
       <c r="C163" t="s">
-        <v>564</v>
-      </c>
-      <c r="D163">
-        <v>1849</v>
-      </c>
-      <c r="E163" t="s">
-        <v>524</v>
+        <v>555</v>
+      </c>
+      <c r="D163" t="s">
+        <v>556</v>
+      </c>
+      <c r="E163">
+        <v>599</v>
       </c>
       <c r="F163" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="G163" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>1333834</v>
+        <v>1297644</v>
       </c>
       <c r="B164" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C164" t="s">
-        <v>567</v>
-      </c>
-      <c r="D164">
-        <v>699</v>
-      </c>
-      <c r="E164" t="s">
-        <v>524</v>
+        <v>503</v>
+      </c>
+      <c r="D164" t="s">
+        <v>559</v>
+      </c>
+      <c r="E164">
+        <v>859</v>
       </c>
       <c r="F164" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="G164" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>1266587</v>
+        <v>1319221</v>
       </c>
       <c r="B165" t="s">
-        <v>570</v>
+        <v>509</v>
       </c>
       <c r="C165" t="s">
-        <v>571</v>
-      </c>
-      <c r="D165">
-        <v>599</v>
-      </c>
-      <c r="E165" t="s">
-        <v>524</v>
+        <v>161</v>
+      </c>
+      <c r="D165" t="s">
+        <v>562</v>
+      </c>
+      <c r="E165">
+        <v>649</v>
       </c>
       <c r="F165" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="G165" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>1297644</v>
+        <v>1276730</v>
       </c>
       <c r="B166" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C166" t="s">
-        <v>574</v>
-      </c>
-      <c r="D166">
-        <v>859</v>
-      </c>
-      <c r="E166" t="s">
-        <v>524</v>
+        <v>503</v>
+      </c>
+      <c r="D166" t="s">
+        <v>565</v>
+      </c>
+      <c r="E166">
+        <v>579</v>
       </c>
       <c r="F166" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="G166" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>1319221</v>
+        <v>1328819</v>
       </c>
       <c r="B167" t="s">
-        <v>163</v>
+        <v>509</v>
       </c>
       <c r="C167" t="s">
-        <v>577</v>
-      </c>
-      <c r="D167">
-        <v>649</v>
-      </c>
-      <c r="E167" t="s">
-        <v>524</v>
+        <v>7</v>
+      </c>
+      <c r="D167" t="s">
+        <v>568</v>
+      </c>
+      <c r="E167">
+        <v>3799</v>
       </c>
       <c r="F167" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="G167" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>1276730</v>
+        <v>657424</v>
       </c>
       <c r="B168" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="C168" t="s">
-        <v>580</v>
-      </c>
-      <c r="D168">
-        <v>579</v>
-      </c>
-      <c r="E168" t="s">
-        <v>524</v>
+        <v>297</v>
+      </c>
+      <c r="D168" t="s">
+        <v>571</v>
+      </c>
+      <c r="E168">
+        <v>779</v>
       </c>
       <c r="F168" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="G168" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169">
-        <v>1328819</v>
+        <v>1056271</v>
       </c>
       <c r="B169" t="s">
+        <v>509</v>
+      </c>
+      <c r="C169" t="s">
         <v>7</v>
       </c>
-      <c r="C169" t="s">
-        <v>583</v>
-      </c>
-      <c r="D169">
-        <v>3799</v>
-      </c>
-      <c r="E169" t="s">
-        <v>524</v>
+      <c r="D169" t="s">
+        <v>574</v>
+      </c>
+      <c r="E169">
+        <v>699</v>
       </c>
       <c r="F169" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="G169" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>657424</v>
+        <v>1145833</v>
       </c>
       <c r="B170" t="s">
-        <v>302</v>
+        <v>609</v>
       </c>
       <c r="C170" t="s">
-        <v>586</v>
-      </c>
-      <c r="D170">
-        <v>779</v>
-      </c>
-      <c r="E170" t="s">
-        <v>524</v>
+        <v>381</v>
+      </c>
+      <c r="D170" t="s">
+        <v>577</v>
+      </c>
+      <c r="E170">
+        <v>339</v>
       </c>
       <c r="F170" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="G170" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>1056271</v>
+        <v>1230134</v>
       </c>
       <c r="B171" t="s">
-        <v>7</v>
+        <v>609</v>
       </c>
       <c r="C171" t="s">
-        <v>589</v>
-      </c>
-      <c r="D171">
-        <v>699</v>
-      </c>
-      <c r="E171" t="s">
-        <v>524</v>
+        <v>76</v>
+      </c>
+      <c r="D171" t="s">
+        <v>580</v>
+      </c>
+      <c r="E171">
+        <v>99</v>
       </c>
       <c r="F171" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="G171" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172">
-        <v>1145833</v>
+        <v>1294102</v>
       </c>
       <c r="B172" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C172" t="s">
-        <v>592</v>
-      </c>
-      <c r="D172">
-        <v>339</v>
-      </c>
-      <c r="E172" t="s">
-        <v>593</v>
+        <v>382</v>
+      </c>
+      <c r="D172" t="s">
+        <v>583</v>
+      </c>
+      <c r="E172">
+        <v>249</v>
       </c>
       <c r="F172" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G172" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173">
-        <v>1230134</v>
+        <v>713778</v>
       </c>
       <c r="B173" t="s">
-        <v>76</v>
+        <v>609</v>
       </c>
       <c r="C173" t="s">
-        <v>596</v>
-      </c>
-      <c r="D173">
-        <v>99</v>
-      </c>
-      <c r="E173" t="s">
-        <v>593</v>
+        <v>419</v>
+      </c>
+      <c r="D173" t="s">
+        <v>586</v>
+      </c>
+      <c r="E173">
+        <v>349</v>
       </c>
       <c r="F173" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="G173" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174">
-        <v>1294102</v>
+        <v>615023</v>
       </c>
       <c r="B174" t="s">
-        <v>388</v>
+        <v>609</v>
       </c>
       <c r="C174" t="s">
-        <v>599</v>
-      </c>
-      <c r="D174">
-        <v>249</v>
-      </c>
-      <c r="E174" t="s">
-        <v>593</v>
+        <v>381</v>
+      </c>
+      <c r="D174" t="s">
+        <v>589</v>
+      </c>
+      <c r="E174">
+        <v>58</v>
       </c>
       <c r="F174" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="G174" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175">
-        <v>713778</v>
+        <v>434026</v>
       </c>
       <c r="B175" t="s">
-        <v>425</v>
+        <v>609</v>
       </c>
       <c r="C175" t="s">
-        <v>602</v>
-      </c>
-      <c r="D175">
-        <v>349</v>
-      </c>
-      <c r="E175" t="s">
+        <v>381</v>
+      </c>
+      <c r="D175" t="s">
+        <v>592</v>
+      </c>
+      <c r="E175">
+        <v>229</v>
+      </c>
+      <c r="F175" t="s">
         <v>593</v>
       </c>
-      <c r="F175" t="s">
-        <v>603</v>
-      </c>
       <c r="G175" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176">
-        <v>615023</v>
+        <v>652970</v>
       </c>
       <c r="B176" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C176" t="s">
-        <v>605</v>
-      </c>
-      <c r="D176">
-        <v>58</v>
-      </c>
-      <c r="E176" t="s">
-        <v>593</v>
+        <v>419</v>
+      </c>
+      <c r="D176" t="s">
+        <v>595</v>
+      </c>
+      <c r="E176">
+        <v>209</v>
       </c>
       <c r="F176" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="G176" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177">
-        <v>434026</v>
+        <v>1258807</v>
       </c>
       <c r="B177" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C177" t="s">
-        <v>608</v>
-      </c>
-      <c r="D177">
-        <v>229</v>
-      </c>
-      <c r="E177" t="s">
-        <v>593</v>
+        <v>598</v>
+      </c>
+      <c r="D177" t="s">
+        <v>599</v>
+      </c>
+      <c r="E177">
+        <v>399</v>
       </c>
       <c r="F177" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="G177" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178">
-        <v>652970</v>
+        <v>1315345</v>
       </c>
       <c r="B178" t="s">
-        <v>425</v>
+        <v>609</v>
       </c>
       <c r="C178" t="s">
-        <v>611</v>
-      </c>
-      <c r="D178">
-        <v>209</v>
-      </c>
-      <c r="E178" t="s">
-        <v>593</v>
+        <v>430</v>
+      </c>
+      <c r="D178" t="s">
+        <v>602</v>
+      </c>
+      <c r="E178">
+        <v>295</v>
       </c>
       <c r="F178" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="G178" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179">
-        <v>1258807</v>
+        <v>1145831</v>
       </c>
       <c r="B179" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C179" t="s">
-        <v>615</v>
-      </c>
-      <c r="D179">
-        <v>399</v>
-      </c>
-      <c r="E179" t="s">
-        <v>593</v>
+        <v>381</v>
+      </c>
+      <c r="D179" t="s">
+        <v>605</v>
+      </c>
+      <c r="E179">
+        <v>99</v>
       </c>
       <c r="F179" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
       <c r="G179" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180">
-        <v>1315345</v>
+        <v>1294942</v>
       </c>
       <c r="B180" t="s">
-        <v>436</v>
+        <v>609</v>
       </c>
       <c r="C180" t="s">
-        <v>618</v>
-      </c>
-      <c r="D180">
-        <v>295</v>
-      </c>
-      <c r="E180" t="s">
-        <v>593</v>
+        <v>80</v>
+      </c>
+      <c r="D180" t="s">
+        <v>608</v>
+      </c>
+      <c r="E180">
+        <v>89</v>
       </c>
       <c r="F180" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="G180" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181">
-        <v>1145831</v>
+        <v>1078841</v>
       </c>
       <c r="B181" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C181" t="s">
-        <v>621</v>
-      </c>
-      <c r="D181">
-        <v>99</v>
-      </c>
-      <c r="E181" t="s">
-        <v>593</v>
+        <v>598</v>
+      </c>
+      <c r="D181" t="s">
+        <v>612</v>
+      </c>
+      <c r="E181">
+        <v>199</v>
       </c>
       <c r="F181" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="G181" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182">
-        <v>1294942</v>
+        <v>1172768</v>
       </c>
       <c r="B182" t="s">
-        <v>81</v>
+        <v>609</v>
       </c>
       <c r="C182" t="s">
-        <v>624</v>
-      </c>
-      <c r="D182">
-        <v>89</v>
-      </c>
-      <c r="E182" t="s">
-        <v>625</v>
+        <v>381</v>
+      </c>
+      <c r="D182" t="s">
+        <v>615</v>
+      </c>
+      <c r="E182">
+        <v>569</v>
       </c>
       <c r="F182" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="G182" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183">
-        <v>1078841</v>
+        <v>1219968</v>
       </c>
       <c r="B183" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C183" t="s">
-        <v>628</v>
-      </c>
-      <c r="D183">
-        <v>199</v>
-      </c>
-      <c r="E183" t="s">
-        <v>625</v>
+        <v>618</v>
+      </c>
+      <c r="D183" t="s">
+        <v>619</v>
+      </c>
+      <c r="E183">
+        <v>99</v>
       </c>
       <c r="F183" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="G183" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184">
-        <v>1172768</v>
+        <v>475517</v>
       </c>
       <c r="B184" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C184" t="s">
-        <v>631</v>
-      </c>
-      <c r="D184">
-        <v>569</v>
-      </c>
-      <c r="E184" t="s">
-        <v>625</v>
+        <v>381</v>
+      </c>
+      <c r="D184" t="s">
+        <v>622</v>
+      </c>
+      <c r="E184">
+        <v>399</v>
       </c>
       <c r="F184" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="G184" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185">
-        <v>1219968</v>
+        <v>1294120</v>
       </c>
       <c r="B185" t="s">
-        <v>634</v>
+        <v>609</v>
       </c>
       <c r="C185" t="s">
-        <v>635</v>
-      </c>
-      <c r="D185">
-        <v>99</v>
-      </c>
-      <c r="E185" t="s">
+        <v>382</v>
+      </c>
+      <c r="D185" t="s">
         <v>625</v>
       </c>
+      <c r="E185">
+        <v>349</v>
+      </c>
       <c r="F185" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="G185" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186">
-        <v>475517</v>
+        <v>574603</v>
       </c>
       <c r="B186" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C186" t="s">
-        <v>638</v>
-      </c>
-      <c r="D186">
-        <v>399</v>
-      </c>
-      <c r="E186" t="s">
-        <v>625</v>
+        <v>381</v>
+      </c>
+      <c r="D186" t="s">
+        <v>628</v>
+      </c>
+      <c r="E186">
+        <v>119</v>
       </c>
       <c r="F186" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="G186" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187">
-        <v>1294120</v>
+        <v>679990</v>
       </c>
       <c r="B187" t="s">
-        <v>388</v>
+        <v>609</v>
       </c>
       <c r="C187" t="s">
-        <v>641</v>
-      </c>
-      <c r="D187">
-        <v>349</v>
-      </c>
-      <c r="E187" t="s">
-        <v>625</v>
+        <v>430</v>
+      </c>
+      <c r="D187" t="s">
+        <v>631</v>
+      </c>
+      <c r="E187">
+        <v>289</v>
       </c>
       <c r="F187" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="G187" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188">
-        <v>574603</v>
+        <v>1244301</v>
       </c>
       <c r="B188" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C188" t="s">
-        <v>644</v>
-      </c>
-      <c r="D188">
-        <v>119</v>
-      </c>
-      <c r="E188" t="s">
-        <v>625</v>
+        <v>430</v>
+      </c>
+      <c r="D188" t="s">
+        <v>634</v>
+      </c>
+      <c r="E188">
+        <v>699</v>
       </c>
       <c r="F188" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="G188" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189">
-        <v>679990</v>
+        <v>743071</v>
       </c>
       <c r="B189" t="s">
-        <v>436</v>
+        <v>609</v>
       </c>
       <c r="C189" t="s">
-        <v>647</v>
-      </c>
-      <c r="D189">
-        <v>289</v>
-      </c>
-      <c r="E189" t="s">
-        <v>625</v>
+        <v>381</v>
+      </c>
+      <c r="D189" t="s">
+        <v>637</v>
+      </c>
+      <c r="E189">
+        <v>259</v>
       </c>
       <c r="F189" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="G189" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190">
-        <v>1244301</v>
+        <v>1276183</v>
       </c>
       <c r="B190" t="s">
-        <v>436</v>
+        <v>609</v>
       </c>
       <c r="C190" t="s">
-        <v>650</v>
-      </c>
-      <c r="D190">
-        <v>699</v>
-      </c>
-      <c r="E190" t="s">
-        <v>625</v>
+        <v>381</v>
+      </c>
+      <c r="D190" t="s">
+        <v>640</v>
+      </c>
+      <c r="E190">
+        <v>239</v>
       </c>
       <c r="F190" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="G190" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191">
-        <v>743071</v>
+        <v>1078835</v>
       </c>
       <c r="B191" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C191" t="s">
-        <v>653</v>
-      </c>
-      <c r="D191">
-        <v>259</v>
-      </c>
-      <c r="E191" t="s">
-        <v>625</v>
+        <v>598</v>
+      </c>
+      <c r="D191" t="s">
+        <v>643</v>
+      </c>
+      <c r="E191">
+        <v>99</v>
       </c>
       <c r="F191" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="G191" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192">
-        <v>1276183</v>
+        <v>1066503</v>
       </c>
       <c r="B192" t="s">
-        <v>387</v>
+        <v>609</v>
       </c>
       <c r="C192" t="s">
-        <v>656</v>
-      </c>
-      <c r="D192">
-        <v>239</v>
-      </c>
-      <c r="E192" t="s">
-        <v>625</v>
+        <v>430</v>
+      </c>
+      <c r="D192" t="s">
+        <v>646</v>
+      </c>
+      <c r="E192">
+        <v>529</v>
       </c>
       <c r="F192" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="G192" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193">
-        <v>1078835</v>
+        <v>1120138</v>
       </c>
       <c r="B193" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C193" t="s">
-        <v>659</v>
-      </c>
-      <c r="D193">
-        <v>99</v>
-      </c>
-      <c r="E193" t="s">
-        <v>625</v>
+        <v>430</v>
+      </c>
+      <c r="D193" t="s">
+        <v>649</v>
+      </c>
+      <c r="E193">
+        <v>259</v>
       </c>
       <c r="F193" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="G193" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194">
-        <v>1066503</v>
+        <v>1237164</v>
       </c>
       <c r="B194" t="s">
-        <v>436</v>
+        <v>654</v>
       </c>
       <c r="C194" t="s">
-        <v>662</v>
-      </c>
-      <c r="D194">
-        <v>529</v>
-      </c>
-      <c r="E194" t="s">
-        <v>625</v>
+        <v>652</v>
+      </c>
+      <c r="D194" t="s">
+        <v>653</v>
+      </c>
+      <c r="E194">
+        <v>605</v>
       </c>
       <c r="F194" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="G194" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195">
-        <v>1120138</v>
+        <v>1163212</v>
       </c>
       <c r="B195" t="s">
-        <v>436</v>
+        <v>654</v>
       </c>
       <c r="C195" t="s">
-        <v>665</v>
-      </c>
-      <c r="D195">
-        <v>259</v>
-      </c>
-      <c r="E195" t="s">
-        <v>625</v>
+        <v>657</v>
+      </c>
+      <c r="D195" t="s">
+        <v>658</v>
+      </c>
+      <c r="E195">
+        <v>299</v>
       </c>
       <c r="F195" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="G195" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196">
-        <v>1237164</v>
+        <v>1119466</v>
       </c>
       <c r="B196" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="C196" t="s">
-        <v>669</v>
-      </c>
-      <c r="D196">
-        <v>605</v>
-      </c>
-      <c r="E196" t="s">
-        <v>670</v>
+        <v>652</v>
+      </c>
+      <c r="D196" t="s">
+        <v>661</v>
+      </c>
+      <c r="E196">
+        <v>320</v>
       </c>
       <c r="F196" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="G196" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197">
-        <v>1163212</v>
+        <v>1237155</v>
       </c>
       <c r="B197" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="C197" t="s">
-        <v>674</v>
-      </c>
-      <c r="D197">
-        <v>299</v>
-      </c>
-      <c r="E197" t="s">
-        <v>670</v>
+        <v>652</v>
+      </c>
+      <c r="D197" t="s">
+        <v>664</v>
+      </c>
+      <c r="E197">
+        <v>605</v>
       </c>
       <c r="F197" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="G197" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198">
-        <v>1119466</v>
+        <v>717575</v>
       </c>
       <c r="B198" t="s">
+        <v>654</v>
+      </c>
+      <c r="C198" t="s">
+        <v>667</v>
+      </c>
+      <c r="D198" t="s">
         <v>668</v>
       </c>
-      <c r="C198" t="s">
-        <v>677</v>
-      </c>
-      <c r="D198">
-        <v>320</v>
-      </c>
-      <c r="E198" t="s">
+      <c r="E198">
+        <v>3699</v>
+      </c>
+      <c r="F198" t="s">
+        <v>669</v>
+      </c>
+      <c r="G198" t="s">
         <v>670</v>
-      </c>
-      <c r="F198" t="s">
-        <v>678</v>
-      </c>
-      <c r="G198" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199">
-        <v>1237155</v>
+        <v>1205703</v>
       </c>
       <c r="B199" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="C199" t="s">
-        <v>680</v>
-      </c>
-      <c r="D199">
-        <v>605</v>
-      </c>
-      <c r="E199" t="s">
-        <v>670</v>
+        <v>657</v>
+      </c>
+      <c r="D199" t="s">
+        <v>671</v>
+      </c>
+      <c r="E199">
+        <v>139</v>
       </c>
       <c r="F199" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="G199" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200">
-        <v>717575</v>
+        <v>1175479</v>
       </c>
       <c r="B200" t="s">
-        <v>683</v>
+        <v>654</v>
       </c>
       <c r="C200" t="s">
-        <v>684</v>
-      </c>
-      <c r="D200">
-        <v>3699</v>
-      </c>
-      <c r="E200" t="s">
-        <v>670</v>
+        <v>674</v>
+      </c>
+      <c r="D200" t="s">
+        <v>675</v>
+      </c>
+      <c r="E200">
+        <v>199</v>
       </c>
       <c r="F200" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="G200" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201">
-        <v>1205703</v>
+        <v>1205701</v>
       </c>
       <c r="B201" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="C201" t="s">
-        <v>687</v>
-      </c>
-      <c r="D201">
-        <v>139</v>
-      </c>
-      <c r="E201" t="s">
-        <v>670</v>
+        <v>657</v>
+      </c>
+      <c r="D201" t="s">
+        <v>678</v>
+      </c>
+      <c r="E201">
+        <v>135</v>
       </c>
       <c r="F201" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="G201" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202">
-        <v>1175479</v>
+        <v>1163204</v>
       </c>
       <c r="B202" t="s">
-        <v>690</v>
+        <v>654</v>
       </c>
       <c r="C202" t="s">
-        <v>691</v>
-      </c>
-      <c r="D202">
-        <v>199</v>
-      </c>
-      <c r="E202" t="s">
-        <v>670</v>
+        <v>657</v>
+      </c>
+      <c r="D202" t="s">
+        <v>681</v>
+      </c>
+      <c r="E202">
+        <v>279</v>
       </c>
       <c r="F202" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="G202" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203">
-        <v>1205701</v>
+        <v>1161930</v>
       </c>
       <c r="B203" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="C203" t="s">
-        <v>694</v>
-      </c>
-      <c r="D203">
-        <v>135</v>
-      </c>
-      <c r="E203" t="s">
-        <v>670</v>
+        <v>684</v>
+      </c>
+      <c r="D203" t="s">
+        <v>685</v>
+      </c>
+      <c r="E203">
+        <v>189</v>
       </c>
       <c r="F203" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="G203" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204">
-        <v>1163204</v>
+        <v>1186703</v>
       </c>
       <c r="B204" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="C204" t="s">
-        <v>697</v>
-      </c>
-      <c r="D204">
-        <v>279</v>
-      </c>
-      <c r="E204" t="s">
-        <v>670</v>
+        <v>684</v>
+      </c>
+      <c r="D204" t="s">
+        <v>688</v>
+      </c>
+      <c r="E204">
+        <v>179</v>
       </c>
       <c r="F204" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="G204" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205">
-        <v>1161930</v>
+        <v>747460</v>
       </c>
       <c r="B205" t="s">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="C205" t="s">
-        <v>701</v>
-      </c>
-      <c r="D205">
-        <v>189</v>
-      </c>
-      <c r="E205" t="s">
-        <v>670</v>
+        <v>652</v>
+      </c>
+      <c r="D205" t="s">
+        <v>691</v>
+      </c>
+      <c r="E205">
+        <v>1339</v>
       </c>
       <c r="F205" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="G205" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206">
-        <v>1186703</v>
+        <v>1278727</v>
       </c>
       <c r="B206" t="s">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="C206" t="s">
-        <v>704</v>
-      </c>
-      <c r="D206">
-        <v>179</v>
-      </c>
-      <c r="E206" t="s">
-        <v>670</v>
+        <v>40</v>
+      </c>
+      <c r="D206" t="s">
+        <v>694</v>
+      </c>
+      <c r="E206">
+        <v>2215</v>
       </c>
       <c r="F206" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="G206" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207">
-        <v>747460</v>
+        <v>1068860</v>
       </c>
       <c r="B207" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="C207" t="s">
-        <v>707</v>
-      </c>
-      <c r="D207">
-        <v>1339</v>
-      </c>
-      <c r="E207" t="s">
-        <v>670</v>
+        <v>697</v>
+      </c>
+      <c r="D207" t="s">
+        <v>698</v>
+      </c>
+      <c r="E207">
+        <v>888</v>
       </c>
       <c r="F207" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="G207" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208">
-        <v>1278727</v>
+        <v>1317712</v>
       </c>
       <c r="B208" t="s">
-        <v>40</v>
+        <v>654</v>
       </c>
       <c r="C208" t="s">
-        <v>710</v>
-      </c>
-      <c r="D208">
-        <v>2215</v>
-      </c>
-      <c r="E208" t="s">
-        <v>670</v>
+        <v>392</v>
+      </c>
+      <c r="D208" t="s">
+        <v>701</v>
+      </c>
+      <c r="E208">
+        <v>349</v>
       </c>
       <c r="F208" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="G208" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209">
-        <v>1068860</v>
+        <v>1241587</v>
       </c>
       <c r="B209" t="s">
-        <v>713</v>
+        <v>654</v>
       </c>
       <c r="C209" t="s">
-        <v>714</v>
-      </c>
-      <c r="D209">
-        <v>888</v>
-      </c>
-      <c r="E209" t="s">
-        <v>670</v>
+        <v>704</v>
+      </c>
+      <c r="D209" t="s">
+        <v>705</v>
+      </c>
+      <c r="E209">
+        <v>397</v>
       </c>
       <c r="F209" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="G209" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210">
-        <v>1317712</v>
+        <v>1198955</v>
       </c>
       <c r="B210" t="s">
-        <v>398</v>
+        <v>654</v>
       </c>
       <c r="C210" t="s">
-        <v>717</v>
-      </c>
-      <c r="D210">
-        <v>349</v>
-      </c>
-      <c r="E210" t="s">
-        <v>670</v>
+        <v>708</v>
+      </c>
+      <c r="D210" t="s">
+        <v>709</v>
+      </c>
+      <c r="E210">
+        <v>199</v>
       </c>
       <c r="F210" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="G210" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211">
-        <v>1241587</v>
+        <v>1119463</v>
       </c>
       <c r="B211" t="s">
-        <v>720</v>
+        <v>654</v>
       </c>
       <c r="C211" t="s">
-        <v>721</v>
-      </c>
-      <c r="D211">
-        <v>397</v>
-      </c>
-      <c r="E211" t="s">
-        <v>670</v>
+        <v>652</v>
+      </c>
+      <c r="D211" t="s">
+        <v>712</v>
+      </c>
+      <c r="E211">
+        <v>399</v>
       </c>
       <c r="F211" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="G211" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212">
-        <v>1198955</v>
+        <v>1119461</v>
       </c>
       <c r="B212" t="s">
-        <v>724</v>
+        <v>654</v>
       </c>
       <c r="C212" t="s">
-        <v>725</v>
-      </c>
-      <c r="D212">
-        <v>199</v>
-      </c>
-      <c r="E212" t="s">
-        <v>670</v>
+        <v>652</v>
+      </c>
+      <c r="D212" t="s">
+        <v>715</v>
+      </c>
+      <c r="E212">
+        <v>136</v>
       </c>
       <c r="F212" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="G212" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213">
-        <v>1119463</v>
+        <v>1119459</v>
       </c>
       <c r="B213" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="C213" t="s">
-        <v>728</v>
-      </c>
-      <c r="D213">
-        <v>399</v>
-      </c>
-      <c r="E213" t="s">
-        <v>670</v>
+        <v>652</v>
+      </c>
+      <c r="D213" t="s">
+        <v>719</v>
+      </c>
+      <c r="E213">
+        <v>136</v>
       </c>
       <c r="F213" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="G213" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214">
-        <v>1119461</v>
+        <v>1285257</v>
       </c>
       <c r="B214" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="C214" t="s">
-        <v>731</v>
-      </c>
-      <c r="D214">
-        <v>136</v>
-      </c>
-      <c r="E214" t="s">
-        <v>670</v>
+        <v>674</v>
+      </c>
+      <c r="D214" t="s">
+        <v>722</v>
+      </c>
+      <c r="E214">
+        <v>849</v>
       </c>
       <c r="F214" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="G214" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215">
-        <v>1119459</v>
+        <v>1285147</v>
       </c>
       <c r="B215" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="C215" t="s">
-        <v>735</v>
-      </c>
-      <c r="D215">
-        <v>136</v>
-      </c>
-      <c r="E215" t="s">
-        <v>670</v>
+        <v>704</v>
+      </c>
+      <c r="D215" t="s">
+        <v>725</v>
+      </c>
+      <c r="E215">
+        <v>1199</v>
       </c>
       <c r="F215" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="G215" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216">
-        <v>1285257</v>
+        <v>1244354</v>
       </c>
       <c r="B216" t="s">
-        <v>690</v>
+        <v>654</v>
       </c>
       <c r="C216" t="s">
-        <v>738</v>
-      </c>
-      <c r="D216">
-        <v>849</v>
-      </c>
-      <c r="E216" t="s">
-        <v>670</v>
+        <v>728</v>
+      </c>
+      <c r="D216" t="s">
+        <v>729</v>
+      </c>
+      <c r="E216">
+        <v>279</v>
       </c>
       <c r="F216" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="G216" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217">
-        <v>1285147</v>
+        <v>1229062</v>
       </c>
       <c r="B217" t="s">
-        <v>720</v>
+        <v>654</v>
       </c>
       <c r="C217" t="s">
-        <v>741</v>
-      </c>
-      <c r="D217">
-        <v>1199</v>
-      </c>
-      <c r="E217" t="s">
-        <v>670</v>
+        <v>718</v>
+      </c>
+      <c r="D217" t="s">
+        <v>732</v>
+      </c>
+      <c r="E217">
+        <v>279</v>
       </c>
       <c r="F217" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="G217" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218">
-        <v>1244354</v>
+        <v>1265852</v>
       </c>
       <c r="B218" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="C218" t="s">
-        <v>745</v>
-      </c>
-      <c r="D218">
-        <v>279</v>
-      </c>
-      <c r="E218" t="s">
-        <v>670</v>
+        <v>7</v>
+      </c>
+      <c r="D218" t="s">
+        <v>735</v>
+      </c>
+      <c r="E218">
+        <v>999</v>
       </c>
       <c r="F218" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="G218" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219">
-        <v>1229062</v>
+        <v>1316243</v>
       </c>
       <c r="B219" t="s">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="C219" t="s">
-        <v>748</v>
-      </c>
-      <c r="D219">
-        <v>279</v>
-      </c>
-      <c r="E219" t="s">
-        <v>670</v>
+        <v>460</v>
+      </c>
+      <c r="D219" t="s">
+        <v>738</v>
+      </c>
+      <c r="E219">
+        <v>449</v>
       </c>
       <c r="F219" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="G219" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220">
-        <v>1265852</v>
+        <v>1278400</v>
       </c>
       <c r="B220" t="s">
-        <v>7</v>
+        <v>764</v>
       </c>
       <c r="C220" t="s">
-        <v>751</v>
-      </c>
-      <c r="D220">
-        <v>999</v>
-      </c>
-      <c r="E220" t="s">
-        <v>752</v>
+        <v>33</v>
+      </c>
+      <c r="D220" t="s">
+        <v>741</v>
+      </c>
+      <c r="E220">
+        <v>1919</v>
       </c>
       <c r="F220" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="G220" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221">
-        <v>1316243</v>
+        <v>1291199</v>
       </c>
       <c r="B221" t="s">
-        <v>468</v>
+        <v>764</v>
       </c>
       <c r="C221" t="s">
-        <v>755</v>
-      </c>
-      <c r="D221">
-        <v>449</v>
-      </c>
-      <c r="E221" t="s">
-        <v>752</v>
+        <v>744</v>
+      </c>
+      <c r="D221" t="s">
+        <v>745</v>
+      </c>
+      <c r="E221">
+        <v>599</v>
       </c>
       <c r="F221" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="G221" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222">
-        <v>1278400</v>
+        <v>1313287</v>
       </c>
       <c r="B222" t="s">
-        <v>33</v>
+        <v>764</v>
       </c>
       <c r="C222" t="s">
-        <v>758</v>
-      </c>
-      <c r="D222">
-        <v>1919</v>
-      </c>
-      <c r="E222" t="s">
-        <v>752</v>
+        <v>443</v>
+      </c>
+      <c r="D222" t="s">
+        <v>748</v>
+      </c>
+      <c r="E222">
+        <v>549</v>
       </c>
       <c r="F222" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="G222" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223">
-        <v>1291199</v>
+        <v>1307531</v>
       </c>
       <c r="B223" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C223" t="s">
-        <v>762</v>
-      </c>
-      <c r="D223">
-        <v>599</v>
-      </c>
-      <c r="E223" t="s">
+        <v>443</v>
+      </c>
+      <c r="D223" t="s">
+        <v>751</v>
+      </c>
+      <c r="E223">
+        <v>1299</v>
+      </c>
+      <c r="F223" t="s">
         <v>752</v>
       </c>
-      <c r="F223" t="s">
-        <v>763</v>
-      </c>
       <c r="G223" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224">
-        <v>1313287</v>
+        <v>1288372</v>
       </c>
       <c r="B224" t="s">
-        <v>450</v>
+        <v>764</v>
       </c>
       <c r="C224" t="s">
-        <v>765</v>
-      </c>
-      <c r="D224">
-        <v>549</v>
-      </c>
-      <c r="E224" t="s">
-        <v>752</v>
+        <v>40</v>
+      </c>
+      <c r="D224" t="s">
+        <v>754</v>
+      </c>
+      <c r="E224">
+        <v>2999</v>
       </c>
       <c r="F224" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="G224" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225">
-        <v>1307531</v>
+        <v>1314535</v>
       </c>
       <c r="B225" t="s">
-        <v>450</v>
+        <v>764</v>
       </c>
       <c r="C225" t="s">
-        <v>768</v>
-      </c>
-      <c r="D225">
-        <v>1299</v>
-      </c>
-      <c r="E225" t="s">
-        <v>752</v>
+        <v>62</v>
+      </c>
+      <c r="D225" t="s">
+        <v>757</v>
+      </c>
+      <c r="E225">
+        <v>2199</v>
       </c>
       <c r="F225" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="G225" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226">
-        <v>1288372</v>
+        <v>1306362</v>
       </c>
       <c r="B226" t="s">
-        <v>40</v>
+        <v>764</v>
       </c>
       <c r="C226" t="s">
-        <v>771</v>
-      </c>
-      <c r="D226">
-        <v>2999</v>
-      </c>
-      <c r="E226" t="s">
-        <v>752</v>
+        <v>760</v>
+      </c>
+      <c r="D226" t="s">
+        <v>761</v>
+      </c>
+      <c r="E226">
+        <v>599</v>
       </c>
       <c r="F226" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="G226" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227">
-        <v>1314535</v>
+        <v>1210598</v>
       </c>
       <c r="B227" t="s">
-        <v>62</v>
+        <v>764</v>
       </c>
       <c r="C227" t="s">
-        <v>774</v>
-      </c>
-      <c r="D227">
-        <v>2199</v>
-      </c>
-      <c r="E227" t="s">
-        <v>752</v>
+        <v>443</v>
+      </c>
+      <c r="D227" t="s">
+        <v>765</v>
+      </c>
+      <c r="E227">
+        <v>599</v>
       </c>
       <c r="F227" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="G227" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228">
-        <v>1306362</v>
+        <v>1244945</v>
       </c>
       <c r="B228" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="C228" t="s">
-        <v>778</v>
-      </c>
-      <c r="D228">
-        <v>599</v>
-      </c>
-      <c r="E228" t="s">
-        <v>752</v>
+        <v>40</v>
+      </c>
+      <c r="D228" t="s">
+        <v>768</v>
+      </c>
+      <c r="E228">
+        <v>4859</v>
       </c>
       <c r="F228" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="G228" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229">
-        <v>1210598</v>
+        <v>1233939</v>
       </c>
       <c r="B229" t="s">
-        <v>450</v>
+        <v>764</v>
       </c>
       <c r="C229" t="s">
-        <v>782</v>
-      </c>
-      <c r="D229">
-        <v>599</v>
-      </c>
-      <c r="E229" t="s">
-        <v>781</v>
+        <v>760</v>
+      </c>
+      <c r="D229" t="s">
+        <v>771</v>
+      </c>
+      <c r="E229">
+        <v>999</v>
       </c>
       <c r="F229" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="G229" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230">
-        <v>1244945</v>
+        <v>1313413</v>
       </c>
       <c r="B230" t="s">
-        <v>40</v>
+        <v>764</v>
       </c>
       <c r="C230" t="s">
-        <v>785</v>
-      </c>
-      <c r="D230">
-        <v>4859</v>
-      </c>
-      <c r="E230" t="s">
-        <v>781</v>
+        <v>443</v>
+      </c>
+      <c r="D230" t="s">
+        <v>774</v>
+      </c>
+      <c r="E230">
+        <v>3299</v>
       </c>
       <c r="F230" t="s">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="G230" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231">
-        <v>1233939</v>
+        <v>1165458</v>
       </c>
       <c r="B231" t="s">
+        <v>764</v>
+      </c>
+      <c r="C231" t="s">
+        <v>26</v>
+      </c>
+      <c r="D231" t="s">
         <v>777</v>
       </c>
-      <c r="C231" t="s">
-        <v>788</v>
-      </c>
-      <c r="D231">
-        <v>999</v>
-      </c>
-      <c r="E231" t="s">
-        <v>781</v>
+      <c r="E231">
+        <v>549</v>
       </c>
       <c r="F231" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="G231" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232">
-        <v>1313413</v>
+        <v>1265851</v>
       </c>
       <c r="B232" t="s">
-        <v>450</v>
+        <v>764</v>
       </c>
       <c r="C232" t="s">
-        <v>791</v>
-      </c>
-      <c r="D232">
-        <v>3299</v>
-      </c>
-      <c r="E232" t="s">
+        <v>7</v>
+      </c>
+      <c r="D232" t="s">
+        <v>780</v>
+      </c>
+      <c r="E232">
+        <v>702</v>
+      </c>
+      <c r="F232" t="s">
         <v>781</v>
       </c>
-      <c r="F232" t="s">
-        <v>792</v>
-      </c>
       <c r="G232" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233">
-        <v>1165458</v>
+        <v>1314534</v>
       </c>
       <c r="B233" t="s">
-        <v>26</v>
+        <v>764</v>
       </c>
       <c r="C233" t="s">
-        <v>794</v>
-      </c>
-      <c r="D233">
-        <v>549</v>
-      </c>
-      <c r="E233" t="s">
-        <v>781</v>
+        <v>62</v>
+      </c>
+      <c r="D233" t="s">
+        <v>783</v>
+      </c>
+      <c r="E233">
+        <v>1499</v>
       </c>
       <c r="F233" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="G233" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234">
-        <v>1265851</v>
+        <v>1195782</v>
       </c>
       <c r="B234" t="s">
+        <v>764</v>
+      </c>
+      <c r="C234" t="s">
         <v>7</v>
       </c>
-      <c r="C234" t="s">
-        <v>797</v>
-      </c>
-      <c r="D234">
-        <v>702</v>
-      </c>
-      <c r="E234" t="s">
-        <v>781</v>
+      <c r="D234" t="s">
+        <v>786</v>
+      </c>
+      <c r="E234">
+        <v>699</v>
       </c>
       <c r="F234" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="G234" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235">
-        <v>1314534</v>
+        <v>1285144</v>
       </c>
       <c r="B235" t="s">
+        <v>764</v>
+      </c>
+      <c r="C235" t="s">
         <v>62</v>
       </c>
-      <c r="C235" t="s">
-        <v>800</v>
-      </c>
-      <c r="D235">
-        <v>1499</v>
-      </c>
-      <c r="E235" t="s">
-        <v>781</v>
+      <c r="D235" t="s">
+        <v>789</v>
+      </c>
+      <c r="E235">
+        <v>2199</v>
       </c>
       <c r="F235" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="G235" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236">
-        <v>1195782</v>
+        <v>1313286</v>
       </c>
       <c r="B236" t="s">
-        <v>7</v>
+        <v>764</v>
       </c>
       <c r="C236" t="s">
-        <v>803</v>
-      </c>
-      <c r="D236">
-        <v>699</v>
-      </c>
-      <c r="E236" t="s">
-        <v>781</v>
+        <v>443</v>
+      </c>
+      <c r="D236" t="s">
+        <v>792</v>
+      </c>
+      <c r="E236">
+        <v>499</v>
       </c>
       <c r="F236" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="G236" t="s">
-        <v>805</v>
+        <v>750</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237">
-        <v>1285144</v>
+        <v>1313412</v>
       </c>
       <c r="B237" t="s">
-        <v>62</v>
+        <v>764</v>
       </c>
       <c r="C237" t="s">
-        <v>806</v>
-      </c>
-      <c r="D237">
-        <v>2199</v>
-      </c>
-      <c r="E237" t="s">
-        <v>781</v>
+        <v>443</v>
+      </c>
+      <c r="D237" t="s">
+        <v>794</v>
+      </c>
+      <c r="E237">
+        <v>1599</v>
       </c>
       <c r="F237" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="G237" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238">
-        <v>1313286</v>
+        <v>1262454</v>
       </c>
       <c r="B238" t="s">
-        <v>450</v>
+        <v>764</v>
       </c>
       <c r="C238" t="s">
-        <v>809</v>
-      </c>
-      <c r="D238">
-        <v>499</v>
-      </c>
-      <c r="E238" t="s">
-        <v>781</v>
+        <v>443</v>
+      </c>
+      <c r="D238" t="s">
+        <v>797</v>
+      </c>
+      <c r="E238">
+        <v>999</v>
       </c>
       <c r="F238" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="G238" t="s">
-        <v>767</v>
+        <v>799</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239">
-        <v>1313412</v>
+        <v>1313415</v>
       </c>
       <c r="B239" t="s">
-        <v>450</v>
+        <v>764</v>
       </c>
       <c r="C239" t="s">
-        <v>811</v>
-      </c>
-      <c r="D239">
-        <v>1599</v>
-      </c>
-      <c r="E239" t="s">
-        <v>781</v>
+        <v>443</v>
+      </c>
+      <c r="D239" t="s">
+        <v>800</v>
+      </c>
+      <c r="E239">
+        <v>629</v>
       </c>
       <c r="F239" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="G239" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240">
-        <v>1262454</v>
+        <v>1290961</v>
       </c>
       <c r="B240" t="s">
-        <v>450</v>
+        <v>876</v>
       </c>
       <c r="C240" t="s">
-        <v>814</v>
-      </c>
-      <c r="D240">
-        <v>999</v>
-      </c>
-      <c r="E240" t="s">
-        <v>781</v>
+        <v>803</v>
+      </c>
+      <c r="D240" t="s">
+        <v>804</v>
+      </c>
+      <c r="E240">
+        <v>239</v>
       </c>
       <c r="F240" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="G240" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241">
-        <v>1313415</v>
+        <v>1244381</v>
       </c>
       <c r="B241" t="s">
-        <v>450</v>
+        <v>876</v>
       </c>
       <c r="C241" t="s">
-        <v>817</v>
-      </c>
-      <c r="D241">
-        <v>629</v>
-      </c>
-      <c r="E241" t="s">
-        <v>781</v>
+        <v>807</v>
+      </c>
+      <c r="D241" t="s">
+        <v>808</v>
+      </c>
+      <c r="E241">
+        <v>329</v>
       </c>
       <c r="F241" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="G241" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242">
-        <v>1290961</v>
+        <v>1134664</v>
       </c>
       <c r="B242" t="s">
-        <v>820</v>
+        <v>876</v>
       </c>
       <c r="C242" t="s">
-        <v>821</v>
-      </c>
-      <c r="D242">
-        <v>239</v>
-      </c>
-      <c r="E242" t="s">
-        <v>822</v>
+        <v>811</v>
+      </c>
+      <c r="D242" t="s">
+        <v>812</v>
+      </c>
+      <c r="E242">
+        <v>549</v>
       </c>
       <c r="F242" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="G242" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243">
-        <v>1244381</v>
+        <v>1168226</v>
       </c>
       <c r="B243" t="s">
-        <v>825</v>
+        <v>876</v>
       </c>
       <c r="C243" t="s">
-        <v>826</v>
-      </c>
-      <c r="D243">
-        <v>329</v>
-      </c>
-      <c r="E243" t="s">
-        <v>822</v>
+        <v>815</v>
+      </c>
+      <c r="D243" t="s">
+        <v>816</v>
+      </c>
+      <c r="E243">
+        <v>399</v>
       </c>
       <c r="F243" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="G243" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244">
-        <v>1134664</v>
+        <v>1291825</v>
       </c>
       <c r="B244" t="s">
-        <v>829</v>
+        <v>876</v>
       </c>
       <c r="C244" t="s">
-        <v>830</v>
-      </c>
-      <c r="D244">
-        <v>549</v>
-      </c>
-      <c r="E244" t="s">
-        <v>822</v>
+        <v>811</v>
+      </c>
+      <c r="D244" t="s">
+        <v>819</v>
+      </c>
+      <c r="E244">
+        <v>2249</v>
       </c>
       <c r="F244" t="s">
-        <v>831</v>
+        <v>820</v>
       </c>
       <c r="G244" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245">
-        <v>1168226</v>
+        <v>466049</v>
       </c>
       <c r="B245" t="s">
-        <v>833</v>
+        <v>876</v>
       </c>
       <c r="C245" t="s">
-        <v>834</v>
-      </c>
-      <c r="D245">
-        <v>399</v>
-      </c>
-      <c r="E245" t="s">
+        <v>811</v>
+      </c>
+      <c r="D245" t="s">
         <v>822</v>
       </c>
+      <c r="E245">
+        <v>149</v>
+      </c>
       <c r="F245" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="G245" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246">
-        <v>1291825</v>
+        <v>1294998</v>
       </c>
       <c r="B246" t="s">
-        <v>829</v>
+        <v>876</v>
       </c>
       <c r="C246" t="s">
-        <v>837</v>
-      </c>
-      <c r="D246">
-        <v>2249</v>
-      </c>
-      <c r="E246" t="s">
-        <v>822</v>
+        <v>811</v>
+      </c>
+      <c r="D246" t="s">
+        <v>825</v>
+      </c>
+      <c r="E246">
+        <v>1399</v>
       </c>
       <c r="F246" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="G246" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247">
-        <v>466049</v>
+        <v>1271919</v>
       </c>
       <c r="B247" t="s">
+        <v>876</v>
+      </c>
+      <c r="C247" t="s">
+        <v>322</v>
+      </c>
+      <c r="D247" t="s">
+        <v>828</v>
+      </c>
+      <c r="E247">
+        <v>1299</v>
+      </c>
+      <c r="F247" t="s">
         <v>829</v>
       </c>
-      <c r="C247" t="s">
-        <v>840</v>
-      </c>
-      <c r="D247">
-        <v>149</v>
-      </c>
-      <c r="E247" t="s">
-        <v>822</v>
-      </c>
-      <c r="F247" t="s">
-        <v>841</v>
-      </c>
       <c r="G247" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248">
-        <v>1294998</v>
+        <v>1288081</v>
       </c>
       <c r="B248" t="s">
-        <v>829</v>
+        <v>876</v>
       </c>
       <c r="C248" t="s">
-        <v>843</v>
-      </c>
-      <c r="D248">
-        <v>1399</v>
-      </c>
-      <c r="E248" t="s">
-        <v>822</v>
+        <v>831</v>
+      </c>
+      <c r="D248" t="s">
+        <v>832</v>
+      </c>
+      <c r="E248">
+        <v>899</v>
       </c>
       <c r="F248" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="G248" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249">
-        <v>1271919</v>
+        <v>1274966</v>
       </c>
       <c r="B249" t="s">
-        <v>327</v>
+        <v>876</v>
       </c>
       <c r="C249" t="s">
-        <v>846</v>
-      </c>
-      <c r="D249">
-        <v>1299</v>
-      </c>
-      <c r="E249" t="s">
-        <v>822</v>
+        <v>322</v>
+      </c>
+      <c r="D249" t="s">
+        <v>835</v>
+      </c>
+      <c r="E249">
+        <v>449</v>
       </c>
       <c r="F249" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="G249" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250">
-        <v>1288081</v>
+        <v>1249062</v>
       </c>
       <c r="B250" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="C250" t="s">
-        <v>850</v>
-      </c>
-      <c r="D250">
-        <v>899</v>
-      </c>
-      <c r="E250" t="s">
-        <v>822</v>
+        <v>322</v>
+      </c>
+      <c r="D250" t="s">
+        <v>838</v>
+      </c>
+      <c r="E250">
+        <v>164</v>
       </c>
       <c r="F250" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="G250" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251">
-        <v>1274966</v>
+        <v>521479</v>
       </c>
       <c r="B251" t="s">
-        <v>327</v>
+        <v>876</v>
       </c>
       <c r="C251" t="s">
-        <v>853</v>
-      </c>
-      <c r="D251">
-        <v>449</v>
-      </c>
-      <c r="E251" t="s">
-        <v>822</v>
+        <v>322</v>
+      </c>
+      <c r="D251" t="s">
+        <v>841</v>
+      </c>
+      <c r="E251">
+        <v>354</v>
       </c>
       <c r="F251" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="G251" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252">
-        <v>1249062</v>
+        <v>1290381</v>
       </c>
       <c r="B252" t="s">
-        <v>327</v>
+        <v>876</v>
       </c>
       <c r="C252" t="s">
-        <v>856</v>
-      </c>
-      <c r="D252">
-        <v>164</v>
-      </c>
-      <c r="E252" t="s">
-        <v>822</v>
+        <v>844</v>
+      </c>
+      <c r="D252" t="s">
+        <v>845</v>
+      </c>
+      <c r="E252">
+        <v>199</v>
       </c>
       <c r="F252" t="s">
-        <v>857</v>
+        <v>846</v>
       </c>
       <c r="G252" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253">
-        <v>521479</v>
+        <v>1168233</v>
       </c>
       <c r="B253" t="s">
-        <v>327</v>
+        <v>876</v>
       </c>
       <c r="C253" t="s">
-        <v>859</v>
-      </c>
-      <c r="D253">
-        <v>354</v>
-      </c>
-      <c r="E253" t="s">
-        <v>822</v>
+        <v>815</v>
+      </c>
+      <c r="D253" t="s">
+        <v>848</v>
+      </c>
+      <c r="E253">
+        <v>549</v>
       </c>
       <c r="F253" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="G253" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254">
-        <v>1290381</v>
+        <v>1294051</v>
       </c>
       <c r="B254" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="C254" t="s">
-        <v>863</v>
-      </c>
-      <c r="D254">
-        <v>199</v>
-      </c>
-      <c r="E254" t="s">
-        <v>822</v>
+        <v>322</v>
+      </c>
+      <c r="D254" t="s">
+        <v>851</v>
+      </c>
+      <c r="E254">
+        <v>1099</v>
       </c>
       <c r="F254" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="G254" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255">
-        <v>1168233</v>
+        <v>682700</v>
       </c>
       <c r="B255" t="s">
-        <v>833</v>
+        <v>876</v>
       </c>
       <c r="C255" t="s">
-        <v>866</v>
-      </c>
-      <c r="D255">
-        <v>549</v>
-      </c>
-      <c r="E255" t="s">
-        <v>822</v>
+        <v>811</v>
+      </c>
+      <c r="D255" t="s">
+        <v>854</v>
+      </c>
+      <c r="E255">
+        <v>189</v>
       </c>
       <c r="F255" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="G255" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256">
-        <v>1294051</v>
+        <v>718522</v>
       </c>
       <c r="B256" t="s">
-        <v>327</v>
+        <v>876</v>
       </c>
       <c r="C256" t="s">
-        <v>869</v>
-      </c>
-      <c r="D256">
-        <v>1099</v>
-      </c>
-      <c r="E256" t="s">
-        <v>822</v>
+        <v>811</v>
+      </c>
+      <c r="D256" t="s">
+        <v>857</v>
+      </c>
+      <c r="E256">
+        <v>219</v>
       </c>
       <c r="F256" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="G256" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257">
-        <v>682700</v>
+        <v>1260308</v>
       </c>
       <c r="B257" t="s">
-        <v>829</v>
+        <v>876</v>
       </c>
       <c r="C257" t="s">
-        <v>872</v>
-      </c>
-      <c r="D257">
-        <v>189</v>
-      </c>
-      <c r="E257" t="s">
-        <v>822</v>
+        <v>460</v>
+      </c>
+      <c r="D257" t="s">
+        <v>860</v>
+      </c>
+      <c r="E257">
+        <v>899</v>
       </c>
       <c r="F257" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="G257" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258">
-        <v>718522</v>
+        <v>1212069</v>
       </c>
       <c r="B258" t="s">
-        <v>829</v>
+        <v>876</v>
       </c>
       <c r="C258" t="s">
-        <v>876</v>
-      </c>
-      <c r="D258">
-        <v>219</v>
-      </c>
-      <c r="E258" t="s">
-        <v>875</v>
+        <v>322</v>
+      </c>
+      <c r="D258" t="s">
+        <v>863</v>
+      </c>
+      <c r="E258">
+        <v>2999</v>
       </c>
       <c r="F258" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="G258" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259">
-        <v>1260308</v>
+        <v>1205881</v>
       </c>
       <c r="B259" t="s">
-        <v>468</v>
+        <v>876</v>
       </c>
       <c r="C259" t="s">
-        <v>879</v>
-      </c>
-      <c r="D259">
-        <v>899</v>
-      </c>
-      <c r="E259" t="s">
-        <v>875</v>
+        <v>844</v>
+      </c>
+      <c r="D259" t="s">
+        <v>866</v>
+      </c>
+      <c r="E259">
+        <v>379</v>
       </c>
       <c r="F259" t="s">
-        <v>880</v>
+        <v>867</v>
       </c>
       <c r="G259" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260">
-        <v>1212069</v>
+        <v>1219899</v>
       </c>
       <c r="B260" t="s">
-        <v>327</v>
+        <v>876</v>
       </c>
       <c r="C260" t="s">
-        <v>882</v>
-      </c>
-      <c r="D260">
-        <v>2999</v>
-      </c>
-      <c r="E260" t="s">
-        <v>875</v>
+        <v>803</v>
+      </c>
+      <c r="D260" t="s">
+        <v>869</v>
+      </c>
+      <c r="E260">
+        <v>129</v>
       </c>
       <c r="F260" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="G260" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A261">
-        <v>1205881</v>
-      </c>
-      <c r="B261" t="s">
-        <v>862</v>
-      </c>
-      <c r="C261" t="s">
-        <v>885</v>
-      </c>
-      <c r="D261">
-        <v>379</v>
-      </c>
-      <c r="E261" t="s">
-        <v>875</v>
-      </c>
-      <c r="F261" t="s">
-        <v>886</v>
-      </c>
-      <c r="G261" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A262">
-        <v>1219899</v>
-      </c>
-      <c r="B262" t="s">
-        <v>820</v>
-      </c>
-      <c r="C262" t="s">
-        <v>888</v>
-      </c>
-      <c r="D262">
-        <v>129</v>
-      </c>
-      <c r="E262" t="s">
-        <v>875</v>
-      </c>
-      <c r="F262" t="s">
-        <v>889</v>
-      </c>
-      <c r="G262" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/processed_products_data_clean.xlsx
+++ b/processed_products_data_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arturpietrzak/Documents/vsc/customer-service-llm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E51B0B-305E-8B41-AD73-03E2562F466D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5359371B-9C00-8244-9EA6-02A9EC64A045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="36000" windowHeight="22520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3280" yWindow="22360" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="890">
   <si>
     <t>id</t>
   </si>
@@ -13347,6 +13347,45 @@
   <si>
     <t>Routery</t>
   </si>
+  <si>
+    <t>questions</t>
+  </si>
+  <si>
+    <t>1. Jaki procesor jest używany w tym smartfonie i jakie są jego kluczowe parametry wydajnościowe (np. liczba rdzeni, taktowanie)? 2. Jaki typ wyświetlacza ma ten smartfon, jaka jest jego rozdzielczość i częstotliwość odświeżania? 3. Jaka jest pojemność baterii i czy smartfon obsługuje szybkie ładowanie? Jeśli tak, jaka jest maksymalna moc ładowania? 4. Jakie są rozdzielczości i typy tylnych aparatów w tym smartfonie? 5. Czy ten smartfon obsługuje łączność 5G i jakie inne opcje łączności bezprzewodowej są dostępne (np. Wi-Fi, Bluetooth, NFC)? 6. Jaka jest maksymalna pojemność pamięci masowej tego smartfona, w tym zarówno pamięć wewnętrzna, jak i wszelkie opcje rozszerzalnej pamięci masowej? 7. Jaki system operacyjny działa w tym smartfonie i jaka jest określona wersja? 8. Jakie materiały są używane w konstrukcji wyświetlacza lub obudowy tego smartfona i czy posiada on jakieś szczególne certyfikaty trwałości (np. stopień ochrony IP, szkło Gorilla)? 9. Czy ten smartfon obsługuje funkcję dual SIM, a jeśli tak, to jaki typ konfiguracji karty SIM jest używany (np. nano-SIM, eSIM)? 10. Jaka jest rozdzielczość i główne funkcje przedniego aparatu w tym smartfonie? 11. Jakie czujniki są zawarte w tym smartfonie (np. akcelerometr, żyroskop, skaner linii papilarnych) i gdzie znajduje się skaner linii papilarnych? 12. Czy ten smartfon obsługuje ładowanie bezprzewodowe, a jeśli tak, to jaka jest maksymalna moc ładowania bezprzewodowego? 13. Jakie są wymiary (wysokość, szerokość, grubość) i waga tego smartfona? 14. Jakie dodatkowe funkcje lub akcesoria są wyróżnione w opisie smartfona (np. rysik, głośniki stereo, dołączone etui)? 15. Jaki jest okres gwarancji na ten smartfon i jaki rodzaj gwarancji jest udzielany?</t>
+  </si>
+  <si>
+    <t>1. Jaka jest pojemność nominalna powerbanku i ile razy może naładować typowy smartfon (np. iPhone 15 lub Galaxy S23)? 2. Jakie rodzaje złączy są dostępne w powerbanku i które urządzenia można nimi ładować? 3. Czy powerbank obsługuje technologię szybkiego ładowania, taką jak Power Delivery lub Quick Charge? Jeśli tak, jaka jest maksymalna moc ładowania? 4. Ile urządzeń można ładować jednocześnie za pomocą tego powerbanku? 5. Czy powerbank posiada funkcję ładowania bezprzewodowego? Jeśli tak, jaka jest maksymalna moc ładowania bezprzewodowego? 6. Jakie zabezpieczenia (np. przed przegrzaniem, przeładowaniem) oferuje powerbank, aby zapewnić bezpieczeństwo użytkowania? 7. Jakie są wymiary i waga powerbanku, i czy jest on odpowiedni do zabrania na pokład samolotu? 8. Czy powerbank ma wbudowany wyświetlacz? Jeśli tak, jakie informacje wyświetla? 9. Jakie akcesoria są dołączone do powerbanku (np. kable, adaptery)? 10. Jaki jest okres gwarancji oferowany przez producenta powerbanku? 11. Czy powerbank posiada funkcję jump startera? Jeśli tak, jakie pojazdy może uruchomić? 12. Jakie napięcia i prądy wyjściowe obsługuje powerbank, i jak wpływają one na szybkość ładowania? 13. Czy powerbank jest wyposażony w zintegrowany kabel? Jeśli tak, jakiego typu? 14. Jakie dodatkowe funkcje (np. latarka, podstawka, tryb trickle charge) oferuje powerbank? 15. Z jakiego materiału wykonano obudowę powerbanku i czy producent podkreśla jakieś ekologiczne aspekty produktu?</t>
+  </si>
+  <si>
+    <t>1. Jaka jest maksymalna prędkość odczytu sekwencyjnego tego dysku SSD i jak wpływa ona na jego wydajność w aplikacjach do gier? 2. Opisz typ pamięci używanej w tym dysku SSD (np. TLC, QLC, MLC) i wyjaśnij, jak wpływa ona na trwałość i wydajność dysku. 3. Jaki jest współczynnik kształtu tego dysku SSD i jak wpływa on na jego zgodność z nowoczesnymi laptopami lub komputerami stacjonarnymi? 4. Jak interfejs tego dysku SSD (np. PCIe NVMe 4.0 x4, SATA) wpływa na jego możliwości przesyłania danych? 5. Jaki jest wskaźnik całkowitej liczby zapisanych bajtów (TBW) dla tego dysku SSD i co wskazuje on na jego żywotność? 6. Czy ten dysk SSD zawiera radiator lub radiator i jak ta funkcja (lub jej brak) wpływa na jego wydajność cieplną podczas intensywnych zadań? 7. Jaki jest średni czas między awariami (MTBF) dla tego dysku SSD i jak odzwierciedla on niezawodność dysku? 8. W jaki sposób losowe odczytywanie IOPS (operacji wejścia/wyjścia na sekundę) tego dysku SSD wpływa na jego wydajność w scenariuszach obejmujących dostęp do małych plików, takich jak ładowanie zasobów gry? 9. Jakie konkretne technologie (np. S.M.A.R.T., TRIM, LDPC) są obsługiwane przez ten dysk SSD i w jaki sposób zwiększają jego funkcjonalność lub integralność danych? 10. Jaki jest okres gwarancji na ten dysk SSD i co sugeruje on na temat zaufania producenta do długowieczności produktu? 11. W jaki sposób wydajność energetyczna tego dysku SSD przyczynia się do jego przydatności do użytku w laptopach? 12. Czy ten dysk SSD jest kompatybilny z PlayStation 5 i jeśli tak, jakie korzyści wydajnościowe oferuje w grach na tej konsoli? 13. Jaka jest fizyczna waga tego dysku SSD i w jaki sposób może ona wpłynąć na jego użytkowanie w urządzeniach przenośnych? 14. W jaki sposób oprogramowanie dysku SSD (np. Samsung Magician, MSI Center, SSD Toolbox) zwiększa kontrolę użytkownika nad wydajnością i konserwacją dysku? 15. Na podstawie specyfikacji dysku SSD, do jakich typów obciążeń (np. gier, edycji wideo, ogólnego użytkowania komputera) jest on najlepiej przystosowany i dlaczego?</t>
+  </si>
+  <si>
+    <t>1. Jakie rodzaje aktywności fizycznych może śledzić ten smartwatch? 2. Jakie funkcje zdrowotne oferuje ten smartwatch w zakresie monitorowania parametrów ciała? 3. Jak długo smartwatch może działać na jednym ładowaniu w trybie normalnego użytkowania? 4. Jakie technologie łączności są dostępne w tym smartwatchu? 5. Czy ten smartwatch jest odporny na wodę? Jeśli tak, jaki jest jego poziom wodoszczelności? 6. Jakie materiały zostały użyte do wykonania koperty i paska tego smartwatcha? 7. Jakie funkcje telefoniczne są dostępne w tym smartwatchu? 8. Jakie funkcje nawigacyjne oferuje ten smartwatch? 9. Jaki typ wyświetlacza jest zastosowany w tym smartwatchu i jakie są jego kluczowe cechy? 10. Czy ten smartwatch obsługuje płatności zbliżeniowe? Jeśli tak, jakie technologie płatności są wspierane? 11. Jakie funkcje multimedialne są dostępne w tym smartwatchu? 12. Jakie dodatkowe funkcje, poza monitorowaniem aktywności i zdrowia, oferuje ten smartwatch? 13. Z jakimi systemami operacyjnymi smartfonów jest kompatybilny ten smartwatch? 14. Jakie dane dotyczące snu może monitorować ten smartwatch? 15. Jakie elementy są dołączone w zestawie z tym smartwatchem?.</t>
+  </si>
+  <si>
+    <t>1. Jaka jest podstawowa częstotliwość taktowania procesora graficznego w tej karcie graficznej? 2. Jaka jest częstotliwość taktowania procesora graficznego w trybie boost w tej karcie graficznej? 3. Ile pamięci VRAM ma ta karta graficzna i jaki jest jej typ? 4. Jaka jest szerokość magistrali pamięci tej karty graficznej? 5. Jaką technologię skalowania obsługuje ta karta graficzna? 6. Czy ta karta graficzna obsługuje ray tracing, a jeśli tak, to jaką generację lub wersję? 7. Ile rdzeni CUDA lub procesorów strumieniowych ma ta karta graficzna? 8. Jakiego typu gniazda PCIe używa ta karta graficzna i jaka jest jego konfiguracja linii? 9. Jakie są typy i liczba wyjść wyświetlacza dostępnych na tej karcie graficznej? 10. Ile monitorów może obsługiwać jednocześnie ta karta graficzna? 11. Jaka jest zalecana moc zasilacza dla tej karty graficznej? 12. Jaki typ układu chłodzenia jest używany w tej karcie graficznej i ile ma wentylatorów? 13. Czy ta karta graficzna ma oświetlenie RGB lub inne ulepszenia estetyczne? 14. Jaki jest rozmiar fizyczny (długość, szerokość, wysokość) tej karty graficznej? 15. Jakie konkretne technologie (np. NVIDIA Reflex, AMD FreeSync) są obsługiwane przez tę kartę graficzną w celu zwiększenia wydajności w grach?</t>
+  </si>
+  <si>
+    <t>1. Jakie jest główne przeznaczenie tej klawiatury (np. gry, praca biurowa, programowanie)? 2. Jakiego typu przełączniki wykorzystuje ta klawiatura i jakie są ich główne cechy? 3. Czy ta klawiatura obsługuje łączność bezprzewodową? Jeśli tak, jakie interfejsy bezprzewodowe są dostępne? 4. Jaki jest typ układu tej klawiatury (np. pełnowymiarowy, TKL, 60%)? 5. Czy ta klawiatura ma oświetlenie RGB i jeśli tak, jaki typ dostosowywania RGB jest dostępny (np. na klawisz, strefowy, jednokolorowy)? 6. Jakie materiały są używane w konstrukcji klawiatury i w jaki sposób przyczyniają się do jej trwałości lub estetyki? 7. Czy ta klawiatura obsługuje programowanie makr i jeśli tak, w jaki sposób można je skonfigurować? 8. Jakie systemy operacyjne są zgodne z tą klawiaturą? 9. Czy ta klawiatura zawiera podpórkę pod nadgarstki, a jeśli nie, czy jest ona dostępna jako opcjonalne akcesorium? 10. Jaki jest okres gwarancji na tę klawiaturę i kto ją zapewnia (producent czy sprzedawca)? 11. Jakie są wymiary i waga tej klawiatury i jak wpływają one na jej przenośność? 12. Czy ta klawiatura ma funkcję anti-ghosting lub N-key rollover i jakie korzyści przynosi to użytkownikowi? 13. Jakie dodatkowe akcesoria, jeśli takie są, są dołączone do tej klawiatury? 14. Czy ta klawiatura obsługuje przełączniki hot-swap i jeśli tak, jakie typy przełączników są kompatybilne? 15. Jakie konkretne funkcje oferuje ta klawiatura, aby zwiększyć komfort użytkownika lub ergonomię (np. regulowane nóżki, profile nasadek klawiszy, konstrukcja o niskim profilu)?</t>
+  </si>
+  <si>
+    <t>1. Jaki jest model procesora i jego specyfikacje (np. rdzenie, wątki, prędkość zegara) w laptopie? 2. Ile pamięci RAM jest zainstalowanej i jaki jest jej typ i prędkość? 3. Jaka jest pojemność pamięci masowej i typ (np. SSD, HDD) laptopa? 4. Czy laptop ma dedykowaną kartę graficzną, a jeśli tak, jaki jest jej model i pojemność pamięci? 5. Jaki jest rozmiar ekranu, rozdzielczość i częstotliwość odświeżania wyświetlacza laptopa? 6. Jaki typ technologii wyświetlania (np. IPS, OLED, WVA) jest używany w laptopie? 7. Czy laptop ma ekran dotykowy, a jeśli nie, jaki typ touchpada jest dołączony? 8. Jaki jest typ baterii i pojemność (jeśli podano) laptopa? 9. Jaki system operacyjny jest preinstalowany na laptopie? 10. Jakie opcje łączności (np. Wi-Fi, Bluetooth, LAN) są dostępne w laptopie? 11. Jakie porty i złącza (np. USB, HDMI, Thunderbolt) są zawarte w laptopie? 12. Czy laptop zawiera funkcje bezpieczeństwa, takie jak czytnik linii papilarnych lub szyfrowanie TPM? 13. Jaka jest waga i wymiary (wysokość, szerokość, głębokość) laptopa? 14. Jaki jest czas trwania i rodzaj gwarancji dołączonej do laptopa? 15. Czy laptop ma jakieś certyfikaty środowiskowe lub trwałości (np. MIL-STD-810H, EPEAT)?</t>
+  </si>
+  <si>
+    <t>1. Jaką rozdzielczość ekranu oferuje monitor? 2. Jaka jest częstotliwość odświeżania ekranu? 3. Jaki typ matrycy został zastosowany w monitorze? 4. Czy monitor obsługuje technologię HDR? Jeśli tak, to jaki standard? 5. Jaki jest czas reakcji matrycy monitora? 6. Jakie technologie synchronizacji są wspierane przez monitor? 7. Czy monitor posiada technologie ochrony oczu, takie jak redukcja migotania lub filtr światła niebieskiego? 8. Jaka jest jasność ekranu w cd/m²? 9. Jaki jest kontrast statyczny monitora? 10. Jakie złącza są dostępne w monitorze? 11. Czy monitor ma wbudowane głośniki? Jeśli tak, jaka jest ich moc? 12. Czy monitor umożliwia regulację wysokości, pochylenia lub obrotu ekranu? 13. Jaka jest klasa energetyczna monitora? 14. Jakie jest pokrycie przestrzeni barw (np. sRGB, DCI-P3) według specyfikacji? 15. Czy monitor jest zakrzywiony, a jeśli tak, jaki jest promień krzywizny?</t>
+  </si>
+  <si>
+    <t>1. Jaką maksymalną rozdzielczość DPI oferuje sensor myszy? 2. Jakie rodzaje łączności obsługuje mysz? 3. Ile przycisków ma mysz i czy są one programowalne? 4. Jaki jest czas pracy na baterii myszy po pełnym naładowaniu lub przy użyciu jednej baterii? 5. Czy mysz posiada podświetlenie, a jeśli tak, jakie elementy są podświetlane? 6. Jaki jest profil myszy (np. uniwersalny, praworęczny) i dla jakiego typu użytkownika jest przeznaczona? 7. Jakie dodatkowe akcesoria są dołączone do myszy? 8. Jaka jest waga myszy i czy jest ona uznawana za lekką w swojej kategorii? 9. Jaką technologię sensor wykorzystuje mysz i na jakich powierzchniach może działać? 10. Czy mysz oferuje regulację rozdzielczości DPI, a jeśli tak, w jakim zakresie? 11. Jaka jest żywotność przycisków myszy (w milionach kliknięć)? 12. Czy mysz posiada jakieś specjalne cechy ergonomiczne, takie jak antypoślizgowe panele lub pionowy kąt ułożenia dłoni? 13. Jakie oprogramowanie można wykorzystać do personalizacji ustawień myszy? 14. Jaki jest zasięg pracy myszy w trybie bezprzewodowym? 15. Czy mysz ma jakieś unikalne technologie, takie jak ciche kliknięcia, szybkie przewijanie lub stację dokującą?</t>
+  </si>
+  <si>
+    <t>1. Jaki jest czas pracy baterii słuchawek, gdy włączona jest aktywna redukcja szumów (ANC)? 2. Jaki typ wersji Bluetooth jest używany do łączności bezprzewodowej w słuchawkach? 3. Jaka jest średnica przetworników słuchawek i jak wpływa to na jakość dźwięku? 4. Czy model słuchawek obsługuje połączenie przewodowe, a jeśli tak, to jaki typ złącza jest używany? 5. Jaki jest maksymalny zasięg bezprzewodowy słuchawek? 6. Jakie materiały są używane do nauszników i jak wpływają one na komfort podczas dłuższego użytkowania? 7. Czy model słuchawek oferuje dedykowaną aplikację mobilną do personalizacji i jakie funkcje można za jej pomocą regulować? 8. Jaka jest waga słuchawek i jak wpływa to na przenośność? 9. Jakie kodeki audio są obsługiwane przez słuchawki do bezprzewodowej transmisji dźwięku? 10. Czy model słuchawek ma składaną konstrukcję i jak wpływa to na przechowywanie i przenoszenie? 11. Jaki jest czas ładowania słuchawek, aby osiągnąć pełną pojemność baterii? 12. Czy model słuchawek zawiera mikrofon, a jeśli tak, jaka technologia jest używana do poprawy jakości połączeń? 13. Jaki jest okres gwarancji producenta na słuchawki? 14. Jakie dodatkowe akcesoria są dołączone do słuchawek w zestawie? 15. Czy model słuchawek obsługuje połączenie wielopunktowe, co pozwala na jednoczesne podłączenie do wielu urządzeń?</t>
+  </si>
+  <si>
+    <t>1. Jaki jest producent i model tego tabletu? 2. Jaka jest przekątna ekranu tabletu i jaki typ ekranu został zastosowany? 3. Jaka jest rozdzielczość ekranu tego urządzenia? 4. Jaką pojemność pamięci wbudowanej oferuje ten tablet? 5. Ile wynosi pamięć RAM w tym tablecie? 6. Jaki system operacyjny jest zainstalowany na tym urządzeniu? 7. Jaka jest pojemność baterii w tym tablecie i jaki jest jej typ? 8. Jaką maksymalną moc ładowania obsługuje ten tablet? 9. Jakie rodzaje łączności bezprzewodowej są dostępne w tym tablecie (np. Wi-Fi, Bluetooth, LTE)? 10. Jakie aparaty fotograficzne (przedni i tylny) znajdują się w tym tablecie i jakie mają rozdzielczości? 11. Jakie czujniki są wbudowane w ten tablet (np. akcelerometr, żyroskop, czujnik światła)? 12. Jakie złącza fizyczne są dostępne w tym tablecie (np. USB, wyjście słuchawkowe, czytnik kart pamięci)? 13. Jakie dodatkowe informacje lub funkcje wyróżnia producent w opisie tego tabletu (np. skaner twarzy, odporność na wodę, obsługa rysika)? 14. Jaka jest waga i jakie są wymiary (szerokość, wysokość, grubość) tego tabletu? 15. Jak długo wynosi okres gwarancji producenta dla tego tabletu?</t>
+  </si>
+  <si>
+    <t>1. Jaka jest maksymalna prędkość transmisji bezprzewodowej obsługiwana przez ten router? 2. Jakie standardy Wi-Fi obsługuje ten router? 3. W jakich pasmach częstotliwości działa ten router (np. 2,4 GHz, 5 GHz, 6 GHz)? 4. Ile portów LAN jest dostępnych w tym routerze i jakie są ich prędkości? 5. Czy ten router obsługuje zabezpieczenia WPA3 i jakie inne protokoły bezpieczeństwa są dostępne? 6. Jakie typy anten (wewnętrzne lub zewnętrzne) wykorzystuje ten router i ile ich jest? 7. Jakie opcje zarządzania i konfiguracji są dostępne dla tego routera (np. interfejs internetowy, aplikacja mobilna)? 8. Czy ten router obsługuje funkcjonalność VPN i jeśli tak, jakie konkretne protokoły VPN są obsługiwane? 9. Jakie dodatkowe funkcje oferuje ten router, takie jak kontrola rodzicielska, QoS lub sieć Mesh? 10. Jakie są wymiary fizyczne (wysokość, szerokość, głębokość) i waga tego routera? 11. Jaki jest okres gwarancji producenta na ten router? 12. Czy ten router obsługuje technologie MU-MIMO lub OFDMA i w jaki sposób zwiększają one wydajność? 13. Jaki jest kolor tego routera i jakie akcesoria są dołączone do niego? 14. Czy ten router obsługuje zaawansowane funkcje sieciowe, takie jak Beamforming lub IPv6? 15. Czy ten router może być używany w trybach innych niż standardowy tryb routera (np. Access Point, Repeater)?</t>
+  </si>
 </sst>
 </file>
 
@@ -13375,7 +13414,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -13398,13 +13437,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -13709,13 +13762,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G260"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13737,8 +13791,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1275908</v>
       </c>
@@ -13760,8 +13817,11 @@
       <c r="G2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1315538</v>
       </c>
@@ -13783,8 +13843,11 @@
       <c r="G3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1309423</v>
       </c>
@@ -13806,8 +13869,11 @@
       <c r="G4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1276020</v>
       </c>
@@ -13829,8 +13895,11 @@
       <c r="G5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1276626</v>
       </c>
@@ -13852,8 +13921,11 @@
       <c r="G6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1308418</v>
       </c>
@@ -13875,8 +13947,11 @@
       <c r="G7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1306175</v>
       </c>
@@ -13898,8 +13973,11 @@
       <c r="G8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1311166</v>
       </c>
@@ -13921,8 +13999,11 @@
       <c r="G9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1275905</v>
       </c>
@@ -13944,8 +14025,11 @@
       <c r="G10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1301316</v>
       </c>
@@ -13967,8 +14051,11 @@
       <c r="G11" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1203369</v>
       </c>
@@ -13990,8 +14077,11 @@
       <c r="G12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1267692</v>
       </c>
@@ -14013,8 +14103,11 @@
       <c r="G13" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1281379</v>
       </c>
@@ -14036,8 +14129,11 @@
       <c r="G14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1308427</v>
       </c>
@@ -14059,8 +14155,11 @@
       <c r="G15" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1297576</v>
       </c>
@@ -14082,8 +14181,11 @@
       <c r="G16" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1311800</v>
       </c>
@@ -14105,8 +14207,11 @@
       <c r="G17" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1319519</v>
       </c>
@@ -14128,8 +14233,11 @@
       <c r="G18" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1314673</v>
       </c>
@@ -14151,8 +14259,11 @@
       <c r="G19" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1268020</v>
       </c>
@@ -14174,8 +14285,11 @@
       <c r="G20" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1195867</v>
       </c>
@@ -14197,8 +14311,11 @@
       <c r="G21" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1256852</v>
       </c>
@@ -14220,8 +14337,11 @@
       <c r="G22" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1299238</v>
       </c>
@@ -14243,8 +14363,11 @@
       <c r="G23" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1276972</v>
       </c>
@@ -14266,8 +14389,11 @@
       <c r="G24" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1274200</v>
       </c>
@@ -14289,8 +14415,11 @@
       <c r="G25" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1310912</v>
       </c>
@@ -14312,8 +14441,11 @@
       <c r="G26" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1294886</v>
       </c>
@@ -14335,8 +14467,11 @@
       <c r="G27" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1316771</v>
       </c>
@@ -14358,8 +14493,11 @@
       <c r="G28" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1276422</v>
       </c>
@@ -14381,8 +14519,11 @@
       <c r="G29" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1287637</v>
       </c>
@@ -14404,8 +14545,11 @@
       <c r="G30" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1310903</v>
       </c>
@@ -14427,8 +14571,11 @@
       <c r="G31" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1276909</v>
       </c>
@@ -14450,8 +14597,11 @@
       <c r="G32" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1220008</v>
       </c>
@@ -14473,8 +14623,11 @@
       <c r="G33" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1314072</v>
       </c>
@@ -14496,8 +14649,11 @@
       <c r="G34" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1245980</v>
       </c>
@@ -14519,8 +14675,11 @@
       <c r="G35" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1288162</v>
       </c>
@@ -14542,8 +14701,11 @@
       <c r="G36" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1178231</v>
       </c>
@@ -14562,8 +14724,11 @@
       <c r="F37" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1270311</v>
       </c>
@@ -14585,8 +14750,11 @@
       <c r="G38" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1310909</v>
       </c>
@@ -14608,8 +14776,11 @@
       <c r="G39" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1279543</v>
       </c>
@@ -14631,8 +14802,11 @@
       <c r="G40" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1284014</v>
       </c>
@@ -14654,8 +14828,11 @@
       <c r="G41" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1279537</v>
       </c>
@@ -14677,8 +14854,11 @@
       <c r="G42" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>691100</v>
       </c>
@@ -14700,8 +14880,11 @@
       <c r="G43" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>590339</v>
       </c>
@@ -14723,8 +14906,11 @@
       <c r="G44" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1309298</v>
       </c>
@@ -14746,8 +14932,11 @@
       <c r="G45" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1160141</v>
       </c>
@@ -14769,8 +14958,11 @@
       <c r="G46" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1163934</v>
       </c>
@@ -14792,8 +14984,11 @@
       <c r="G47" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>1311951</v>
       </c>
@@ -14815,8 +15010,11 @@
       <c r="G48" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>1290963</v>
       </c>
@@ -14838,8 +15036,11 @@
       <c r="G49" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1083717</v>
       </c>
@@ -14861,8 +15062,11 @@
       <c r="G50" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>1273617</v>
       </c>
@@ -14884,8 +15088,11 @@
       <c r="G51" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>1273429</v>
       </c>
@@ -14907,8 +15114,11 @@
       <c r="G52" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>590335</v>
       </c>
@@ -14930,8 +15140,11 @@
       <c r="G53" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>1146134</v>
       </c>
@@ -14953,8 +15166,11 @@
       <c r="G54" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1290960</v>
       </c>
@@ -14976,8 +15192,11 @@
       <c r="G55" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>621625</v>
       </c>
@@ -14999,8 +15218,11 @@
       <c r="G56" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1083719</v>
       </c>
@@ -15022,8 +15244,11 @@
       <c r="G57" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1273616</v>
       </c>
@@ -15045,8 +15270,11 @@
       <c r="G58" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1275363</v>
       </c>
@@ -15068,8 +15296,11 @@
       <c r="G59" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>1146135</v>
       </c>
@@ -15091,8 +15322,11 @@
       <c r="G60" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>691108</v>
       </c>
@@ -15114,8 +15348,11 @@
       <c r="G61" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>590340</v>
       </c>
@@ -15137,8 +15374,11 @@
       <c r="G62" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>704554</v>
       </c>
@@ -15160,8 +15400,11 @@
       <c r="G63" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>734881</v>
       </c>
@@ -15183,8 +15426,11 @@
       <c r="G64" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>1138151</v>
       </c>
@@ -15206,8 +15452,11 @@
       <c r="G65" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1154568</v>
       </c>
@@ -15229,8 +15478,11 @@
       <c r="G66" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H66" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>1145893</v>
       </c>
@@ -15252,8 +15504,11 @@
       <c r="G67" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>1206542</v>
       </c>
@@ -15275,8 +15530,11 @@
       <c r="G68" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>1278012</v>
       </c>
@@ -15298,8 +15556,11 @@
       <c r="G69" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>1242902</v>
       </c>
@@ -15321,8 +15582,11 @@
       <c r="G70" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H70" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>1311370</v>
       </c>
@@ -15344,8 +15608,11 @@
       <c r="G71" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H71" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>1262079</v>
       </c>
@@ -15367,8 +15634,11 @@
       <c r="G72" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H72" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>1273180</v>
       </c>
@@ -15390,8 +15660,11 @@
       <c r="G73" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>1154522</v>
       </c>
@@ -15413,8 +15686,11 @@
       <c r="G74" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>1141440</v>
       </c>
@@ -15436,8 +15712,11 @@
       <c r="G75" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H75" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>1276872</v>
       </c>
@@ -15459,8 +15738,11 @@
       <c r="G76" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H76" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>1276873</v>
       </c>
@@ -15482,8 +15764,11 @@
       <c r="G77" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H77" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>1224532</v>
       </c>
@@ -15505,8 +15790,11 @@
       <c r="G78" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H78" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>1204690</v>
       </c>
@@ -15528,8 +15816,11 @@
       <c r="G79" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H79" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>1150231</v>
       </c>
@@ -15551,8 +15842,11 @@
       <c r="G80" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H80" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>1241003</v>
       </c>
@@ -15574,8 +15868,11 @@
       <c r="G81" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H81" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>1229681</v>
       </c>
@@ -15597,8 +15894,11 @@
       <c r="G82" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H82" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>1233789</v>
       </c>
@@ -15620,8 +15920,11 @@
       <c r="G83" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H83" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>1048088</v>
       </c>
@@ -15643,8 +15946,11 @@
       <c r="G84" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H84" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>1221697</v>
       </c>
@@ -15666,8 +15972,11 @@
       <c r="G85" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H85" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>1226981</v>
       </c>
@@ -15689,8 +15998,11 @@
       <c r="G86" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H86" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>1300165</v>
       </c>
@@ -15712,8 +16024,11 @@
       <c r="G87" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H87" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>715089</v>
       </c>
@@ -15735,8 +16050,11 @@
       <c r="G88" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H88" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>742554</v>
       </c>
@@ -15758,8 +16076,11 @@
       <c r="G89" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H89" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>661713</v>
       </c>
@@ -15781,8 +16102,11 @@
       <c r="G90" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H90" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>1309819</v>
       </c>
@@ -15804,8 +16128,11 @@
       <c r="G91" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H91" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>1335485</v>
       </c>
@@ -15827,8 +16154,11 @@
       <c r="G92" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H92" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>1226950</v>
       </c>
@@ -15850,8 +16180,11 @@
       <c r="G93" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H93" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>1314559</v>
       </c>
@@ -15873,8 +16206,11 @@
       <c r="G94" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H94" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>1104110</v>
       </c>
@@ -15896,8 +16232,11 @@
       <c r="G95" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H95" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>1165457</v>
       </c>
@@ -15919,8 +16258,11 @@
       <c r="G96" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H96" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>1299534</v>
       </c>
@@ -15942,8 +16284,11 @@
       <c r="G97" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H97" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1072799</v>
       </c>
@@ -15965,8 +16310,11 @@
       <c r="G98" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H98" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>1300167</v>
       </c>
@@ -15988,8 +16336,11 @@
       <c r="G99" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H99" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>1330926</v>
       </c>
@@ -16011,8 +16362,11 @@
       <c r="G100" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H100" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>1177472</v>
       </c>
@@ -16034,8 +16388,11 @@
       <c r="G101" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H101" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>1321575</v>
       </c>
@@ -16057,8 +16414,11 @@
       <c r="G102" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H102" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>1309821</v>
       </c>
@@ -16080,8 +16440,11 @@
       <c r="G103" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H103" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>1331028</v>
       </c>
@@ -16103,8 +16466,11 @@
       <c r="G104" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H104" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>1309179</v>
       </c>
@@ -16126,8 +16492,11 @@
       <c r="G105" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H105" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>687373</v>
       </c>
@@ -16149,8 +16518,11 @@
       <c r="G106" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H106" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>1316744</v>
       </c>
@@ -16172,8 +16544,11 @@
       <c r="G107" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H107" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>338132</v>
       </c>
@@ -16195,8 +16570,11 @@
       <c r="G108" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H108" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>1314060</v>
       </c>
@@ -16218,8 +16596,11 @@
       <c r="G109" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H109" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>1310434</v>
       </c>
@@ -16241,8 +16622,11 @@
       <c r="G110" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H110" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>57307</v>
       </c>
@@ -16264,8 +16648,11 @@
       <c r="G111" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H111" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>741760</v>
       </c>
@@ -16287,8 +16674,11 @@
       <c r="G112" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H112" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>1219218</v>
       </c>
@@ -16310,8 +16700,11 @@
       <c r="G113" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H113" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>741766</v>
       </c>
@@ -16333,8 +16726,11 @@
       <c r="G114" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H114" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>1301397</v>
       </c>
@@ -16356,8 +16752,11 @@
       <c r="G115" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H115" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>595144</v>
       </c>
@@ -16379,8 +16778,11 @@
       <c r="G116" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H116" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>1290024</v>
       </c>
@@ -16402,8 +16804,11 @@
       <c r="G117" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H117" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>719865</v>
       </c>
@@ -16425,8 +16830,11 @@
       <c r="G118" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H118" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>1290020</v>
       </c>
@@ -16448,8 +16856,11 @@
       <c r="G119" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H119" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>1310435</v>
       </c>
@@ -16471,8 +16882,11 @@
       <c r="G120" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H120" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>1069873</v>
       </c>
@@ -16494,8 +16908,11 @@
       <c r="G121" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H121" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>1056646</v>
       </c>
@@ -16517,8 +16934,11 @@
       <c r="G122" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H122" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>679823</v>
       </c>
@@ -16540,8 +16960,11 @@
       <c r="G123" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H123" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>1066515</v>
       </c>
@@ -16563,8 +16986,11 @@
       <c r="G124" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H124" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>1266238</v>
       </c>
@@ -16586,8 +17012,11 @@
       <c r="G125" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H125" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>148477</v>
       </c>
@@ -16609,8 +17038,11 @@
       <c r="G126" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H126" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>1331550</v>
       </c>
@@ -16632,8 +17064,11 @@
       <c r="G127" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H127" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>1307417</v>
       </c>
@@ -16655,8 +17090,11 @@
       <c r="G128" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H128" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>1328947</v>
       </c>
@@ -16678,8 +17116,11 @@
       <c r="G129" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H129" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1301192</v>
       </c>
@@ -16701,8 +17142,11 @@
       <c r="G130" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H130" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>1297981</v>
       </c>
@@ -16724,8 +17168,11 @@
       <c r="G131" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H131" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>1241536</v>
       </c>
@@ -16747,8 +17194,11 @@
       <c r="G132" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H132" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>1323373</v>
       </c>
@@ -16770,8 +17220,11 @@
       <c r="G133" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H133" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>1271993</v>
       </c>
@@ -16793,8 +17246,11 @@
       <c r="G134" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H134" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>1292135</v>
       </c>
@@ -16816,8 +17272,11 @@
       <c r="G135" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H135" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>1292431</v>
       </c>
@@ -16839,8 +17298,11 @@
       <c r="G136" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H136" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>1281089</v>
       </c>
@@ -16862,8 +17324,11 @@
       <c r="G137" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H137" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>1312203</v>
       </c>
@@ -16885,8 +17350,11 @@
       <c r="G138" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H138" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>1299517</v>
       </c>
@@ -16908,8 +17376,11 @@
       <c r="G139" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H139" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>1298239</v>
       </c>
@@ -16931,8 +17402,11 @@
       <c r="G140" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H140" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>1222789</v>
       </c>
@@ -16954,8 +17428,11 @@
       <c r="G141" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H141" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>1271981</v>
       </c>
@@ -16977,8 +17454,11 @@
       <c r="G142" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H142" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>1317567</v>
       </c>
@@ -17000,8 +17480,11 @@
       <c r="G143" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H143" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>1273586</v>
       </c>
@@ -17023,8 +17506,11 @@
       <c r="G144" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H144" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>1296932</v>
       </c>
@@ -17046,8 +17532,11 @@
       <c r="G145" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H145" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>1316334</v>
       </c>
@@ -17069,8 +17558,11 @@
       <c r="G146" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H146" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>1276733</v>
       </c>
@@ -17092,8 +17584,11 @@
       <c r="G147" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H147" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>1228926</v>
       </c>
@@ -17115,8 +17610,11 @@
       <c r="G148" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H148" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>1241603</v>
       </c>
@@ -17138,8 +17636,11 @@
       <c r="G149" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H149" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>1247744</v>
       </c>
@@ -17161,8 +17662,11 @@
       <c r="G150" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H150" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>1123913</v>
       </c>
@@ -17184,8 +17688,11 @@
       <c r="G151" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H151" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>1210799</v>
       </c>
@@ -17207,8 +17714,11 @@
       <c r="G152" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H152" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>1109993</v>
       </c>
@@ -17230,8 +17740,11 @@
       <c r="G153" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H153" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>1265660</v>
       </c>
@@ -17253,8 +17766,11 @@
       <c r="G154" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H154" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>1222094</v>
       </c>
@@ -17276,8 +17792,11 @@
       <c r="G155" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H155" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>1328816</v>
       </c>
@@ -17299,8 +17818,11 @@
       <c r="G156" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H156" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>1212512</v>
       </c>
@@ -17322,8 +17844,11 @@
       <c r="G157" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H157" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>1328818</v>
       </c>
@@ -17345,8 +17870,11 @@
       <c r="G158" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H158" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>1228812</v>
       </c>
@@ -17368,8 +17896,11 @@
       <c r="G159" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H159" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>1160222</v>
       </c>
@@ -17391,8 +17922,11 @@
       <c r="G160" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H160" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>1092721</v>
       </c>
@@ -17414,8 +17948,11 @@
       <c r="G161" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H161" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1333834</v>
       </c>
@@ -17437,8 +17974,11 @@
       <c r="G162" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H162" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>1266587</v>
       </c>
@@ -17460,8 +18000,11 @@
       <c r="G163" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H163" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>1297644</v>
       </c>
@@ -17483,8 +18026,11 @@
       <c r="G164" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H164" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>1319221</v>
       </c>
@@ -17506,8 +18052,11 @@
       <c r="G165" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H165" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>1276730</v>
       </c>
@@ -17529,8 +18078,11 @@
       <c r="G166" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H166" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>1328819</v>
       </c>
@@ -17552,8 +18104,11 @@
       <c r="G167" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H167" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>657424</v>
       </c>
@@ -17575,8 +18130,11 @@
       <c r="G168" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H168" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>1056271</v>
       </c>
@@ -17598,8 +18156,11 @@
       <c r="G169" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H169" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>1145833</v>
       </c>
@@ -17621,8 +18182,11 @@
       <c r="G170" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H170" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>1230134</v>
       </c>
@@ -17644,8 +18208,11 @@
       <c r="G171" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H171" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>1294102</v>
       </c>
@@ -17667,8 +18234,11 @@
       <c r="G172" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H172" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>713778</v>
       </c>
@@ -17690,8 +18260,11 @@
       <c r="G173" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H173" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>615023</v>
       </c>
@@ -17713,8 +18286,11 @@
       <c r="G174" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H174" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>434026</v>
       </c>
@@ -17736,8 +18312,11 @@
       <c r="G175" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H175" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>652970</v>
       </c>
@@ -17759,8 +18338,11 @@
       <c r="G176" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H176" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>1258807</v>
       </c>
@@ -17782,8 +18364,11 @@
       <c r="G177" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H177" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>1315345</v>
       </c>
@@ -17805,8 +18390,11 @@
       <c r="G178" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H178" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>1145831</v>
       </c>
@@ -17828,8 +18416,11 @@
       <c r="G179" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H179" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>1294942</v>
       </c>
@@ -17851,8 +18442,11 @@
       <c r="G180" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H180" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>1078841</v>
       </c>
@@ -17874,8 +18468,11 @@
       <c r="G181" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H181" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>1172768</v>
       </c>
@@ -17897,8 +18494,11 @@
       <c r="G182" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H182" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>1219968</v>
       </c>
@@ -17920,8 +18520,11 @@
       <c r="G183" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H183" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>475517</v>
       </c>
@@ -17943,8 +18546,11 @@
       <c r="G184" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H184" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>1294120</v>
       </c>
@@ -17966,8 +18572,11 @@
       <c r="G185" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H185" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>574603</v>
       </c>
@@ -17989,8 +18598,11 @@
       <c r="G186" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H186" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>679990</v>
       </c>
@@ -18012,8 +18624,11 @@
       <c r="G187" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H187" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>1244301</v>
       </c>
@@ -18035,8 +18650,11 @@
       <c r="G188" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H188" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>743071</v>
       </c>
@@ -18058,8 +18676,11 @@
       <c r="G189" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H189" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>1276183</v>
       </c>
@@ -18081,8 +18702,11 @@
       <c r="G190" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H190" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>1078835</v>
       </c>
@@ -18104,8 +18728,11 @@
       <c r="G191" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H191" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>1066503</v>
       </c>
@@ -18127,8 +18754,11 @@
       <c r="G192" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H192" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>1120138</v>
       </c>
@@ -18150,8 +18780,11 @@
       <c r="G193" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H193" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1237164</v>
       </c>
@@ -18173,8 +18806,11 @@
       <c r="G194" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H194" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>1163212</v>
       </c>
@@ -18196,8 +18832,11 @@
       <c r="G195" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H195" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>1119466</v>
       </c>
@@ -18219,8 +18858,11 @@
       <c r="G196" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H196" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>1237155</v>
       </c>
@@ -18242,8 +18884,11 @@
       <c r="G197" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H197" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>717575</v>
       </c>
@@ -18265,8 +18910,11 @@
       <c r="G198" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H198" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>1205703</v>
       </c>
@@ -18288,8 +18936,11 @@
       <c r="G199" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H199" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>1175479</v>
       </c>
@@ -18311,8 +18962,11 @@
       <c r="G200" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H200" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>1205701</v>
       </c>
@@ -18334,8 +18988,11 @@
       <c r="G201" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H201" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>1163204</v>
       </c>
@@ -18357,8 +19014,11 @@
       <c r="G202" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H202" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>1161930</v>
       </c>
@@ -18380,8 +19040,11 @@
       <c r="G203" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H203" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>1186703</v>
       </c>
@@ -18403,8 +19066,11 @@
       <c r="G204" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H204" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>747460</v>
       </c>
@@ -18426,8 +19092,11 @@
       <c r="G205" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H205" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>1278727</v>
       </c>
@@ -18449,8 +19118,11 @@
       <c r="G206" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H206" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>1068860</v>
       </c>
@@ -18472,8 +19144,11 @@
       <c r="G207" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H207" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>1317712</v>
       </c>
@@ -18495,8 +19170,11 @@
       <c r="G208" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H208" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>1241587</v>
       </c>
@@ -18518,8 +19196,11 @@
       <c r="G209" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H209" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>1198955</v>
       </c>
@@ -18541,8 +19222,11 @@
       <c r="G210" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H210" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>1119463</v>
       </c>
@@ -18564,8 +19248,11 @@
       <c r="G211" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H211" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>1119461</v>
       </c>
@@ -18587,8 +19274,11 @@
       <c r="G212" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H212" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>1119459</v>
       </c>
@@ -18610,8 +19300,11 @@
       <c r="G213" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H213" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>1285257</v>
       </c>
@@ -18633,8 +19326,11 @@
       <c r="G214" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H214" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>1285147</v>
       </c>
@@ -18656,8 +19352,11 @@
       <c r="G215" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H215" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>1244354</v>
       </c>
@@ -18679,8 +19378,11 @@
       <c r="G216" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H216" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>1229062</v>
       </c>
@@ -18702,8 +19404,11 @@
       <c r="G217" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H217" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>1265852</v>
       </c>
@@ -18725,8 +19430,11 @@
       <c r="G218" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H218" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>1316243</v>
       </c>
@@ -18748,8 +19456,11 @@
       <c r="G219" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H219" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>1278400</v>
       </c>
@@ -18771,8 +19482,11 @@
       <c r="G220" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H220" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>1291199</v>
       </c>
@@ -18794,8 +19508,11 @@
       <c r="G221" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H221" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>1313287</v>
       </c>
@@ -18817,8 +19534,11 @@
       <c r="G222" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H222" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>1307531</v>
       </c>
@@ -18840,8 +19560,11 @@
       <c r="G223" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H223" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>1288372</v>
       </c>
@@ -18863,8 +19586,11 @@
       <c r="G224" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H224" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>1314535</v>
       </c>
@@ -18886,8 +19612,11 @@
       <c r="G225" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H225" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1306362</v>
       </c>
@@ -18909,8 +19638,11 @@
       <c r="G226" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H226" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>1210598</v>
       </c>
@@ -18932,8 +19664,11 @@
       <c r="G227" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H227" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>1244945</v>
       </c>
@@ -18955,8 +19690,11 @@
       <c r="G228" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H228" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>1233939</v>
       </c>
@@ -18978,8 +19716,11 @@
       <c r="G229" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H229" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>1313413</v>
       </c>
@@ -19001,8 +19742,11 @@
       <c r="G230" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H230" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>1165458</v>
       </c>
@@ -19024,8 +19768,11 @@
       <c r="G231" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H231" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>1265851</v>
       </c>
@@ -19047,8 +19794,11 @@
       <c r="G232" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H232" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>1314534</v>
       </c>
@@ -19070,8 +19820,11 @@
       <c r="G233" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H233" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>1195782</v>
       </c>
@@ -19093,8 +19846,11 @@
       <c r="G234" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H234" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>1285144</v>
       </c>
@@ -19116,8 +19872,11 @@
       <c r="G235" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H235" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>1313286</v>
       </c>
@@ -19139,8 +19898,11 @@
       <c r="G236" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H236" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>1313412</v>
       </c>
@@ -19162,8 +19924,11 @@
       <c r="G237" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H237" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>1262454</v>
       </c>
@@ -19185,8 +19950,11 @@
       <c r="G238" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H238" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>1313415</v>
       </c>
@@ -19208,8 +19976,11 @@
       <c r="G239" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H239" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>1290961</v>
       </c>
@@ -19231,8 +20002,11 @@
       <c r="G240" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H240" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>1244381</v>
       </c>
@@ -19254,8 +20028,11 @@
       <c r="G241" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H241" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>1134664</v>
       </c>
@@ -19277,8 +20054,11 @@
       <c r="G242" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H242" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>1168226</v>
       </c>
@@ -19300,8 +20080,11 @@
       <c r="G243" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H243" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>1291825</v>
       </c>
@@ -19323,8 +20106,11 @@
       <c r="G244" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H244" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>466049</v>
       </c>
@@ -19346,8 +20132,11 @@
       <c r="G245" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H245" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>1294998</v>
       </c>
@@ -19369,8 +20158,11 @@
       <c r="G246" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H246" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>1271919</v>
       </c>
@@ -19392,8 +20184,11 @@
       <c r="G247" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H247" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>1288081</v>
       </c>
@@ -19415,8 +20210,11 @@
       <c r="G248" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H248" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>1274966</v>
       </c>
@@ -19438,8 +20236,11 @@
       <c r="G249" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H249" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>1249062</v>
       </c>
@@ -19461,8 +20262,11 @@
       <c r="G250" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H250" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>521479</v>
       </c>
@@ -19484,8 +20288,11 @@
       <c r="G251" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H251" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>1290381</v>
       </c>
@@ -19507,8 +20314,11 @@
       <c r="G252" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H252" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>1168233</v>
       </c>
@@ -19530,8 +20340,11 @@
       <c r="G253" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H253" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>1294051</v>
       </c>
@@ -19553,8 +20366,11 @@
       <c r="G254" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H254" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>682700</v>
       </c>
@@ -19576,8 +20392,11 @@
       <c r="G255" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H255" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>718522</v>
       </c>
@@ -19599,8 +20418,11 @@
       <c r="G256" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H256" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>1260308</v>
       </c>
@@ -19622,8 +20444,11 @@
       <c r="G257" t="s">
         <v>862</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H257" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1212069</v>
       </c>
@@ -19645,8 +20470,11 @@
       <c r="G258" t="s">
         <v>865</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H258" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>1205881</v>
       </c>
@@ -19668,8 +20496,11 @@
       <c r="G259" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H259" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>1219899</v>
       </c>
@@ -19690,6 +20521,9 @@
       </c>
       <c r="G260" t="s">
         <v>871</v>
+      </c>
+      <c r="H260" t="s">
+        <v>889</v>
       </c>
     </row>
   </sheetData>
